--- a/simulatedData/dataset_hypothetical.xlsx
+++ b/simulatedData/dataset_hypothetical.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L130"/>
+  <dimension ref="A1:L132"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -504,1895 +504,1895 @@
         <v>0</v>
       </c>
       <c r="E2" t="n">
-        <v>9.699347069291395</v>
+        <v>9.699347069291397</v>
       </c>
       <c r="F2" t="n">
-        <v>4.985069224042764</v>
+        <v>4.985069224042763</v>
       </c>
       <c r="G2" t="n">
         <v>0</v>
       </c>
       <c r="H2" t="n">
-        <v>2.697430405583722</v>
+        <v>2.69743038542935</v>
       </c>
       <c r="I2" t="n">
-        <v>50.0993040383034</v>
+        <v>50.0993034714063</v>
       </c>
       <c r="J2" t="n">
         <v>0</v>
       </c>
       <c r="K2" t="n">
-        <v>3.092067180779261</v>
+        <v>3.092067173384319</v>
       </c>
       <c r="L2" t="n">
-        <v>25.25641040310607</v>
+        <v>25.25641044512075</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>1.59700622192675e-11</v>
+        <v>4.818890932283339e-12</v>
       </c>
       <c r="B3" t="n">
         <v>0</v>
       </c>
       <c r="C3" t="n">
-        <v>-13.75</v>
+        <v>-24</v>
       </c>
       <c r="D3" t="n">
         <v>0</v>
       </c>
       <c r="E3" t="n">
-        <v>8.893963074455888</v>
+        <v>9.63035488551003</v>
       </c>
       <c r="F3" t="n">
-        <v>5.437790479813613</v>
+        <v>5.020873794760699</v>
       </c>
       <c r="G3" t="n">
         <v>0</v>
       </c>
       <c r="H3" t="n">
-        <v>3.462688404189407</v>
+        <v>2.758249423216762</v>
       </c>
       <c r="I3" t="n">
-        <v>36.69925568724278</v>
+        <v>48.61131297180568</v>
       </c>
       <c r="J3" t="n">
         <v>0</v>
       </c>
       <c r="K3" t="n">
-        <v>4.064561490513734</v>
+        <v>3.176064831617197</v>
       </c>
       <c r="L3" t="n">
-        <v>18.9403806800143</v>
+        <v>24.5436117665439</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>1.507349472382152e-11</v>
+        <v>4.815811529851255e-12</v>
       </c>
       <c r="B4" t="n">
         <v>0</v>
       </c>
       <c r="C4" t="n">
-        <v>-2.5</v>
+        <v>-23</v>
       </c>
       <c r="D4" t="n">
         <v>0</v>
       </c>
       <c r="E4" t="n">
-        <v>8.033893955626731</v>
+        <v>9.560827209729428</v>
       </c>
       <c r="F4" t="n">
-        <v>6.021981359610387</v>
+        <v>5.057481072452409</v>
       </c>
       <c r="G4" t="n">
         <v>0</v>
       </c>
       <c r="H4" t="n">
-        <v>4.31742026496268</v>
+        <v>2.82085533822959</v>
       </c>
       <c r="I4" t="n">
-        <v>28.63990654393838</v>
+        <v>47.18827644611995</v>
       </c>
       <c r="J4" t="n">
         <v>0</v>
       </c>
       <c r="K4" t="n">
-        <v>5.055702035797738</v>
+        <v>3.260709249356306</v>
       </c>
       <c r="L4" t="n">
-        <v>15.12651732498182</v>
+        <v>23.86623886383631</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>1.130749740890322</v>
+        <v>4.810787306799591e-12</v>
       </c>
       <c r="B5" t="n">
         <v>0</v>
       </c>
       <c r="C5" t="n">
-        <v>8.75</v>
+        <v>-22</v>
       </c>
       <c r="D5" t="n">
         <v>0</v>
       </c>
       <c r="E5" t="n">
-        <v>7.137381015435102</v>
+        <v>9.490772943835177</v>
       </c>
       <c r="F5" t="n">
-        <v>6.781742360490201</v>
+        <v>5.094910212584622</v>
       </c>
       <c r="G5" t="n">
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>5.150212148608645</v>
+        <v>2.885113010565214</v>
       </c>
       <c r="I5" t="n">
-        <v>23.69073351504635</v>
+        <v>45.82807871494958</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>6.013539744734469</v>
+        <v>3.345941090590222</v>
       </c>
       <c r="L5" t="n">
-        <v>12.67302773292551</v>
+        <v>23.22209150109784</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>8.678847465867547</v>
+        <v>4.803835669331699e-12</v>
       </c>
       <c r="B6" t="n">
         <v>0</v>
       </c>
       <c r="C6" t="n">
-        <v>20</v>
+        <v>-21</v>
       </c>
       <c r="D6" t="n">
         <v>0</v>
       </c>
       <c r="E6" t="n">
-        <v>6.22981468054237</v>
+        <v>9.420201171386378</v>
       </c>
       <c r="F6" t="n">
-        <v>7.775428450084861</v>
+        <v>5.133180979166142</v>
       </c>
       <c r="G6" t="n">
         <v>0</v>
       </c>
       <c r="H6" t="n">
-        <v>5.846909926368793</v>
+        <v>2.950892882690657</v>
       </c>
       <c r="I6" t="n">
-        <v>20.72742782212901</v>
+        <v>44.5284663082974</v>
       </c>
       <c r="J6" t="n">
         <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>6.810947385881176</v>
+        <v>3.431702821871986</v>
       </c>
       <c r="L6" t="n">
-        <v>11.16889058380283</v>
+        <v>22.60912863329828</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>-1.246514748113091e-12</v>
+        <v>4.794974800622795e-12</v>
       </c>
       <c r="B7" t="n">
-        <v>80</v>
+        <v>0</v>
       </c>
       <c r="C7" t="n">
-        <v>-25</v>
+        <v>-20</v>
       </c>
       <c r="D7" t="n">
         <v>0</v>
       </c>
       <c r="E7" t="n">
-        <v>9.699347069291383</v>
+        <v>9.349121163616877</v>
       </c>
       <c r="F7" t="n">
-        <v>4.985069224042773</v>
+        <v>5.172313763739869</v>
       </c>
       <c r="G7" t="n">
         <v>0</v>
       </c>
       <c r="H7" t="n">
-        <v>2.697430406208522</v>
+        <v>3.018070959187208</v>
       </c>
       <c r="I7" t="n">
-        <v>50.09930405710428</v>
+        <v>43.2870928103194</v>
       </c>
       <c r="J7" t="n">
         <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>1.851286181708365</v>
+        <v>3.517939749213151</v>
       </c>
       <c r="L7" t="n">
-        <v>45.44973876386989</v>
+        <v>22.02544939518506</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>4.66354120409438e-12</v>
+        <v>4.784223650566282e-12</v>
       </c>
       <c r="B8" t="n">
-        <v>80</v>
+        <v>0</v>
       </c>
       <c r="C8" t="n">
-        <v>-13.75</v>
+        <v>-19</v>
       </c>
       <c r="D8" t="n">
         <v>0</v>
       </c>
       <c r="E8" t="n">
-        <v>8.893963074455879</v>
+        <v>9.277542385800684</v>
       </c>
       <c r="F8" t="n">
-        <v>5.437790479813626</v>
+        <v>5.21232960476861</v>
       </c>
       <c r="G8" t="n">
         <v>0</v>
       </c>
       <c r="H8" t="n">
-        <v>3.462688417353021</v>
+        <v>3.086528906612338</v>
       </c>
       <c r="I8" t="n">
-        <v>36.699255452372</v>
+        <v>42.10156260324491</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>2.692712473971542</v>
+        <v>3.604599176807855</v>
       </c>
       <c r="L8" t="n">
-        <v>29.33723733507603</v>
+        <v>21.46928765764942</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>1.496922028887749e-11</v>
+        <v>1.615375460547206e-11</v>
       </c>
       <c r="B9" t="n">
-        <v>80</v>
+        <v>0</v>
       </c>
       <c r="C9" t="n">
-        <v>-2.5</v>
+        <v>-18</v>
       </c>
       <c r="D9" t="n">
         <v>0</v>
       </c>
       <c r="E9" t="n">
-        <v>8.033893955626722</v>
+        <v>9.205474504005355</v>
       </c>
       <c r="F9" t="n">
-        <v>6.021981359610403</v>
+        <v>5.253250207385433</v>
       </c>
       <c r="G9" t="n">
         <v>0</v>
       </c>
       <c r="H9" t="n">
-        <v>4.317420249584317</v>
+        <v>3.156153512598828</v>
       </c>
       <c r="I9" t="n">
-        <v>28.63990669631185</v>
+        <v>40.9694764901717</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
       </c>
       <c r="K9" t="n">
-        <v>3.62178686075474</v>
+        <v>3.691630534726485</v>
       </c>
       <c r="L9" t="n">
-        <v>21.3623889381296</v>
+        <v>20.93900050172503</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>1.130749740895365</v>
+        <v>1.611868224115192e-11</v>
       </c>
       <c r="B10" t="n">
-        <v>80</v>
+        <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>8.75</v>
+        <v>-17</v>
       </c>
       <c r="D10" t="n">
         <v>0</v>
       </c>
       <c r="E10" t="n">
-        <v>7.13738101543509</v>
+        <v>9.132927392258562</v>
       </c>
       <c r="F10" t="n">
-        <v>6.781742360490131</v>
+        <v>5.295097963471854</v>
       </c>
       <c r="G10" t="n">
         <v>0</v>
       </c>
       <c r="H10" t="n">
-        <v>5.15021214860514</v>
+        <v>3.226838708796441</v>
       </c>
       <c r="I10" t="n">
-        <v>23.69073351507986</v>
+        <v>39.88840949574709</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
       </c>
       <c r="K10" t="n">
-        <v>4.535282099547086</v>
+        <v>3.778985064195272</v>
       </c>
       <c r="L10" t="n">
-        <v>16.91156195179535</v>
+        <v>20.43306025874206</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>6.587348719392646</v>
+        <v>4.740829331029515e-12</v>
       </c>
       <c r="B11" t="n">
-        <v>80</v>
+        <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>20</v>
+        <v>-16</v>
       </c>
       <c r="D11" t="n">
         <v>0</v>
       </c>
       <c r="E11" t="n">
-        <v>6.229814680542377</v>
+        <v>9.059911140154993</v>
       </c>
       <c r="F11" t="n">
-        <v>7.775428450084768</v>
+        <v>5.337895972019203</v>
       </c>
       <c r="G11" t="n">
         <v>0</v>
       </c>
       <c r="H11" t="n">
-        <v>5.846909926368791</v>
+        <v>3.298482028508494</v>
       </c>
       <c r="I11" t="n">
-        <v>20.72742782212902</v>
+        <v>38.85601511690004</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
       </c>
       <c r="K11" t="n">
-        <v>5.37836943030751</v>
+        <v>3.866615747698372</v>
       </c>
       <c r="L11" t="n">
-        <v>14.19932256826142</v>
+        <v>19.95004562846234</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>2.054415328636697</v>
+        <v>4.722721599512451e-12</v>
       </c>
       <c r="B12" t="n">
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>-25</v>
+        <v>-15</v>
       </c>
       <c r="D12" t="n">
         <v>0</v>
       </c>
       <c r="E12" t="n">
-        <v>9.699347069291399</v>
+        <v>8.986436060932464</v>
       </c>
       <c r="F12" t="n">
-        <v>4.985069224042763</v>
+        <v>5.381668059720168</v>
       </c>
       <c r="G12" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="H12" t="n">
-        <v>2.683989998574744</v>
+        <v>3.370986326462548</v>
       </c>
       <c r="I12" t="n">
-        <v>50.44368285083898</v>
+        <v>37.8699922225055</v>
       </c>
       <c r="J12" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="K12" t="n">
-        <v>3.072411329380345</v>
+        <v>3.954477138722531</v>
       </c>
       <c r="L12" t="n">
-        <v>25.42946125387104</v>
+        <v>19.48863399885695</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>14.86183105254005</v>
+        <v>4.702829566374978e-12</v>
       </c>
       <c r="B13" t="n">
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>-13.75</v>
+        <v>-14</v>
       </c>
       <c r="D13" t="n">
         <v>0</v>
       </c>
       <c r="E13" t="n">
-        <v>8.893963074455888</v>
+        <v>8.912512700048374</v>
       </c>
       <c r="F13" t="n">
-        <v>5.437790479813619</v>
+        <v>5.426438801725505</v>
       </c>
       <c r="G13" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="H13" t="n">
-        <v>3.359702168137186</v>
+        <v>3.444260067875105</v>
       </c>
       <c r="I13" t="n">
-        <v>38.01979183547741</v>
+        <v>36.92809202184588</v>
       </c>
       <c r="J13" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="K13" t="n">
-        <v>3.897867400629934</v>
+        <v>4.042525290505201</v>
       </c>
       <c r="L13" t="n">
-        <v>19.78338751270351</v>
+        <v>19.04759385653467</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>22.77239842197734</v>
+        <v>1.592839723049625e-11</v>
       </c>
       <c r="B14" t="n">
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>-2.5</v>
+        <v>-13</v>
       </c>
       <c r="D14" t="n">
         <v>0</v>
       </c>
       <c r="E14" t="n">
-        <v>8.033893955626734</v>
+        <v>8.838151844289545</v>
       </c>
       <c r="F14" t="n">
-        <v>6.021981359610391</v>
+        <v>5.47223354249082</v>
       </c>
       <c r="G14" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="H14" t="n">
-        <v>4.15400161677759</v>
+        <v>3.51821573641599</v>
       </c>
       <c r="I14" t="n">
-        <v>29.87827983808542</v>
+        <v>36.02815393731253</v>
       </c>
       <c r="J14" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="K14" t="n">
-        <v>4.772900865456391</v>
+        <v>4.130717623279303</v>
       </c>
       <c r="L14" t="n">
-        <v>16.04624057494804</v>
+        <v>18.62577808350046</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>25.27625378113423</v>
+        <v>1.586863780719597e-11</v>
       </c>
       <c r="B15" t="n">
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>8.75</v>
+        <v>-12</v>
       </c>
       <c r="D15" t="n">
         <v>0</v>
       </c>
       <c r="E15" t="n">
-        <v>7.137381015435103</v>
+        <v>8.763364531451209</v>
       </c>
       <c r="F15" t="n">
-        <v>6.781742360490169</v>
+        <v>5.519078416623445</v>
       </c>
       <c r="G15" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="H15" t="n">
-        <v>4.966491053906231</v>
+        <v>3.592771068345179</v>
       </c>
       <c r="I15" t="n">
-        <v>24.62409403718416</v>
+        <v>35.16808564140039</v>
       </c>
       <c r="J15" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="K15" t="n">
-        <v>5.680154661073904</v>
+        <v>4.219012847189298</v>
       </c>
       <c r="L15" t="n">
-        <v>13.43036493790994</v>
+        <v>18.22211753388449</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>26.90132105753864</v>
+        <v>4.632685396169775e-12</v>
       </c>
       <c r="B16" t="n">
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>20</v>
+        <v>-11</v>
       </c>
       <c r="D16" t="n">
         <v>0</v>
       </c>
       <c r="E16" t="n">
-        <v>6.229814680542415</v>
+        <v>8.688162060623027</v>
       </c>
       <c r="F16" t="n">
-        <v>7.775428450084326</v>
+        <v>5.567000369624424</v>
       </c>
       <c r="G16" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="H16" t="n">
-        <v>5.709722682678406</v>
+        <v>3.667848520867208</v>
       </c>
       <c r="I16" t="n">
-        <v>21.24927763819726</v>
+        <v>34.34587579881062</v>
       </c>
       <c r="J16" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="K16" t="n">
-        <v>6.523361592502432</v>
+        <v>4.307370868128792</v>
       </c>
       <c r="L16" t="n">
-        <v>11.66804559417191</v>
+        <v>17.83561520763794</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>1.568349716443079</v>
+        <v>1.573493969530995e-11</v>
       </c>
       <c r="B17" t="n">
-        <v>80</v>
+        <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>-25</v>
+        <v>-10</v>
       </c>
       <c r="D17" t="n">
         <v>0</v>
       </c>
       <c r="E17" t="n">
-        <v>9.699347069291395</v>
+        <v>8.612556003123021</v>
       </c>
       <c r="F17" t="n">
-        <v>4.985069224042777</v>
+        <v>5.616027178402847</v>
       </c>
       <c r="G17" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="H17" t="n">
-        <v>2.683989998574245</v>
+        <v>3.743371842357093</v>
       </c>
       <c r="I17" t="n">
-        <v>50.44368285084949</v>
+        <v>33.55964164941631</v>
       </c>
       <c r="J17" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="K17" t="n">
-        <v>1.84823871369611</v>
+        <v>4.395752719513276</v>
       </c>
       <c r="L17" t="n">
-        <v>45.54579539577981</v>
+        <v>17.46534079616599</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>9.853804239676323</v>
+        <v>1.566113173175429e-11</v>
       </c>
       <c r="B18" t="n">
-        <v>80</v>
+        <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>-13.75</v>
+        <v>-9</v>
       </c>
       <c r="D18" t="n">
         <v>0</v>
       </c>
       <c r="E18" t="n">
-        <v>8.893963074455876</v>
+        <v>8.53655821412304</v>
       </c>
       <c r="F18" t="n">
-        <v>5.437790479813618</v>
+        <v>5.666187471420748</v>
       </c>
       <c r="G18" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="H18" t="n">
-        <v>3.359702168141676</v>
+        <v>3.819270954890266</v>
       </c>
       <c r="I18" t="n">
-        <v>38.01979183536874</v>
+        <v>32.80755260969687</v>
       </c>
       <c r="J18" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="K18" t="n">
-        <v>2.682070057045771</v>
+        <v>4.484120483205356</v>
       </c>
       <c r="L18" t="n">
-        <v>29.46509407454469</v>
+        <v>17.11042571753297</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>16.01283874200326</v>
+        <v>1.558277290874763e-11</v>
       </c>
       <c r="B19" t="n">
-        <v>80</v>
+        <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>-2.5</v>
+        <v>-8</v>
       </c>
       <c r="D19" t="n">
         <v>0</v>
       </c>
       <c r="E19" t="n">
-        <v>8.033893955626722</v>
+        <v>8.460180845012575</v>
       </c>
       <c r="F19" t="n">
-        <v>6.021981359610399</v>
+        <v>5.717510748302256</v>
       </c>
       <c r="G19" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="H19" t="n">
-        <v>4.154001616777593</v>
+        <v>3.895478511670832</v>
       </c>
       <c r="I19" t="n">
-        <v>29.8782798380854</v>
+        <v>32.08787906372914</v>
       </c>
       <c r="J19" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="K19" t="n">
-        <v>3.542470971089408</v>
+        <v>4.57243723482427</v>
       </c>
       <c r="L19" t="n">
-        <v>21.86503073404833</v>
+        <v>16.77005847775977</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>22.08174068235013</v>
+        <v>1.549993046729767e-11</v>
       </c>
       <c r="B20" t="n">
-        <v>80</v>
+        <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>8.75</v>
+        <v>-7</v>
       </c>
       <c r="D20" t="n">
         <v>0</v>
       </c>
       <c r="E20" t="n">
-        <v>7.137381015435096</v>
+        <v>8.383436356550771</v>
       </c>
       <c r="F20" t="n">
-        <v>6.781742360490197</v>
+        <v>5.770027398716886</v>
       </c>
       <c r="G20" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="H20" t="n">
-        <v>4.966491053906232</v>
+        <v>3.971930492949263</v>
       </c>
       <c r="I20" t="n">
-        <v>24.62409403718416</v>
+        <v>31.39897843768169</v>
       </c>
       <c r="J20" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="K20" t="n">
-        <v>4.29494576102104</v>
+        <v>4.660666984006019</v>
       </c>
       <c r="L20" t="n">
-        <v>17.88895480037395</v>
+        <v>16.44348043496179</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>24.36931381623404</v>
+        <v>1.541267238685443e-11</v>
       </c>
       <c r="B21" t="n">
-        <v>80</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>20</v>
+        <v>-6.000000000000001</v>
       </c>
       <c r="D21" t="n">
         <v>0</v>
       </c>
       <c r="E21" t="n">
-        <v>6.229814680542401</v>
+        <v>8.30633753286056</v>
       </c>
       <c r="F21" t="n">
-        <v>7.775428450084258</v>
+        <v>5.823768720316768</v>
       </c>
       <c r="G21" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="H21" t="n">
-        <v>5.709722682678412</v>
+        <v>4.048565931560494</v>
       </c>
       <c r="I21" t="n">
-        <v>21.24927763819723</v>
+        <v>30.73929403167219</v>
       </c>
       <c r="J21" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="K21" t="n">
-        <v>5.07751195803071</v>
+        <v>4.748774623882341</v>
       </c>
       <c r="L21" t="n">
-        <v>15.06000049265894</v>
+        <v>16.12998188670693</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>3.914673497390443</v>
+        <v>1.532106738369594e-11</v>
       </c>
       <c r="B22" t="n">
         <v>0</v>
       </c>
       <c r="C22" t="n">
-        <v>-25</v>
+        <v>-5</v>
       </c>
       <c r="D22" t="n">
         <v>0</v>
       </c>
       <c r="E22" t="n">
-        <v>9.699347069291397</v>
+        <v>8.228897496322057</v>
       </c>
       <c r="F22" t="n">
-        <v>4.985069224042763</v>
+        <v>5.878766935474659</v>
       </c>
       <c r="G22" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="H22" t="n">
-        <v>2.672349906451689</v>
+        <v>4.125326703088624</v>
       </c>
       <c r="I22" t="n">
-        <v>50.74679737773963</v>
+        <v>30.10735244292725</v>
       </c>
       <c r="J22" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="K22" t="n">
-        <v>3.05458100843513</v>
+        <v>4.836725883699709</v>
       </c>
       <c r="L22" t="n">
-        <v>25.58858546705417</v>
+        <v>15.82889847330952</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>26.45139301620475</v>
+        <v>1.522518491301397e-11</v>
       </c>
       <c r="B23" t="n">
         <v>0</v>
       </c>
       <c r="C23" t="n">
-        <v>-13.75</v>
+        <v>-4</v>
       </c>
       <c r="D23" t="n">
         <v>0</v>
       </c>
       <c r="E23" t="n">
-        <v>8.89396307445589</v>
+        <v>8.151129723426582</v>
       </c>
       <c r="F23" t="n">
-        <v>5.437790479813633</v>
+        <v>5.935055206531888</v>
       </c>
       <c r="G23" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="H23" t="n">
-        <v>3.287772394014637</v>
+        <v>4.202157642877698</v>
       </c>
       <c r="I23" t="n">
-        <v>39.00653446515829</v>
+        <v>29.50175727088129</v>
       </c>
       <c r="J23" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="K23" t="n">
-        <v>3.797490260294298</v>
+        <v>4.924487287408027</v>
       </c>
       <c r="L23" t="n">
-        <v>20.32907736937291</v>
+        <v>15.53960786203673</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>43.56722694637506</v>
+        <v>1.51250951747906e-11</v>
       </c>
       <c r="B24" t="n">
         <v>0</v>
       </c>
       <c r="C24" t="n">
-        <v>-2.5</v>
+        <v>-3</v>
       </c>
       <c r="D24" t="n">
         <v>0</v>
       </c>
       <c r="E24" t="n">
-        <v>8.033893955626734</v>
+        <v>8.073048061657222</v>
       </c>
       <c r="F24" t="n">
-        <v>6.021981359610378</v>
+        <v>5.992667649224881</v>
       </c>
       <c r="G24" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="H24" t="n">
-        <v>4.035261045038132</v>
+        <v>4.279005677896204</v>
       </c>
       <c r="I24" t="n">
-        <v>30.85170336485806</v>
+        <v>28.92119351470508</v>
       </c>
       <c r="J24" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="K24" t="n">
-        <v>4.573057497596507</v>
+        <v>5.01202611496033</v>
       </c>
       <c r="L24" t="n">
-        <v>16.76771663971834</v>
+        <v>15.261526698943</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>48.91295462027036</v>
+        <v>1.502086912356782e-11</v>
       </c>
       <c r="B25" t="n">
         <v>0</v>
       </c>
       <c r="C25" t="n">
-        <v>8.75</v>
+        <v>-2</v>
       </c>
       <c r="D25" t="n">
         <v>0</v>
       </c>
       <c r="E25" t="n">
-        <v>7.137381015435104</v>
+        <v>7.994666747465937</v>
       </c>
       <c r="F25" t="n">
-        <v>6.781742360490188</v>
+        <v>6.051639343908534</v>
       </c>
       <c r="G25" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="H25" t="n">
-        <v>4.822520563476597</v>
+        <v>4.355820388122174</v>
       </c>
       <c r="I25" t="n">
-        <v>25.41058926971592</v>
+        <v>28.36441613992006</v>
       </c>
       <c r="J25" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="K25" t="n">
-        <v>5.445659600883113</v>
+        <v>5.099310367626974</v>
       </c>
       <c r="L25" t="n">
-        <v>14.020254357702</v>
+        <v>14.99410780128293</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>47.24415291930934</v>
+        <v>1.491257848222277e-11</v>
       </c>
       <c r="B26" t="n">
         <v>0</v>
       </c>
       <c r="C26" t="n">
-        <v>20</v>
+        <v>-1</v>
       </c>
       <c r="D26" t="n">
         <v>0</v>
       </c>
       <c r="E26" t="n">
-        <v>6.229814680542389</v>
+        <v>7.916000425422451</v>
       </c>
       <c r="F26" t="n">
-        <v>7.775428450084757</v>
+        <v>6.112006344143049</v>
       </c>
       <c r="G26" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="H26" t="n">
-        <v>5.582196107608259</v>
+        <v>4.432553509000461</v>
       </c>
       <c r="I26" t="n">
-        <v>21.75916478669935</v>
+        <v>27.83025045929205</v>
       </c>
       <c r="J26" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="K26" t="n">
-        <v>6.280953943054538</v>
+        <v>5.186308736296866</v>
       </c>
       <c r="L26" t="n">
-        <v>12.12507452459401</v>
+        <v>14.73683757299216</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>2.986324883345725</v>
+        <v>1.480029575987363e-11</v>
       </c>
       <c r="B27" t="n">
-        <v>80</v>
+        <v>0</v>
       </c>
       <c r="C27" t="n">
-        <v>-25</v>
+        <v>0</v>
       </c>
       <c r="D27" t="n">
         <v>0</v>
       </c>
       <c r="E27" t="n">
-        <v>9.699347069291386</v>
+        <v>7.837064168615009</v>
       </c>
       <c r="F27" t="n">
-        <v>4.98506922404277</v>
+        <v>6.173805682149561</v>
       </c>
       <c r="G27" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="H27" t="n">
-        <v>2.672349906452423</v>
+        <v>4.509158846922761</v>
       </c>
       <c r="I27" t="n">
-        <v>50.74679737773772</v>
+        <v>27.31758801190363</v>
       </c>
       <c r="J27" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="K27" t="n">
-        <v>1.845236132887001</v>
+        <v>5.272990572696988</v>
       </c>
       <c r="L27" t="n">
-        <v>45.64090137698093</v>
+        <v>14.48923362418039</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>18.0870769783449</v>
+        <v>1.468409427405283e-11</v>
       </c>
       <c r="B28" t="n">
-        <v>80</v>
+        <v>0</v>
       </c>
       <c r="C28" t="n">
-        <v>-13.75</v>
+        <v>1</v>
       </c>
       <c r="D28" t="n">
         <v>0</v>
       </c>
       <c r="E28" t="n">
-        <v>8.893963074455877</v>
+        <v>7.757873500388881</v>
       </c>
       <c r="F28" t="n">
-        <v>5.437790479813618</v>
+        <v>6.23707537056989</v>
       </c>
       <c r="G28" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="H28" t="n">
-        <v>3.287772394014977</v>
+        <v>4.585592154086891</v>
       </c>
       <c r="I28" t="n">
-        <v>39.00653446516069</v>
+        <v>26.82538304788634</v>
       </c>
       <c r="J28" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="K28" t="n">
-        <v>2.671816296735744</v>
+        <v>5.359325863194083</v>
       </c>
       <c r="L28" t="n">
-        <v>29.58939954626219</v>
+        <v>14.25084257790937</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>30.32560532117454</v>
+        <v>1.45640481772966e-11</v>
       </c>
       <c r="B29" t="n">
-        <v>80</v>
+        <v>0</v>
       </c>
       <c r="C29" t="n">
-        <v>-2.5</v>
+        <v>2</v>
       </c>
       <c r="D29" t="n">
         <v>0</v>
       </c>
       <c r="E29" t="n">
-        <v>8.033893955626716</v>
+        <v>7.678444417513585</v>
       </c>
       <c r="F29" t="n">
-        <v>6.021981359610341</v>
+        <v>6.301854399891663</v>
       </c>
       <c r="G29" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="H29" t="n">
-        <v>4.035261045038137</v>
+        <v>4.661811018407692</v>
       </c>
       <c r="I29" t="n">
-        <v>30.85170336485804</v>
+        <v>26.35264904849958</v>
       </c>
       <c r="J29" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="K29" t="n">
-        <v>3.489788485214075</v>
+        <v>5.445285204849962</v>
       </c>
       <c r="L29" t="n">
-        <v>22.21254942024597</v>
+        <v>14.02123804899962</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>41.83405738391046</v>
+        <v>1.444023248831234e-11</v>
       </c>
       <c r="B30" t="n">
-        <v>80</v>
+        <v>0</v>
       </c>
       <c r="C30" t="n">
-        <v>8.75</v>
+        <v>3</v>
       </c>
       <c r="D30" t="n">
         <v>0</v>
       </c>
       <c r="E30" t="n">
-        <v>7.137381015435089</v>
+        <v>7.598793414876552</v>
       </c>
       <c r="F30" t="n">
-        <v>6.78174236049011</v>
+        <v>6.368182730810259</v>
       </c>
       <c r="G30" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="H30" t="n">
-        <v>4.822520563476608</v>
+        <v>4.737774732483755</v>
       </c>
       <c r="I30" t="n">
-        <v>25.41058926971587</v>
+        <v>25.89845560569227</v>
       </c>
       <c r="J30" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="K30" t="n">
-        <v>4.139100966891535</v>
+        <v>5.530839783609424</v>
       </c>
       <c r="L30" t="n">
-        <v>18.58667031895314</v>
+        <v>13.80001878022639</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>42.87263657139304</v>
+        <v>1.431272312789768e-11</v>
       </c>
       <c r="B31" t="n">
-        <v>80</v>
+        <v>0</v>
       </c>
       <c r="C31" t="n">
-        <v>20</v>
+        <v>4</v>
       </c>
       <c r="D31" t="n">
         <v>0</v>
       </c>
       <c r="E31" t="n">
-        <v>6.229814680542401</v>
+        <v>7.518937511806604</v>
       </c>
       <c r="F31" t="n">
-        <v>7.775428450084199</v>
+        <v>6.436101280702517</v>
       </c>
       <c r="G31" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="H31" t="n">
-        <v>5.582196107608263</v>
+        <v>4.813444211282237</v>
       </c>
       <c r="I31" t="n">
-        <v>21.75916478669933</v>
+        <v>25.46192506409847</v>
       </c>
       <c r="J31" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="K31" t="n">
-        <v>4.863817567332301</v>
+        <v>5.615961354369177</v>
       </c>
       <c r="L31" t="n">
-        <v>15.7384372624687</v>
+        <v>13.58680692298745</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>5.626518182189856</v>
+        <v>1.418159695979697e-11</v>
       </c>
       <c r="B32" t="n">
         <v>0</v>
       </c>
       <c r="C32" t="n">
-        <v>-25</v>
+        <v>5</v>
       </c>
       <c r="D32" t="n">
         <v>0</v>
       </c>
       <c r="E32" t="n">
-        <v>9.699347069291422</v>
+        <v>7.43889428013757</v>
       </c>
       <c r="F32" t="n">
-        <v>4.985069224042793</v>
+        <v>6.505651903280182</v>
       </c>
       <c r="G32" t="n">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="H32" t="n">
-        <v>2.66205279742255</v>
+        <v>4.888781886760984</v>
       </c>
       <c r="I32" t="n">
-        <v>51.01881471155237</v>
+        <v>25.04222956274659</v>
       </c>
       <c r="J32" t="n">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="K32" t="n">
-        <v>3.038164646143397</v>
+        <v>5.700622222755028</v>
       </c>
       <c r="L32" t="n">
-        <v>25.7369329001457</v>
+        <v>13.38124645038788</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>35.94585648229967</v>
+        <v>0.2416149156737015</v>
       </c>
       <c r="B33" t="n">
         <v>0</v>
       </c>
       <c r="C33" t="n">
-        <v>-13.75</v>
+        <v>6.000000000000001</v>
       </c>
       <c r="D33" t="n">
         <v>0</v>
       </c>
       <c r="E33" t="n">
-        <v>8.893963074455886</v>
+        <v>7.358681874128892</v>
       </c>
       <c r="F33" t="n">
-        <v>5.437790479813589</v>
+        <v>6.576877360362939</v>
       </c>
       <c r="G33" t="n">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="H33" t="n">
-        <v>3.23390866764632</v>
+        <v>4.960086384449329</v>
       </c>
       <c r="I33" t="n">
-        <v>39.78379692135647</v>
+        <v>24.65800819910117</v>
       </c>
       <c r="J33" t="n">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="K33" t="n">
-        <v>3.728320023411244</v>
+        <v>5.784795228444019</v>
       </c>
       <c r="L33" t="n">
-        <v>20.723408132835</v>
+        <v>13.18300169178787</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>62.75045844289043</v>
+        <v>0.545486432314442</v>
       </c>
       <c r="B34" t="n">
         <v>0</v>
       </c>
       <c r="C34" t="n">
-        <v>-2.5</v>
+        <v>7</v>
       </c>
       <c r="D34" t="n">
         <v>0</v>
       </c>
       <c r="E34" t="n">
-        <v>8.033893955626732</v>
+        <v>7.278319062367192</v>
       </c>
       <c r="F34" t="n">
-        <v>6.021981359610386</v>
+        <v>6.649821284579757</v>
       </c>
       <c r="G34" t="n">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="H34" t="n">
-        <v>3.942070052245327</v>
+        <v>5.02997695411799</v>
       </c>
       <c r="I34" t="n">
-        <v>31.66426126596989</v>
+        <v>24.29307441699436</v>
       </c>
       <c r="J34" t="n">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="K34" t="n">
-        <v>4.423556610747725</v>
+        <v>5.868453729884763</v>
       </c>
       <c r="L34" t="n">
-        <v>17.35206755808755</v>
+        <v>12.9917559787475</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>71.66456933459564</v>
+        <v>0.8714397698282672</v>
       </c>
       <c r="B35" t="n">
         <v>0</v>
       </c>
       <c r="C35" t="n">
-        <v>8.75</v>
+        <v>8</v>
       </c>
       <c r="D35" t="n">
         <v>0</v>
       </c>
       <c r="E35" t="n">
-        <v>7.137381015435104</v>
+        <v>7.197825261779796</v>
       </c>
       <c r="F35" t="n">
-        <v>6.7817423604902</v>
+        <v>6.724528131648263</v>
       </c>
       <c r="G35" t="n">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="H35" t="n">
-        <v>4.708092425168001</v>
+        <v>5.099017878523849</v>
       </c>
       <c r="I35" t="n">
-        <v>26.07397481154727</v>
+        <v>23.94338537308727</v>
       </c>
       <c r="J35" t="n">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="K35" t="n">
-        <v>5.265961320099168</v>
+        <v>5.951571590283761</v>
       </c>
       <c r="L35" t="n">
-        <v>14.5089985305808</v>
+        <v>12.80721039317958</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>68.60674574486825</v>
+        <v>1.220056913693688</v>
       </c>
       <c r="B36" t="n">
         <v>0</v>
       </c>
       <c r="C36" t="n">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="D36" t="n">
         <v>0</v>
       </c>
       <c r="E36" t="n">
-        <v>6.229814680542369</v>
+        <v>7.117220573898448</v>
       </c>
       <c r="F36" t="n">
-        <v>7.775428450084854</v>
+        <v>6.80104312071458</v>
       </c>
       <c r="G36" t="n">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="H36" t="n">
-        <v>5.467817013843038</v>
+        <v>5.167161373423991</v>
       </c>
       <c r="I36" t="n">
-        <v>22.23836450104416</v>
+        <v>23.60829563425076</v>
       </c>
       <c r="J36" t="n">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="K36" t="n">
-        <v>6.083014358417225</v>
+        <v>6.034123164740941</v>
       </c>
       <c r="L36" t="n">
-        <v>12.52592282596335</v>
+        <v>12.62908260930837</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>4.289496939608167</v>
+        <v>1.623790945734489</v>
       </c>
       <c r="B37" t="n">
-        <v>80</v>
+        <v>0</v>
       </c>
       <c r="C37" t="n">
-        <v>-25</v>
+        <v>10</v>
       </c>
       <c r="D37" t="n">
         <v>0</v>
       </c>
       <c r="E37" t="n">
-        <v>9.699347069291395</v>
+        <v>7.036525823518714</v>
       </c>
       <c r="F37" t="n">
-        <v>4.98506922404278</v>
+        <v>6.879412161042477</v>
       </c>
       <c r="G37" t="n">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="H37" t="n">
-        <v>2.662052797422338</v>
+        <v>5.23436232746914</v>
       </c>
       <c r="I37" t="n">
-        <v>51.01881471155346</v>
+        <v>23.28719013934224</v>
       </c>
       <c r="J37" t="n">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="K37" t="n">
-        <v>1.842277261632965</v>
+        <v>6.114834605629501</v>
       </c>
       <c r="L37" t="n">
-        <v>45.73508506566576</v>
+        <v>12.45969049902879</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>25.13339181157621</v>
+        <v>2.186736238782685</v>
       </c>
       <c r="B38" t="n">
-        <v>80</v>
+        <v>0</v>
       </c>
       <c r="C38" t="n">
-        <v>-13.75</v>
+        <v>11</v>
       </c>
       <c r="D38" t="n">
         <v>0</v>
       </c>
       <c r="E38" t="n">
-        <v>8.893963074455879</v>
+        <v>6.955762599907265</v>
       </c>
       <c r="F38" t="n">
-        <v>5.437790479813627</v>
+        <v>6.959681763129194</v>
       </c>
       <c r="G38" t="n">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="H38" t="n">
-        <v>3.233908667650401</v>
+        <v>5.300578531506626</v>
       </c>
       <c r="I38" t="n">
-        <v>39.78379692134193</v>
+        <v>22.97948170839178</v>
       </c>
       <c r="J38" t="n">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="K38" t="n">
-        <v>2.66192087558712</v>
+        <v>6.18958445574463</v>
       </c>
       <c r="L38" t="n">
-        <v>29.71041596725174</v>
+        <v>12.30684554192779</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>43.57565003288252</v>
+        <v>2.782187956903099</v>
       </c>
       <c r="B39" t="n">
-        <v>80</v>
+        <v>0</v>
       </c>
       <c r="C39" t="n">
-        <v>-2.5</v>
+        <v>12</v>
       </c>
       <c r="D39" t="n">
         <v>0</v>
       </c>
       <c r="E39" t="n">
-        <v>8.03389395562672</v>
+        <v>6.87495330071666</v>
       </c>
       <c r="F39" t="n">
-        <v>6.021981359610394</v>
+        <v>7.041898932091645</v>
       </c>
       <c r="G39" t="n">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="H39" t="n">
-        <v>3.942070052245333</v>
+        <v>5.365770894385467</v>
       </c>
       <c r="I39" t="n">
-        <v>31.66426126596984</v>
+        <v>22.68460880172402</v>
       </c>
       <c r="J39" t="n">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="K39" t="n">
-        <v>3.45028241133297</v>
+        <v>6.263269000128879</v>
       </c>
       <c r="L39" t="n">
-        <v>22.48070018372238</v>
+        <v>12.15983351180069</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>60.15200184268892</v>
+        <v>3.41023342062372</v>
       </c>
       <c r="B40" t="n">
-        <v>80</v>
+        <v>0</v>
       </c>
       <c r="C40" t="n">
-        <v>8.75</v>
+        <v>13</v>
       </c>
       <c r="D40" t="n">
         <v>0</v>
       </c>
       <c r="E40" t="n">
-        <v>7.137381015435095</v>
+        <v>6.794121178772661</v>
       </c>
       <c r="F40" t="n">
-        <v>6.781742360490199</v>
+        <v>7.126111040903412</v>
       </c>
       <c r="G40" t="n">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="H40" t="n">
-        <v>4.708092425168002</v>
+        <v>5.429903636838494</v>
       </c>
       <c r="I40" t="n">
-        <v>26.07397481154727</v>
+        <v>22.40203352792259</v>
       </c>
       <c r="J40" t="n">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="K40" t="n">
-        <v>4.031083376155782</v>
+        <v>6.335855434439938</v>
       </c>
       <c r="L40" t="n">
-        <v>19.10375237459469</v>
+        <v>12.01843247146544</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>61.81058436610527</v>
+        <v>4.070748177713827</v>
       </c>
       <c r="B41" t="n">
-        <v>80</v>
+        <v>0</v>
       </c>
       <c r="C41" t="n">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="D41" t="n">
         <v>0</v>
       </c>
       <c r="E41" t="n">
-        <v>6.229814680542405</v>
+        <v>6.713290391905609</v>
       </c>
       <c r="F41" t="n">
-        <v>7.775428450084338</v>
+        <v>7.212365680779611</v>
       </c>
       <c r="G41" t="n">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="H41" t="n">
-        <v>5.467817013843104</v>
+        <v>5.492944454476768</v>
       </c>
       <c r="I41" t="n">
-        <v>22.2383645010439</v>
+        <v>22.13123990479459</v>
       </c>
       <c r="J41" t="n">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="K41" t="n">
-        <v>4.699030442860586</v>
+        <v>6.407313127950522</v>
       </c>
       <c r="L41" t="n">
-        <v>16.30547141933661</v>
+        <v>11.88242981402953</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>7.220634641722478</v>
+        <v>4.763381315069029</v>
       </c>
       <c r="B42" t="n">
         <v>0</v>
       </c>
       <c r="C42" t="n">
-        <v>-25</v>
+        <v>15</v>
       </c>
       <c r="D42" t="n">
         <v>0</v>
       </c>
       <c r="E42" t="n">
-        <v>9.699347069291402</v>
+        <v>6.632486056001337</v>
       </c>
       <c r="F42" t="n">
-        <v>4.985069224042773</v>
+        <v>7.300710485690455</v>
       </c>
       <c r="G42" t="n">
-        <v>0.4</v>
+        <v>0</v>
       </c>
       <c r="H42" t="n">
-        <v>2.65279881390623</v>
+        <v>5.554864643466562</v>
       </c>
       <c r="I42" t="n">
-        <v>51.26646119326676</v>
+        <v>21.87173236185276</v>
       </c>
       <c r="J42" t="n">
-        <v>0.4</v>
+        <v>0</v>
       </c>
       <c r="K42" t="n">
-        <v>3.022883063824816</v>
+        <v>6.477613773440733</v>
       </c>
       <c r="L42" t="n">
-        <v>25.87664304552226</v>
+        <v>11.75162156798588</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>44.00029698996187</v>
+        <v>5.487543079383201</v>
       </c>
       <c r="B43" t="n">
         <v>0</v>
       </c>
       <c r="C43" t="n">
-        <v>-13.75</v>
+        <v>16</v>
       </c>
       <c r="D43" t="n">
         <v>0</v>
       </c>
       <c r="E43" t="n">
-        <v>8.89396307445589</v>
+        <v>6.551734301450765</v>
       </c>
       <c r="F43" t="n">
-        <v>5.437790479813612</v>
+        <v>7.391192927639299</v>
       </c>
       <c r="G43" t="n">
-        <v>0.4</v>
+        <v>0</v>
       </c>
       <c r="H43" t="n">
-        <v>3.191539601976165</v>
+        <v>5.61563918274426</v>
       </c>
       <c r="I43" t="n">
-        <v>40.42011776816214</v>
+        <v>21.62303447646442</v>
       </c>
       <c r="J43" t="n">
-        <v>0.4</v>
+        <v>0</v>
       </c>
       <c r="K43" t="n">
-        <v>3.676427612196983</v>
+        <v>6.546731516664598</v>
       </c>
       <c r="L43" t="n">
-        <v>21.02968837175356</v>
+        <v>11.62581178152684</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>80.49158072654993</v>
+        <v>6.242395040274257</v>
       </c>
       <c r="B44" t="n">
         <v>0</v>
       </c>
       <c r="C44" t="n">
-        <v>-2.5</v>
+        <v>17</v>
       </c>
       <c r="D44" t="n">
         <v>0</v>
       </c>
       <c r="E44" t="n">
-        <v>8.033893955626731</v>
+        <v>6.471062333178517</v>
       </c>
       <c r="F44" t="n">
-        <v>6.021981359610337</v>
+        <v>7.483860078972318</v>
       </c>
       <c r="G44" t="n">
-        <v>0.4</v>
+        <v>0</v>
       </c>
       <c r="H44" t="n">
-        <v>3.865612097378002</v>
+        <v>5.675246769240776</v>
       </c>
       <c r="I44" t="n">
-        <v>32.36586355807864</v>
+        <v>21.38468792566679</v>
       </c>
       <c r="J44" t="n">
-        <v>0.4</v>
+        <v>0</v>
       </c>
       <c r="K44" t="n">
-        <v>4.308471749085909</v>
+        <v>6.614643061932762</v>
       </c>
       <c r="L44" t="n">
-        <v>17.83090485499207</v>
+        <v>11.50481198234194</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>93.45952040943031</v>
+        <v>7.026842960152629</v>
       </c>
       <c r="B45" t="n">
         <v>0</v>
       </c>
       <c r="C45" t="n">
-        <v>8.75</v>
+        <v>18</v>
       </c>
       <c r="D45" t="n">
         <v>0</v>
       </c>
       <c r="E45" t="n">
-        <v>7.137381015435102</v>
+        <v>6.390498494430958</v>
       </c>
       <c r="F45" t="n">
-        <v>6.78174236049018</v>
+        <v>7.578758337568981</v>
       </c>
       <c r="G45" t="n">
-        <v>0.4</v>
+        <v>0</v>
       </c>
       <c r="H45" t="n">
-        <v>4.615159685630434</v>
+        <v>5.733669804229781</v>
       </c>
       <c r="I45" t="n">
-        <v>26.63990908304231</v>
+        <v>21.15625163373845</v>
       </c>
       <c r="J45" t="n">
-        <v>0.4</v>
+        <v>0</v>
       </c>
       <c r="K45" t="n">
-        <v>5.120051107912222</v>
+        <v>6.681327751021728</v>
       </c>
       <c r="L45" t="n">
-        <v>14.93195175840776</v>
+        <v>11.38844070853454</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>90.51785275559575</v>
+        <v>7.839532457618419</v>
       </c>
       <c r="B46" t="n">
         <v>0</v>
       </c>
       <c r="C46" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D46" t="n">
         <v>0</v>
       </c>
       <c r="E46" t="n">
-        <v>6.229814680542411</v>
+        <v>6.310072334498395</v>
       </c>
       <c r="F46" t="n">
-        <v>7.775428450084179</v>
+        <v>7.675933110356115</v>
       </c>
       <c r="G46" t="n">
-        <v>0.4</v>
+        <v>0</v>
       </c>
       <c r="H46" t="n">
-        <v>5.366971155165242</v>
+        <v>5.79089433104874</v>
       </c>
       <c r="I46" t="n">
-        <v>22.67925293210462</v>
+        <v>20.93730109162667</v>
       </c>
       <c r="J46" t="n">
-        <v>0.4</v>
+        <v>0</v>
       </c>
       <c r="K46" t="n">
-        <v>5.916680425885124</v>
+        <v>6.746767613261202</v>
       </c>
       <c r="L46" t="n">
-        <v>12.88403084994869</v>
+        <v>11.27652310557143</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>5.501648605656828</v>
+        <v>8.678847465526299</v>
       </c>
       <c r="B47" t="n">
-        <v>80</v>
+        <v>0</v>
       </c>
       <c r="C47" t="n">
-        <v>-25</v>
+        <v>20</v>
       </c>
       <c r="D47" t="n">
         <v>0</v>
       </c>
       <c r="E47" t="n">
-        <v>9.699347069291393</v>
+        <v>6.22981468054239</v>
       </c>
       <c r="F47" t="n">
-        <v>4.98506922404276</v>
+        <v>7.77542845008473</v>
       </c>
       <c r="G47" t="n">
-        <v>0.4</v>
+        <v>0</v>
       </c>
       <c r="H47" t="n">
-        <v>2.652798813906232</v>
+        <v>5.846909926361429</v>
       </c>
       <c r="I47" t="n">
-        <v>51.2664611932667</v>
+        <v>20.72742782215026</v>
       </c>
       <c r="J47" t="n">
-        <v>0.4</v>
+        <v>0</v>
       </c>
       <c r="K47" t="n">
-        <v>1.839360899089016</v>
+        <v>6.810947385913788</v>
       </c>
       <c r="L47" t="n">
-        <v>45.82836864153854</v>
+        <v>11.16889058376146</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>31.29099536286814</v>
+        <v>-3.538937443682084</v>
       </c>
       <c r="B48" t="n">
-        <v>80</v>
+        <v>0</v>
       </c>
       <c r="C48" t="n">
-        <v>-13.75</v>
+        <v>-25</v>
       </c>
       <c r="D48" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="E48" t="n">
-        <v>8.893963074455877</v>
+        <v>9.489621785789449</v>
       </c>
       <c r="F48" t="n">
-        <v>5.437790479813617</v>
+        <v>5.095529895621963</v>
       </c>
       <c r="G48" t="n">
-        <v>0.4</v>
+        <v>0</v>
       </c>
       <c r="H48" t="n">
-        <v>3.191539601976164</v>
+        <v>2.697430303624302</v>
       </c>
       <c r="I48" t="n">
-        <v>40.42011776816214</v>
+        <v>50.09930096397862</v>
       </c>
       <c r="J48" t="n">
-        <v>0.4</v>
+        <v>0</v>
       </c>
       <c r="K48" t="n">
-        <v>2.652356739593821</v>
+        <v>3.092067073281464</v>
       </c>
       <c r="L48" t="n">
-        <v>29.82837934918075</v>
+        <v>25.25641123572337</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>56.04791047956017</v>
+        <v>-7.022259678786298</v>
       </c>
       <c r="B49" t="n">
-        <v>80</v>
+        <v>0</v>
       </c>
       <c r="C49" t="n">
-        <v>-2.5</v>
+        <v>-25</v>
       </c>
       <c r="D49" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="E49" t="n">
-        <v>8.033893955626715</v>
+        <v>9.334823541325351</v>
       </c>
       <c r="F49" t="n">
-        <v>6.021981359610345</v>
+        <v>5.180257545197659</v>
       </c>
       <c r="G49" t="n">
-        <v>0.4</v>
+        <v>0</v>
       </c>
       <c r="H49" t="n">
-        <v>3.865612097378006</v>
+        <v>2.697430405444766</v>
       </c>
       <c r="I49" t="n">
-        <v>32.36586355807859</v>
+        <v>50.09930403406669</v>
       </c>
       <c r="J49" t="n">
-        <v>0.4</v>
+        <v>0</v>
       </c>
       <c r="K49" t="n">
-        <v>3.418589011001661</v>
+        <v>3.09206716885968</v>
       </c>
       <c r="L49" t="n">
-        <v>22.70068930489674</v>
+        <v>25.25641047059553</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>77.1159944037687</v>
+        <v>-10.4495882656387</v>
       </c>
       <c r="B50" t="n">
-        <v>80</v>
+        <v>0</v>
       </c>
       <c r="C50" t="n">
-        <v>8.75</v>
+        <v>-25</v>
       </c>
       <c r="D50" t="n">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="E50" t="n">
-        <v>7.137381015435097</v>
+        <v>9.212529374081235</v>
       </c>
       <c r="F50" t="n">
-        <v>6.781742360490203</v>
+        <v>5.249216019122017</v>
       </c>
       <c r="G50" t="n">
-        <v>0.4</v>
+        <v>0</v>
       </c>
       <c r="H50" t="n">
-        <v>4.615159685630427</v>
+        <v>2.697430408004275</v>
       </c>
       <c r="I50" t="n">
-        <v>26.63990908304234</v>
+        <v>50.09930410377088</v>
       </c>
       <c r="J50" t="n">
-        <v>0.4</v>
+        <v>0</v>
       </c>
       <c r="K50" t="n">
-        <v>3.951489928669312</v>
+        <v>3.09206707396437</v>
       </c>
       <c r="L50" t="n">
-        <v>19.50396332060921</v>
+        <v>25.25641123187271</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>80.79865306933961</v>
+        <v>-13.82660796280592</v>
       </c>
       <c r="B51" t="n">
-        <v>80</v>
+        <v>0</v>
       </c>
       <c r="C51" t="n">
-        <v>20</v>
+        <v>-25</v>
       </c>
       <c r="D51" t="n">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="E51" t="n">
-        <v>6.229814680542364</v>
+        <v>9.111589061977844</v>
       </c>
       <c r="F51" t="n">
-        <v>7.775428450084853</v>
+        <v>5.307534045233507</v>
       </c>
       <c r="G51" t="n">
-        <v>0.4</v>
+        <v>0</v>
       </c>
       <c r="H51" t="n">
-        <v>5.366971155164718</v>
+        <v>2.697430287309031</v>
       </c>
       <c r="I51" t="n">
-        <v>22.67925293210596</v>
+        <v>50.09930053925707</v>
       </c>
       <c r="J51" t="n">
-        <v>0.4</v>
+        <v>0</v>
       </c>
       <c r="K51" t="n">
-        <v>4.56718253819996</v>
+        <v>3.092067364570417</v>
       </c>
       <c r="L51" t="n">
-        <v>16.78992457040859</v>
+        <v>25.25640899724515</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>8.718701187124308</v>
+        <v>-30.14449406562217</v>
       </c>
       <c r="B52" t="n">
         <v>0</v>
@@ -2401,191 +2401,191 @@
         <v>-25</v>
       </c>
       <c r="D52" t="n">
-        <v>0</v>
+        <v>0.9</v>
       </c>
       <c r="E52" t="n">
-        <v>9.699347069291402</v>
+        <v>8.771892049491537</v>
       </c>
       <c r="F52" t="n">
-        <v>4.985069224042757</v>
+        <v>5.513696461027553</v>
       </c>
       <c r="G52" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="H52" t="n">
-        <v>2.644380115871422</v>
+        <v>2.697430374105616</v>
       </c>
       <c r="I52" t="n">
-        <v>51.49443660130384</v>
+        <v>50.09930313708208</v>
       </c>
       <c r="J52" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="K52" t="n">
-        <v>3.008537750400982</v>
+        <v>3.092067061509431</v>
       </c>
       <c r="L52" t="n">
-        <v>26.00923771103495</v>
+        <v>25.25641130165692</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>51.00702072891173</v>
+        <v>2.102152324627045</v>
       </c>
       <c r="B53" t="n">
         <v>0</v>
       </c>
       <c r="C53" t="n">
-        <v>-13.75</v>
+        <v>-25</v>
       </c>
       <c r="D53" t="n">
         <v>0</v>
       </c>
       <c r="E53" t="n">
-        <v>8.893963074455892</v>
+        <v>9.699347069291402</v>
       </c>
       <c r="F53" t="n">
-        <v>5.437790479813631</v>
+        <v>4.985069224042757</v>
       </c>
       <c r="G53" t="n">
-        <v>0.5</v>
+        <v>0.1</v>
       </c>
       <c r="H53" t="n">
-        <v>3.156986522123541</v>
+        <v>2.683989998574897</v>
       </c>
       <c r="I53" t="n">
-        <v>40.95634621232148</v>
+        <v>50.44368285083736</v>
       </c>
       <c r="J53" t="n">
-        <v>0.5</v>
+        <v>0.1082177012392873</v>
       </c>
       <c r="K53" t="n">
-        <v>3.635260372942278</v>
+        <v>3.070883992165573</v>
       </c>
       <c r="L53" t="n">
-        <v>21.27935115700562</v>
+        <v>25.44301119189033</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>96.94718484951784</v>
+        <v>3.839251524594191</v>
       </c>
       <c r="B54" t="n">
         <v>0</v>
       </c>
       <c r="C54" t="n">
-        <v>-2.5</v>
+        <v>-25</v>
       </c>
       <c r="D54" t="n">
         <v>0</v>
       </c>
       <c r="E54" t="n">
-        <v>8.033893955626731</v>
+        <v>9.69934706929139</v>
       </c>
       <c r="F54" t="n">
-        <v>6.021981359610369</v>
+        <v>4.98506922404277</v>
       </c>
       <c r="G54" t="n">
-        <v>0.5</v>
+        <v>0.2</v>
       </c>
       <c r="H54" t="n">
-        <v>3.801082655426756</v>
+        <v>2.672349906452419</v>
       </c>
       <c r="I54" t="n">
-        <v>32.98446551683958</v>
+        <v>50.74679737773776</v>
       </c>
       <c r="J54" t="n">
-        <v>0.5</v>
+        <v>0.1861872028258322</v>
       </c>
       <c r="K54" t="n">
-        <v>4.217727330293614</v>
+        <v>3.056952118327394</v>
       </c>
       <c r="L54" t="n">
-        <v>18.22786668250258</v>
+        <v>25.56730559354525</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>114.4647898430495</v>
+        <v>5.484213403585476</v>
       </c>
       <c r="B55" t="n">
         <v>0</v>
       </c>
       <c r="C55" t="n">
-        <v>8.75</v>
+        <v>-25</v>
       </c>
       <c r="D55" t="n">
         <v>0</v>
       </c>
       <c r="E55" t="n">
-        <v>7.137381015435102</v>
+        <v>9.699347069291393</v>
       </c>
       <c r="F55" t="n">
-        <v>6.781742360490146</v>
+        <v>4.985069224042768</v>
       </c>
       <c r="G55" t="n">
-        <v>0.5</v>
+        <v>0.3</v>
       </c>
       <c r="H55" t="n">
-        <v>4.537208723215568</v>
+        <v>2.662052797422557</v>
       </c>
       <c r="I55" t="n">
-        <v>27.1347775216869</v>
+        <v>51.01881471155225</v>
       </c>
       <c r="J55" t="n">
-        <v>0.5</v>
+        <v>0.2724584114361717</v>
       </c>
       <c r="K55" t="n">
-        <v>4.997103185548007</v>
+        <v>3.042562690630358</v>
       </c>
       <c r="L55" t="n">
-        <v>15.30821699290895</v>
+        <v>25.69701456619961</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>112.2982324360977</v>
+        <v>7.078163436590854</v>
       </c>
       <c r="B56" t="n">
         <v>0</v>
       </c>
       <c r="C56" t="n">
-        <v>20</v>
+        <v>-25</v>
       </c>
       <c r="D56" t="n">
         <v>0</v>
       </c>
       <c r="E56" t="n">
-        <v>6.229814680542374</v>
+        <v>9.699347069291413</v>
       </c>
       <c r="F56" t="n">
-        <v>7.775428450084838</v>
+        <v>4.985069224042746</v>
       </c>
       <c r="G56" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="H56" t="n">
-        <v>5.278418548614056</v>
+        <v>2.652798813905597</v>
       </c>
       <c r="I56" t="n">
-        <v>23.08152203683098</v>
+        <v>51.26646119328322</v>
       </c>
       <c r="J56" t="n">
-        <v>0.5</v>
+        <v>0.3709916581317118</v>
       </c>
       <c r="K56" t="n">
-        <v>5.779022555626172</v>
+        <v>3.027211975723692</v>
       </c>
       <c r="L56" t="n">
-        <v>13.19640798481999</v>
+        <v>25.83690649497285</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>6.639554721812627</v>
+        <v>14.09452555419575</v>
       </c>
       <c r="B57" t="n">
-        <v>80</v>
+        <v>0</v>
       </c>
       <c r="C57" t="n">
         <v>-25</v>
@@ -2594,185 +2594,185 @@
         <v>0</v>
       </c>
       <c r="E57" t="n">
-        <v>9.699347069291395</v>
+        <v>9.699347069291418</v>
       </c>
       <c r="F57" t="n">
-        <v>4.985069224042761</v>
+        <v>4.985069224042745</v>
       </c>
       <c r="G57" t="n">
-        <v>0.5</v>
+        <v>0.9</v>
       </c>
       <c r="H57" t="n">
-        <v>2.644380115871423</v>
+        <v>2.616554302275603</v>
       </c>
       <c r="I57" t="n">
-        <v>51.49443660130381</v>
+        <v>52.26686362450164</v>
       </c>
       <c r="J57" t="n">
-        <v>0.5</v>
+        <v>0.9187962143520164</v>
       </c>
       <c r="K57" t="n">
-        <v>1.83648589527482</v>
+        <v>2.955899517665744</v>
       </c>
       <c r="L57" t="n">
-        <v>45.9207732665876</v>
+        <v>26.50814840086409</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>36.76500156041506</v>
+        <v>2.388112351066671</v>
       </c>
       <c r="B58" t="n">
-        <v>80</v>
+        <v>0</v>
       </c>
       <c r="C58" t="n">
-        <v>-13.75</v>
+        <v>-25</v>
       </c>
       <c r="D58" t="n">
         <v>0</v>
       </c>
       <c r="E58" t="n">
-        <v>8.893963074455881</v>
+        <v>9.699347069291413</v>
       </c>
       <c r="F58" t="n">
-        <v>5.437790479813594</v>
+        <v>4.985069224042779</v>
       </c>
       <c r="G58" t="n">
-        <v>0.5</v>
+        <v>0.1247653346366633</v>
       </c>
       <c r="H58" t="n">
-        <v>3.156986522123538</v>
+        <v>2.680960870595422</v>
       </c>
       <c r="I58" t="n">
-        <v>40.95634621232151</v>
+        <v>50.52212255324282</v>
       </c>
       <c r="J58" t="n">
-        <v>0.5</v>
+        <v>0.1</v>
       </c>
       <c r="K58" t="n">
-        <v>2.643099990447267</v>
+        <v>3.072411329380366</v>
       </c>
       <c r="L58" t="n">
-        <v>29.94349860907796</v>
+        <v>25.42946125386938</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>67.88766758916613</v>
+        <v>3.993545822174557</v>
       </c>
       <c r="B59" t="n">
-        <v>80</v>
+        <v>0</v>
       </c>
       <c r="C59" t="n">
-        <v>-2.5</v>
+        <v>-25</v>
       </c>
       <c r="D59" t="n">
         <v>0</v>
       </c>
       <c r="E59" t="n">
-        <v>8.033893955626716</v>
+        <v>9.699347069291406</v>
       </c>
       <c r="F59" t="n">
-        <v>6.02198135961037</v>
+        <v>4.985069224042771</v>
       </c>
       <c r="G59" t="n">
-        <v>0.5</v>
+        <v>0.2063981465460308</v>
       </c>
       <c r="H59" t="n">
-        <v>3.801082655426761</v>
+        <v>2.671654675914092</v>
       </c>
       <c r="I59" t="n">
-        <v>32.98446551683953</v>
+        <v>50.76504750905971</v>
       </c>
       <c r="J59" t="n">
-        <v>0.5</v>
+        <v>0.2</v>
       </c>
       <c r="K59" t="n">
-        <v>3.392045985434078</v>
+        <v>3.054581008433848</v>
       </c>
       <c r="L59" t="n">
-        <v>22.88837090927239</v>
+        <v>25.58858546719811</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>93.02633523403441</v>
+        <v>5.782095715150174</v>
       </c>
       <c r="B60" t="n">
-        <v>80</v>
+        <v>0</v>
       </c>
       <c r="C60" t="n">
-        <v>8.75</v>
+        <v>-25</v>
       </c>
       <c r="D60" t="n">
         <v>0</v>
       </c>
       <c r="E60" t="n">
-        <v>7.137381015435095</v>
+        <v>9.699347069291395</v>
       </c>
       <c r="F60" t="n">
-        <v>6.7817423604902</v>
+        <v>4.985069224042769</v>
       </c>
       <c r="G60" t="n">
-        <v>0.5</v>
+        <v>0.3137697936590399</v>
       </c>
       <c r="H60" t="n">
-        <v>4.537208723215567</v>
+        <v>2.660722059192307</v>
       </c>
       <c r="I60" t="n">
-        <v>27.13477752168691</v>
+        <v>51.05423924417278</v>
       </c>
       <c r="J60" t="n">
-        <v>0.5</v>
+        <v>0.3</v>
       </c>
       <c r="K60" t="n">
-        <v>3.889847038225816</v>
+        <v>3.038164646011364</v>
       </c>
       <c r="L60" t="n">
-        <v>19.82588625468566</v>
+        <v>25.73693289736029</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>99.53609252808653</v>
+        <v>7.248230992216799</v>
       </c>
       <c r="B61" t="n">
-        <v>80</v>
+        <v>0</v>
       </c>
       <c r="C61" t="n">
-        <v>20</v>
+        <v>-25</v>
       </c>
       <c r="D61" t="n">
         <v>0</v>
       </c>
       <c r="E61" t="n">
-        <v>6.229814680542368</v>
+        <v>9.699347069291408</v>
       </c>
       <c r="F61" t="n">
-        <v>7.775428450084807</v>
+        <v>4.985069224042771</v>
       </c>
       <c r="G61" t="n">
-        <v>0.5</v>
+        <v>0.4026174994879254</v>
       </c>
       <c r="H61" t="n">
-        <v>5.278418548614025</v>
+        <v>2.652568566175737</v>
       </c>
       <c r="I61" t="n">
-        <v>23.08152203683108</v>
+        <v>51.27266195917268</v>
       </c>
       <c r="J61" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="K61" t="n">
-        <v>4.45963731168721</v>
+        <v>3.022883063824818</v>
       </c>
       <c r="L61" t="n">
-        <v>17.20728207799108</v>
+        <v>25.87664304552224</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>10.13664987945919</v>
+        <v>14.22767596066131</v>
       </c>
       <c r="B62" t="n">
         <v>0</v>
@@ -2784,2009 +2784,2009 @@
         <v>0</v>
       </c>
       <c r="E62" t="n">
-        <v>9.699347069291402</v>
+        <v>9.699347069291395</v>
       </c>
       <c r="F62" t="n">
-        <v>4.985069224042759</v>
+        <v>4.985069224042768</v>
       </c>
       <c r="G62" t="n">
-        <v>0.6</v>
+        <v>0.9261043454272662</v>
       </c>
       <c r="H62" t="n">
-        <v>2.63664641227697</v>
+        <v>2.614983040688908</v>
       </c>
       <c r="I62" t="n">
-        <v>51.70616410062791</v>
+        <v>52.31137641976962</v>
       </c>
       <c r="J62" t="n">
-        <v>0.6</v>
+        <v>0.9</v>
       </c>
       <c r="K62" t="n">
-        <v>2.994982225276702</v>
+        <v>2.958056868950862</v>
       </c>
       <c r="L62" t="n">
-        <v>26.13583917523216</v>
+        <v>26.48730884250889</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>57.21809099102809</v>
+        <v>-3.556607353125177</v>
       </c>
       <c r="B63" t="n">
         <v>0</v>
       </c>
       <c r="C63" t="n">
-        <v>-13.75</v>
+        <v>-10</v>
       </c>
       <c r="D63" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="E63" t="n">
-        <v>8.893963074455892</v>
+        <v>8.419262476514666</v>
       </c>
       <c r="F63" t="n">
-        <v>5.437790479813589</v>
+        <v>5.745391646600253</v>
       </c>
       <c r="G63" t="n">
-        <v>0.6</v>
+        <v>0</v>
       </c>
       <c r="H63" t="n">
-        <v>3.12802572896906</v>
+        <v>3.743371491908506</v>
       </c>
       <c r="I63" t="n">
-        <v>41.41839170028976</v>
+        <v>33.55964653086292</v>
       </c>
       <c r="J63" t="n">
-        <v>0.6</v>
+        <v>0</v>
       </c>
       <c r="K63" t="n">
-        <v>3.601305657370947</v>
+        <v>4.395752719775719</v>
       </c>
       <c r="L63" t="n">
-        <v>21.4898971863933</v>
+        <v>17.46534079526109</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>112.2727341863221</v>
+        <v>-6.994453390141751</v>
       </c>
       <c r="B64" t="n">
         <v>0</v>
       </c>
       <c r="C64" t="n">
-        <v>-2.5</v>
+        <v>-10</v>
       </c>
       <c r="D64" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="E64" t="n">
-        <v>8.033893955626731</v>
+        <v>8.276089552328594</v>
       </c>
       <c r="F64" t="n">
-        <v>6.02198135961033</v>
+        <v>5.845127815053154</v>
       </c>
       <c r="G64" t="n">
-        <v>0.6</v>
+        <v>0</v>
       </c>
       <c r="H64" t="n">
-        <v>3.745546403721896</v>
+        <v>3.743371856014079</v>
       </c>
       <c r="I64" t="n">
-        <v>33.53757737607845</v>
+        <v>33.55964144845556</v>
       </c>
       <c r="J64" t="n">
-        <v>0.6</v>
+        <v>0</v>
       </c>
       <c r="K64" t="n">
-        <v>4.144491939889491</v>
+        <v>4.395752719914819</v>
       </c>
       <c r="L64" t="n">
-        <v>18.56161007538462</v>
+        <v>17.46534079473399</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>134.7966248688029</v>
+        <v>-10.34982833341321</v>
       </c>
       <c r="B65" t="n">
         <v>0</v>
       </c>
       <c r="C65" t="n">
-        <v>8.75</v>
+        <v>-10</v>
       </c>
       <c r="D65" t="n">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="E65" t="n">
-        <v>7.137381015435097</v>
+        <v>8.162141933309721</v>
       </c>
       <c r="F65" t="n">
-        <v>6.781742360490123</v>
+        <v>5.927019035346338</v>
       </c>
       <c r="G65" t="n">
-        <v>0.6</v>
+        <v>0</v>
       </c>
       <c r="H65" t="n">
-        <v>4.470193063007794</v>
+        <v>3.743371434397131</v>
       </c>
       <c r="I65" t="n">
-        <v>27.57586184557418</v>
+        <v>33.55964715510039</v>
       </c>
       <c r="J65" t="n">
-        <v>0.6</v>
+        <v>0</v>
       </c>
       <c r="K65" t="n">
-        <v>4.891018902502166</v>
+        <v>4.395752719728842</v>
       </c>
       <c r="L65" t="n">
-        <v>15.64865795554442</v>
+        <v>17.46534079538619</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>133.8104681923682</v>
+        <v>-13.64288997161601</v>
       </c>
       <c r="B66" t="n">
         <v>0</v>
       </c>
       <c r="C66" t="n">
-        <v>20</v>
+        <v>-10</v>
       </c>
       <c r="D66" t="n">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="E66" t="n">
-        <v>6.229814680542418</v>
+        <v>8.06740143910546</v>
       </c>
       <c r="F66" t="n">
-        <v>7.775428450084258</v>
+        <v>5.996877480197115</v>
       </c>
       <c r="G66" t="n">
-        <v>0.6</v>
+        <v>0</v>
       </c>
       <c r="H66" t="n">
-        <v>5.200415654670578</v>
+        <v>3.743371856281114</v>
       </c>
       <c r="I66" t="n">
-        <v>23.44826230416692</v>
+        <v>33.55964144458471</v>
       </c>
       <c r="J66" t="n">
-        <v>0.6</v>
+        <v>0</v>
       </c>
       <c r="K66" t="n">
-        <v>5.661967658597772</v>
+        <v>4.395752719768211</v>
       </c>
       <c r="L66" t="n">
-        <v>13.47431698420639</v>
+        <v>17.46534079528188</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>41.69944329267117</v>
+        <v>-29.48560119040208</v>
       </c>
       <c r="B67" t="n">
-        <v>80</v>
+        <v>0</v>
       </c>
       <c r="C67" t="n">
-        <v>-13.75</v>
+        <v>-10</v>
       </c>
       <c r="D67" t="n">
-        <v>0</v>
+        <v>0.9</v>
       </c>
       <c r="E67" t="n">
-        <v>8.893963074455883</v>
+        <v>7.744056430685746</v>
       </c>
       <c r="F67" t="n">
-        <v>5.437790479813622</v>
+        <v>6.248247945552081</v>
       </c>
       <c r="G67" t="n">
-        <v>0.6</v>
+        <v>0</v>
       </c>
       <c r="H67" t="n">
-        <v>3.12802572896906</v>
+        <v>3.743371856410349</v>
       </c>
       <c r="I67" t="n">
-        <v>41.41839170028975</v>
+        <v>33.5596414427964</v>
       </c>
       <c r="J67" t="n">
-        <v>0.6</v>
+        <v>0</v>
       </c>
       <c r="K67" t="n">
-        <v>2.634129390778139</v>
+        <v>4.395752719920004</v>
       </c>
       <c r="L67" t="n">
-        <v>30.05595978664492</v>
+        <v>17.46534079471174</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>79.17737651341685</v>
+        <v>19.24723242696969</v>
       </c>
       <c r="B68" t="n">
-        <v>80</v>
+        <v>0</v>
       </c>
       <c r="C68" t="n">
-        <v>-2.5</v>
+        <v>-10</v>
       </c>
       <c r="D68" t="n">
         <v>0</v>
       </c>
       <c r="E68" t="n">
-        <v>8.033893955626718</v>
+        <v>8.61255600312302</v>
       </c>
       <c r="F68" t="n">
-        <v>6.021981359610405</v>
+        <v>5.616027178402859</v>
       </c>
       <c r="G68" t="n">
-        <v>0.6</v>
+        <v>0.1</v>
       </c>
       <c r="H68" t="n">
-        <v>3.7455464037219</v>
+        <v>3.61464487639092</v>
       </c>
       <c r="I68" t="n">
-        <v>33.53757737607841</v>
+        <v>34.92415151190161</v>
       </c>
       <c r="J68" t="n">
-        <v>0.6</v>
+        <v>0.1082177012392873</v>
       </c>
       <c r="K68" t="n">
-        <v>3.369144085587918</v>
+        <v>4.159405809410647</v>
       </c>
       <c r="L68" t="n">
-        <v>23.05289649194723</v>
+        <v>18.4926395348988</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>108.1082810005125</v>
+        <v>33.72091318648222</v>
       </c>
       <c r="B69" t="n">
-        <v>80</v>
+        <v>0</v>
       </c>
       <c r="C69" t="n">
-        <v>8.75</v>
+        <v>-10</v>
       </c>
       <c r="D69" t="n">
         <v>0</v>
       </c>
       <c r="E69" t="n">
-        <v>7.137381015435096</v>
+        <v>8.612556003123018</v>
       </c>
       <c r="F69" t="n">
-        <v>6.781742360490204</v>
+        <v>5.61602717840287</v>
       </c>
       <c r="G69" t="n">
-        <v>0.6</v>
+        <v>0.2</v>
       </c>
       <c r="H69" t="n">
-        <v>4.470193063007795</v>
+        <v>3.521833028281219</v>
       </c>
       <c r="I69" t="n">
-        <v>27.57586184557417</v>
+        <v>35.98536345410113</v>
       </c>
       <c r="J69" t="n">
-        <v>0.6</v>
+        <v>0.1861872028258322</v>
       </c>
       <c r="K69" t="n">
-        <v>3.840225206820033</v>
+        <v>4.049546550063069</v>
       </c>
       <c r="L69" t="n">
-        <v>20.09303308155805</v>
+        <v>19.01329900288214</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>117.8426346427914</v>
+        <v>46.63695673391781</v>
       </c>
       <c r="B70" t="n">
-        <v>80</v>
+        <v>0</v>
       </c>
       <c r="C70" t="n">
-        <v>20</v>
+        <v>-10</v>
       </c>
       <c r="D70" t="n">
         <v>0</v>
       </c>
       <c r="E70" t="n">
-        <v>6.229814680542408</v>
+        <v>8.612556003123023</v>
       </c>
       <c r="F70" t="n">
-        <v>7.775428450084336</v>
+        <v>5.616027178402855</v>
       </c>
       <c r="G70" t="n">
-        <v>0.6</v>
+        <v>0.3</v>
       </c>
       <c r="H70" t="n">
-        <v>5.20041565467058</v>
+        <v>3.450971586571708</v>
       </c>
       <c r="I70" t="n">
-        <v>23.4482623041669</v>
+        <v>36.84438848520298</v>
       </c>
       <c r="J70" t="n">
-        <v>0.6</v>
+        <v>0.2724584114361717</v>
       </c>
       <c r="K70" t="n">
-        <v>4.370702054490919</v>
+        <v>3.96087944603085</v>
       </c>
       <c r="L70" t="n">
-        <v>17.56869297714687</v>
+        <v>19.45586233971915</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>-3.538937443681989</v>
+        <v>58.33905675691551</v>
       </c>
       <c r="B71" t="n">
         <v>0</v>
       </c>
       <c r="C71" t="n">
-        <v>-25</v>
+        <v>-10</v>
       </c>
       <c r="D71" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="E71" t="n">
-        <v>9.489621785789451</v>
+        <v>8.612556003123021</v>
       </c>
       <c r="F71" t="n">
-        <v>5.095529895621962</v>
+        <v>5.616027178402868</v>
       </c>
       <c r="G71" t="n">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="H71" t="n">
-        <v>2.697430266093007</v>
+        <v>3.394708122773546</v>
       </c>
       <c r="I71" t="n">
-        <v>50.09929979277508</v>
+        <v>37.55929838657981</v>
       </c>
       <c r="J71" t="n">
-        <v>0</v>
+        <v>0.3709916581317118</v>
       </c>
       <c r="K71" t="n">
-        <v>3.092067190359034</v>
+        <v>3.885472523752267</v>
       </c>
       <c r="L71" t="n">
-        <v>25.25641034795483</v>
+        <v>19.84914493013566</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>-3.592491222312116</v>
+        <v>101.6044903464519</v>
       </c>
       <c r="B72" t="n">
         <v>0</v>
       </c>
       <c r="C72" t="n">
-        <v>-13.75</v>
+        <v>-10</v>
       </c>
       <c r="D72" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="E72" t="n">
-        <v>8.695389066470055</v>
+        <v>8.61255600312302</v>
       </c>
       <c r="F72" t="n">
-        <v>5.562358866991361</v>
+        <v>5.616027178402857</v>
       </c>
       <c r="G72" t="n">
-        <v>0</v>
+        <v>0.9</v>
       </c>
       <c r="H72" t="n">
-        <v>3.462688167973118</v>
+        <v>3.223645099627039</v>
       </c>
       <c r="I72" t="n">
-        <v>36.69925978704315</v>
+        <v>39.93586483587215</v>
       </c>
       <c r="J72" t="n">
-        <v>0</v>
+        <v>0.9187962143520164</v>
       </c>
       <c r="K72" t="n">
-        <v>4.064561490850114</v>
+        <v>3.666551565360047</v>
       </c>
       <c r="L72" t="n">
-        <v>18.94038067854593</v>
+        <v>21.08903337881345</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>-3.436894475674119</v>
+        <v>21.37829750524171</v>
       </c>
       <c r="B73" t="n">
         <v>0</v>
       </c>
       <c r="C73" t="n">
-        <v>-2.5</v>
+        <v>-10</v>
       </c>
       <c r="D73" t="n">
+        <v>0</v>
+      </c>
+      <c r="E73" t="n">
+        <v>8.612556003123018</v>
+      </c>
+      <c r="F73" t="n">
+        <v>5.61602717840287</v>
+      </c>
+      <c r="G73" t="n">
+        <v>0.1247653346366633</v>
+      </c>
+      <c r="H73" t="n">
+        <v>3.589027608060948</v>
+      </c>
+      <c r="I73" t="n">
+        <v>35.2102006432139</v>
+      </c>
+      <c r="J73" t="n">
         <v>0.1</v>
       </c>
-      <c r="E73" t="n">
-        <v>7.851833881946527</v>
-      </c>
-      <c r="F73" t="n">
-        <v>6.16214740055286</v>
-      </c>
-      <c r="G73" t="n">
-        <v>0</v>
-      </c>
-      <c r="H73" t="n">
-        <v>4.317420265039443</v>
-      </c>
-      <c r="I73" t="n">
-        <v>28.63990654316924</v>
-      </c>
-      <c r="J73" t="n">
-        <v>0</v>
-      </c>
       <c r="K73" t="n">
-        <v>5.055702035795592</v>
+        <v>4.173296784901265</v>
       </c>
       <c r="L73" t="n">
-        <v>15.12651732499306</v>
+        <v>18.42886757135937</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>-1.908816633268772</v>
+        <v>35.00167089836352</v>
       </c>
       <c r="B74" t="n">
         <v>0</v>
       </c>
       <c r="C74" t="n">
-        <v>8.75</v>
+        <v>-10</v>
       </c>
       <c r="D74" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="E74" t="n">
-        <v>6.97834077367539</v>
+        <v>8.612556003123021</v>
       </c>
       <c r="F74" t="n">
-        <v>6.937053098653196</v>
+        <v>5.616027178402834</v>
       </c>
       <c r="G74" t="n">
-        <v>0</v>
+        <v>0.2063981465460308</v>
       </c>
       <c r="H74" t="n">
-        <v>5.150212148609003</v>
+        <v>3.516742338019175</v>
       </c>
       <c r="I74" t="n">
-        <v>23.69073351504553</v>
+        <v>36.04561280808695</v>
       </c>
       <c r="J74" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="K74" t="n">
-        <v>6.013539744734469</v>
+        <v>4.033441996411134</v>
       </c>
       <c r="L74" t="n">
-        <v>12.67302773292548</v>
+        <v>19.09214830533379</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>6.834780035391551</v>
+        <v>48.87603260037391</v>
       </c>
       <c r="B75" t="n">
         <v>0</v>
       </c>
       <c r="C75" t="n">
-        <v>20</v>
+        <v>-10</v>
       </c>
       <c r="D75" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="E75" t="n">
-        <v>6.128497937405491</v>
+        <v>8.61255600312302</v>
       </c>
       <c r="F75" t="n">
-        <v>7.904787369195255</v>
+        <v>5.616027178402858</v>
       </c>
       <c r="G75" t="n">
-        <v>0</v>
+        <v>0.3137697936590399</v>
       </c>
       <c r="H75" t="n">
-        <v>5.846909926366483</v>
+        <v>3.442478302831986</v>
       </c>
       <c r="I75" t="n">
-        <v>20.72742782213567</v>
+        <v>36.95038383171704</v>
       </c>
       <c r="J75" t="n">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="K75" t="n">
-        <v>6.810947385913785</v>
+        <v>3.937554987460157</v>
       </c>
       <c r="L75" t="n">
-        <v>11.16889058376146</v>
+        <v>19.57579927509693</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>-3.538937443688777</v>
+        <v>59.45245776562128</v>
       </c>
       <c r="B76" t="n">
-        <v>80</v>
+        <v>0</v>
       </c>
       <c r="C76" t="n">
-        <v>-25</v>
+        <v>-10</v>
       </c>
       <c r="D76" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="E76" t="n">
-        <v>9.489621785789437</v>
+        <v>8.612556003123021</v>
       </c>
       <c r="F76" t="n">
-        <v>5.095529895621969</v>
+        <v>5.616027178402834</v>
       </c>
       <c r="G76" t="n">
-        <v>0</v>
+        <v>0.4026174994879254</v>
       </c>
       <c r="H76" t="n">
-        <v>2.697430343808318</v>
+        <v>3.393387678295042</v>
       </c>
       <c r="I76" t="n">
-        <v>50.09930224527555</v>
+        <v>37.57644467614871</v>
       </c>
       <c r="J76" t="n">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="K76" t="n">
-        <v>1.851286194306214</v>
+        <v>3.866911644169634</v>
       </c>
       <c r="L76" t="n">
-        <v>45.4497398981482</v>
+        <v>19.94845421713874</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>-3.592491222318965</v>
+        <v>102.638124663748</v>
       </c>
       <c r="B77" t="n">
-        <v>80</v>
+        <v>0</v>
       </c>
       <c r="C77" t="n">
-        <v>-13.75</v>
+        <v>-10</v>
       </c>
       <c r="D77" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="E77" t="n">
-        <v>8.695389066470041</v>
+        <v>8.61255600312302</v>
       </c>
       <c r="F77" t="n">
-        <v>5.56235886699137</v>
+        <v>5.616027178402859</v>
       </c>
       <c r="G77" t="n">
-        <v>0</v>
+        <v>0.9261043454272662</v>
       </c>
       <c r="H77" t="n">
-        <v>3.46268824859674</v>
+        <v>3.21758285243637</v>
       </c>
       <c r="I77" t="n">
-        <v>36.69925847321665</v>
+        <v>40.02630051774122</v>
       </c>
       <c r="J77" t="n">
-        <v>0</v>
+        <v>0.9</v>
       </c>
       <c r="K77" t="n">
-        <v>2.692712986681366</v>
+        <v>3.671338418474063</v>
       </c>
       <c r="L77" t="n">
-        <v>29.33723107004002</v>
+        <v>21.06022642645797</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>-3.436894475674225</v>
+        <v>-3.382424291726935</v>
       </c>
       <c r="B78" t="n">
-        <v>80</v>
+        <v>0</v>
       </c>
       <c r="C78" t="n">
-        <v>-2.5</v>
+        <v>0</v>
       </c>
       <c r="D78" t="n">
         <v>0.1</v>
       </c>
       <c r="E78" t="n">
-        <v>7.851833881946513</v>
+        <v>7.658962145149544</v>
       </c>
       <c r="F78" t="n">
-        <v>6.162147400552872</v>
+        <v>6.317949772334973</v>
       </c>
       <c r="G78" t="n">
         <v>0</v>
       </c>
       <c r="H78" t="n">
-        <v>4.317420265039447</v>
+        <v>4.509158846995403</v>
       </c>
       <c r="I78" t="n">
-        <v>28.63990654316927</v>
+        <v>27.31758801122518</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
       </c>
       <c r="K78" t="n">
-        <v>3.621786857550019</v>
+        <v>5.272990572693508</v>
       </c>
       <c r="L78" t="n">
-        <v>21.36238895187618</v>
+        <v>14.48923362419594</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>-1.908816633265347</v>
+        <v>-6.639323072125402</v>
       </c>
       <c r="B79" t="n">
-        <v>80</v>
+        <v>0</v>
       </c>
       <c r="C79" t="n">
-        <v>8.75</v>
+        <v>0</v>
       </c>
       <c r="D79" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="E79" t="n">
-        <v>6.978340773675386</v>
+        <v>7.525051081621916</v>
       </c>
       <c r="F79" t="n">
-        <v>6.937053098653199</v>
+        <v>6.430850327703494</v>
       </c>
       <c r="G79" t="n">
         <v>0</v>
       </c>
       <c r="H79" t="n">
-        <v>5.150212148608951</v>
+        <v>4.509158846995449</v>
       </c>
       <c r="I79" t="n">
-        <v>23.69073351504547</v>
+        <v>27.31758801122301</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
       </c>
       <c r="K79" t="n">
-        <v>4.535282099530353</v>
+        <v>5.272990572696991</v>
       </c>
       <c r="L79" t="n">
-        <v>16.91156195186098</v>
+        <v>14.48923362418054</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>4.74328128961666</v>
+        <v>-9.797266891972548</v>
       </c>
       <c r="B80" t="n">
-        <v>80</v>
+        <v>0</v>
       </c>
       <c r="C80" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="D80" t="n">
-        <v>0.1</v>
+        <v>0.3</v>
       </c>
       <c r="E80" t="n">
-        <v>6.128497937407313</v>
+        <v>7.417853743579847</v>
       </c>
       <c r="F80" t="n">
-        <v>7.904787369190159</v>
+        <v>6.524185059903331</v>
       </c>
       <c r="G80" t="n">
         <v>0</v>
       </c>
       <c r="H80" t="n">
-        <v>5.846909926368793</v>
+        <v>4.509158846995455</v>
       </c>
       <c r="I80" t="n">
-        <v>20.72742782212901</v>
+        <v>27.3175880112232</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
       </c>
       <c r="K80" t="n">
-        <v>5.3783694303075</v>
+        <v>5.272990572696822</v>
       </c>
       <c r="L80" t="n">
-        <v>14.19932256826102</v>
+        <v>14.48923362418303</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>-7.022259678786298</v>
+        <v>-12.86940171717191</v>
       </c>
       <c r="B81" t="n">
         <v>0</v>
       </c>
       <c r="C81" t="n">
-        <v>-25</v>
+        <v>0</v>
       </c>
       <c r="D81" t="n">
-        <v>0.2</v>
+        <v>0.4</v>
       </c>
       <c r="E81" t="n">
-        <v>9.334823541325351</v>
+        <v>7.328660955698762</v>
       </c>
       <c r="F81" t="n">
-        <v>5.180257545197658</v>
+        <v>6.603938387878665</v>
       </c>
       <c r="G81" t="n">
         <v>0</v>
       </c>
       <c r="H81" t="n">
-        <v>2.697430391529677</v>
+        <v>4.509158846908393</v>
       </c>
       <c r="I81" t="n">
-        <v>50.09930364279032</v>
+        <v>27.31758801200958</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
       </c>
       <c r="K81" t="n">
-        <v>3.092067189415312</v>
+        <v>5.27299057269699</v>
       </c>
       <c r="L81" t="n">
-        <v>25.25641035342505</v>
+        <v>14.48923362418117</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>-7.0700180407648</v>
+        <v>-27.15356401559231</v>
       </c>
       <c r="B82" t="n">
         <v>0</v>
       </c>
       <c r="C82" t="n">
-        <v>-13.75</v>
+        <v>0</v>
       </c>
       <c r="D82" t="n">
-        <v>0.2</v>
+        <v>0.9</v>
       </c>
       <c r="E82" t="n">
-        <v>8.549048053328359</v>
+        <v>7.02759939761558</v>
       </c>
       <c r="F82" t="n">
-        <v>5.657882350891801</v>
+        <v>6.888192676121482</v>
       </c>
       <c r="G82" t="n">
         <v>0</v>
       </c>
       <c r="H82" t="n">
-        <v>3.462688417354377</v>
+        <v>4.509158846995449</v>
       </c>
       <c r="I82" t="n">
-        <v>36.69925545241876</v>
+        <v>27.3175880112231</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
       </c>
       <c r="K82" t="n">
-        <v>4.064561490844194</v>
+        <v>5.272990572696989</v>
       </c>
       <c r="L82" t="n">
-        <v>18.94038067856711</v>
+        <v>14.48923362418039</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>-6.754721451973916</v>
+        <v>24.35280591724352</v>
       </c>
       <c r="B83" t="n">
         <v>0</v>
       </c>
       <c r="C83" t="n">
-        <v>-2.5</v>
+        <v>0</v>
       </c>
       <c r="D83" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="E83" t="n">
-        <v>7.715292341424115</v>
+        <v>7.837064168615012</v>
       </c>
       <c r="F83" t="n">
-        <v>6.271635920213032</v>
+        <v>6.173805682149561</v>
       </c>
       <c r="G83" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="H83" t="n">
-        <v>4.317420265039444</v>
+        <v>4.335524995031109</v>
       </c>
       <c r="I83" t="n">
-        <v>28.63990654316929</v>
+        <v>28.50932177756017</v>
       </c>
       <c r="J83" t="n">
-        <v>0</v>
+        <v>0.1082177012392873</v>
       </c>
       <c r="K83" t="n">
-        <v>5.055702035789434</v>
+        <v>4.958162324228196</v>
       </c>
       <c r="L83" t="n">
-        <v>15.1265173250117</v>
+        <v>15.4314273504268</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>-4.730058378004157</v>
+        <v>44.20544047627426</v>
       </c>
       <c r="B84" t="n">
         <v>0</v>
       </c>
       <c r="C84" t="n">
-        <v>8.75</v>
+        <v>0</v>
       </c>
       <c r="D84" t="n">
+        <v>0</v>
+      </c>
+      <c r="E84" t="n">
+        <v>7.837064168615007</v>
+      </c>
+      <c r="F84" t="n">
+        <v>6.173805682149554</v>
+      </c>
+      <c r="G84" t="n">
         <v>0.2</v>
       </c>
-      <c r="E84" t="n">
-        <v>6.859924822263329</v>
-      </c>
-      <c r="F84" t="n">
-        <v>7.057404482604396</v>
-      </c>
-      <c r="G84" t="n">
-        <v>0</v>
-      </c>
       <c r="H84" t="n">
-        <v>5.150212148609477</v>
+        <v>4.210319808315458</v>
       </c>
       <c r="I84" t="n">
-        <v>23.69073351504243</v>
+        <v>29.43892951192797</v>
       </c>
       <c r="J84" t="n">
-        <v>0</v>
+        <v>0.1861872028258322</v>
       </c>
       <c r="K84" t="n">
-        <v>6.013539744734477</v>
+        <v>4.793578934046007</v>
       </c>
       <c r="L84" t="n">
-        <v>12.6730277329258</v>
+        <v>15.97516621938441</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>5.274583491014392</v>
+        <v>63.56325425022536</v>
       </c>
       <c r="B85" t="n">
         <v>0</v>
       </c>
       <c r="C85" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="D85" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="E85" t="n">
-        <v>6.05400035860298</v>
+        <v>7.837064168615009</v>
       </c>
       <c r="F85" t="n">
-        <v>8.002693397332109</v>
+        <v>6.173805682149569</v>
       </c>
       <c r="G85" t="n">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="H85" t="n">
-        <v>5.846909926368786</v>
+        <v>4.11246745646153</v>
       </c>
       <c r="I85" t="n">
-        <v>20.72742782212904</v>
+        <v>30.21129176485882</v>
       </c>
       <c r="J85" t="n">
-        <v>0</v>
+        <v>0.2724584114361717</v>
       </c>
       <c r="K85" t="n">
-        <v>6.810947385881361</v>
+        <v>4.647643714064566</v>
       </c>
       <c r="L85" t="n">
-        <v>11.16889058380589</v>
+        <v>16.49087103004834</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>-7.022259678792995</v>
+        <v>82.74406498369817</v>
       </c>
       <c r="B86" t="n">
-        <v>80</v>
+        <v>0</v>
       </c>
       <c r="C86" t="n">
-        <v>-25</v>
+        <v>0</v>
       </c>
       <c r="D86" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="E86" t="n">
-        <v>9.33482354132534</v>
+        <v>7.837064168615007</v>
       </c>
       <c r="F86" t="n">
-        <v>5.180257545197665</v>
+        <v>6.173805682149557</v>
       </c>
       <c r="G86" t="n">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="H86" t="n">
-        <v>2.697430375761293</v>
+        <v>4.032194573316414</v>
       </c>
       <c r="I86" t="n">
-        <v>50.09930319145615</v>
+        <v>30.87773509975563</v>
       </c>
       <c r="J86" t="n">
-        <v>0</v>
+        <v>0.3709916581317118</v>
       </c>
       <c r="K86" t="n">
-        <v>1.851286196996451</v>
+        <v>4.513984366932661</v>
       </c>
       <c r="L86" t="n">
-        <v>45.44974013208879</v>
+        <v>16.9937723594608</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>-7.070018040760147</v>
+        <v>166.051787943253</v>
       </c>
       <c r="B87" t="n">
-        <v>80</v>
+        <v>0</v>
       </c>
       <c r="C87" t="n">
-        <v>-13.75</v>
+        <v>0</v>
       </c>
       <c r="D87" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="E87" t="n">
-        <v>8.549048053328351</v>
+        <v>7.837064168615006</v>
       </c>
       <c r="F87" t="n">
-        <v>5.657882350891806</v>
+        <v>6.173805682149553</v>
       </c>
       <c r="G87" t="n">
-        <v>0</v>
+        <v>0.9</v>
       </c>
       <c r="H87" t="n">
-        <v>3.462688234275917</v>
+        <v>3.76654313947536</v>
       </c>
       <c r="I87" t="n">
-        <v>36.69925867710384</v>
+        <v>33.32612956193377</v>
       </c>
       <c r="J87" t="n">
-        <v>0</v>
+        <v>0.9187962143520164</v>
       </c>
       <c r="K87" t="n">
-        <v>2.692712986681363</v>
+        <v>4.105149470269706</v>
       </c>
       <c r="L87" t="n">
-        <v>29.33723107003987</v>
+        <v>18.74609482972911</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>-6.754721451974023</v>
+        <v>26.95810080577186</v>
       </c>
       <c r="B88" t="n">
-        <v>80</v>
+        <v>0</v>
       </c>
       <c r="C88" t="n">
-        <v>-2.5</v>
+        <v>0</v>
       </c>
       <c r="D88" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="E88" t="n">
-        <v>7.7152923414241</v>
+        <v>7.837064168615006</v>
       </c>
       <c r="F88" t="n">
-        <v>6.271635920213045</v>
+        <v>6.173805682149554</v>
       </c>
       <c r="G88" t="n">
-        <v>0</v>
+        <v>0.1247653346366633</v>
       </c>
       <c r="H88" t="n">
-        <v>4.317420265039433</v>
+        <v>4.301130354332845</v>
       </c>
       <c r="I88" t="n">
-        <v>28.6399065431704</v>
+        <v>28.75848174617386</v>
       </c>
       <c r="J88" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="K88" t="n">
-        <v>3.621786867810114</v>
+        <v>4.977885818595451</v>
       </c>
       <c r="L88" t="n">
-        <v>21.36238889569771</v>
+        <v>15.36877144665517</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>-4.730058377932623</v>
+        <v>46.1624987222564</v>
       </c>
       <c r="B89" t="n">
-        <v>80</v>
+        <v>0</v>
       </c>
       <c r="C89" t="n">
-        <v>8.75</v>
+        <v>0</v>
       </c>
       <c r="D89" t="n">
+        <v>0</v>
+      </c>
+      <c r="E89" t="n">
+        <v>7.837064168615007</v>
+      </c>
+      <c r="F89" t="n">
+        <v>6.173805682149556</v>
+      </c>
+      <c r="G89" t="n">
+        <v>0.2063981465460308</v>
+      </c>
+      <c r="H89" t="n">
+        <v>4.203379562291722</v>
+      </c>
+      <c r="I89" t="n">
+        <v>29.49233359533105</v>
+      </c>
+      <c r="J89" t="n">
         <v>0.2</v>
       </c>
-      <c r="E89" t="n">
-        <v>6.859924822263326</v>
-      </c>
-      <c r="F89" t="n">
-        <v>7.057404482604401</v>
-      </c>
-      <c r="G89" t="n">
-        <v>0</v>
-      </c>
-      <c r="H89" t="n">
-        <v>5.150212148608379</v>
-      </c>
-      <c r="I89" t="n">
-        <v>23.69073351504732</v>
-      </c>
-      <c r="J89" t="n">
-        <v>0</v>
-      </c>
       <c r="K89" t="n">
-        <v>4.535282099153555</v>
+        <v>4.767998876531849</v>
       </c>
       <c r="L89" t="n">
-        <v>16.91156195309711</v>
+        <v>16.06318375226907</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>3.18308474416524</v>
+        <v>67.33349544284323</v>
       </c>
       <c r="B90" t="n">
-        <v>80</v>
+        <v>0</v>
       </c>
       <c r="C90" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="D90" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="E90" t="n">
-        <v>6.054000358603063</v>
+        <v>7.837064168615006</v>
       </c>
       <c r="F90" t="n">
-        <v>8.002693397331678</v>
+        <v>6.173805682149555</v>
       </c>
       <c r="G90" t="n">
-        <v>0</v>
+        <v>0.3137697936590399</v>
       </c>
       <c r="H90" t="n">
-        <v>5.846909926367826</v>
+        <v>4.100520633784763</v>
       </c>
       <c r="I90" t="n">
-        <v>20.72742782223653</v>
+        <v>30.30853986447129</v>
       </c>
       <c r="J90" t="n">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="K90" t="n">
-        <v>5.378369430307497</v>
+        <v>4.607184891544382</v>
       </c>
       <c r="L90" t="n">
-        <v>14.19932256826086</v>
+        <v>16.63988212863547</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>-10.4495882656387</v>
+        <v>85.06366876632356</v>
       </c>
       <c r="B91" t="n">
         <v>0</v>
       </c>
       <c r="C91" t="n">
-        <v>-25</v>
+        <v>0</v>
       </c>
       <c r="D91" t="n">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="E91" t="n">
-        <v>9.21252937408123</v>
+        <v>7.837064168615009</v>
       </c>
       <c r="F91" t="n">
-        <v>5.24921601912202</v>
+        <v>6.173805682149575</v>
       </c>
       <c r="G91" t="n">
-        <v>0</v>
+        <v>0.4026174994879254</v>
       </c>
       <c r="H91" t="n">
-        <v>2.697430407091475</v>
+        <v>4.0302758839185</v>
       </c>
       <c r="I91" t="n">
-        <v>50.09930407953387</v>
+        <v>30.89404689015254</v>
       </c>
       <c r="J91" t="n">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="K91" t="n">
-        <v>3.092067208581329</v>
+        <v>4.479934196712301</v>
       </c>
       <c r="L91" t="n">
-        <v>25.25641024066373</v>
+        <v>17.12690822717056</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>-10.46507208933645</v>
+        <v>167.8955230012027</v>
       </c>
       <c r="B92" t="n">
         <v>0</v>
       </c>
       <c r="C92" t="n">
-        <v>-13.75</v>
+        <v>0</v>
       </c>
       <c r="D92" t="n">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="E92" t="n">
-        <v>8.43301767691497</v>
+        <v>7.837064168615006</v>
       </c>
       <c r="F92" t="n">
-        <v>5.735988806694715</v>
+        <v>6.17380568214956</v>
       </c>
       <c r="G92" t="n">
-        <v>0</v>
+        <v>0.9261043454272662</v>
       </c>
       <c r="H92" t="n">
-        <v>3.462688417352432</v>
+        <v>3.756446993650571</v>
       </c>
       <c r="I92" t="n">
-        <v>36.69925545234839</v>
+        <v>33.42744356830013</v>
       </c>
       <c r="J92" t="n">
-        <v>0</v>
+        <v>0.9</v>
       </c>
       <c r="K92" t="n">
-        <v>4.06456149085848</v>
+        <v>4.113852220028178</v>
       </c>
       <c r="L92" t="n">
-        <v>18.94038067850117</v>
+        <v>18.70496455751945</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>-9.984188693619178</v>
+        <v>-1.332170214856333</v>
       </c>
       <c r="B93" t="n">
         <v>0</v>
       </c>
       <c r="C93" t="n">
-        <v>-2.5</v>
+        <v>10</v>
       </c>
       <c r="D93" t="n">
-        <v>0.3</v>
+        <v>0.1</v>
       </c>
       <c r="E93" t="n">
-        <v>7.605970677697359</v>
+        <v>6.881596036859924</v>
       </c>
       <c r="F93" t="n">
-        <v>6.362148656201553</v>
+        <v>7.035067073026367</v>
       </c>
       <c r="G93" t="n">
         <v>0</v>
       </c>
       <c r="H93" t="n">
-        <v>4.317420265021632</v>
+        <v>5.234362327473655</v>
       </c>
       <c r="I93" t="n">
-        <v>28.63990654335813</v>
+        <v>23.28719013922434</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
       </c>
       <c r="K93" t="n">
-        <v>5.055702035797743</v>
+        <v>6.114834605628894</v>
       </c>
       <c r="L93" t="n">
-        <v>15.12651732498204</v>
+        <v>12.4596904990298</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>-7.365968100259192</v>
+        <v>-4.049495629276092</v>
       </c>
       <c r="B94" t="n">
         <v>0</v>
       </c>
       <c r="C94" t="n">
-        <v>8.75</v>
+        <v>10</v>
       </c>
       <c r="D94" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="E94" t="n">
-        <v>6.766465349086308</v>
+        <v>6.766664235926041</v>
       </c>
       <c r="F94" t="n">
-        <v>7.155388863827751</v>
+        <v>7.155177451354788</v>
       </c>
       <c r="G94" t="n">
         <v>0</v>
       </c>
       <c r="H94" t="n">
-        <v>5.150212148608789</v>
+        <v>5.234362327461625</v>
       </c>
       <c r="I94" t="n">
-        <v>23.69073351504579</v>
+        <v>23.28719013941486</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
       </c>
       <c r="K94" t="n">
-        <v>6.013539744734726</v>
+        <v>6.114834605629452</v>
       </c>
       <c r="L94" t="n">
-        <v>12.67302773292533</v>
+        <v>12.45969049902895</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>3.91092153648371</v>
+        <v>-6.567710567906022</v>
       </c>
       <c r="B95" t="n">
         <v>0</v>
       </c>
       <c r="C95" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="D95" t="n">
         <v>0.3</v>
       </c>
       <c r="E95" t="n">
-        <v>5.995457690848498</v>
+        <v>6.676228233285356</v>
       </c>
       <c r="F95" t="n">
-        <v>8.081355488651266</v>
+        <v>7.25261875260166</v>
       </c>
       <c r="G95" t="n">
         <v>0</v>
       </c>
       <c r="H95" t="n">
-        <v>5.846909926368792</v>
+        <v>5.234362327483132</v>
       </c>
       <c r="I95" t="n">
-        <v>20.72742782212902</v>
+        <v>23.28719013923191</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
       </c>
       <c r="K95" t="n">
-        <v>6.810947385869359</v>
+        <v>6.114834605629493</v>
       </c>
       <c r="L95" t="n">
-        <v>11.16889058379026</v>
+        <v>12.45969049902883</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>-10.4495882656454</v>
+        <v>-8.916920732880685</v>
       </c>
       <c r="B96" t="n">
-        <v>80</v>
+        <v>0</v>
       </c>
       <c r="C96" t="n">
-        <v>-25</v>
+        <v>10</v>
       </c>
       <c r="D96" t="n">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="E96" t="n">
-        <v>9.212529374081219</v>
+        <v>6.602232654388004</v>
       </c>
       <c r="F96" t="n">
-        <v>5.249216019122025</v>
+        <v>7.334348027625421</v>
       </c>
       <c r="G96" t="n">
         <v>0</v>
       </c>
       <c r="H96" t="n">
-        <v>2.697430397011625</v>
+        <v>5.234362327483363</v>
       </c>
       <c r="I96" t="n">
-        <v>50.09930379941456</v>
+        <v>23.28719013922635</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
       </c>
       <c r="K96" t="n">
-        <v>1.851286032999603</v>
+        <v>6.114834605629477</v>
       </c>
       <c r="L96" t="n">
-        <v>45.44972574208458</v>
+        <v>12.45969049902877</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>-10.46507208933208</v>
+        <v>-18.81803641841031</v>
       </c>
       <c r="B97" t="n">
-        <v>80</v>
+        <v>0</v>
       </c>
       <c r="C97" t="n">
-        <v>-13.75</v>
+        <v>10</v>
       </c>
       <c r="D97" t="n">
-        <v>0.3</v>
+        <v>0.9</v>
       </c>
       <c r="E97" t="n">
-        <v>8.433017676914961</v>
+        <v>6.361184206158711</v>
       </c>
       <c r="F97" t="n">
-        <v>5.735988806694721</v>
+        <v>7.613890141625032</v>
       </c>
       <c r="G97" t="n">
         <v>0</v>
       </c>
       <c r="H97" t="n">
-        <v>3.462688175313513</v>
+        <v>5.234362327483369</v>
       </c>
       <c r="I97" t="n">
-        <v>36.69925968473708</v>
+        <v>23.28719013922631</v>
       </c>
       <c r="J97" t="n">
         <v>0</v>
       </c>
       <c r="K97" t="n">
-        <v>2.692712986681277</v>
+        <v>6.114834605629372</v>
       </c>
       <c r="L97" t="n">
-        <v>29.33723107003303</v>
+        <v>12.45969049902921</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>-9.984188693619284</v>
+        <v>26.3347781324592</v>
       </c>
       <c r="B98" t="n">
-        <v>80</v>
+        <v>0</v>
       </c>
       <c r="C98" t="n">
-        <v>-2.5</v>
+        <v>10</v>
       </c>
       <c r="D98" t="n">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="E98" t="n">
-        <v>7.605970677697347</v>
+        <v>7.03652582351871</v>
       </c>
       <c r="F98" t="n">
-        <v>6.362148656201563</v>
+        <v>6.879412161042484</v>
       </c>
       <c r="G98" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="H98" t="n">
-        <v>4.317420265039446</v>
+        <v>5.052738297533367</v>
       </c>
       <c r="I98" t="n">
-        <v>28.63990654316929</v>
+        <v>24.17662715341196</v>
       </c>
       <c r="J98" t="n">
-        <v>0</v>
+        <v>0.1082177012392873</v>
       </c>
       <c r="K98" t="n">
-        <v>3.621786851634055</v>
+        <v>5.756026313118035</v>
       </c>
       <c r="L98" t="n">
-        <v>21.36238898698148</v>
+        <v>13.25008811295539</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>-7.365968100017102</v>
+        <v>47.70273922685348</v>
       </c>
       <c r="B99" t="n">
-        <v>80</v>
+        <v>0</v>
       </c>
       <c r="C99" t="n">
-        <v>8.75</v>
+        <v>10</v>
       </c>
       <c r="D99" t="n">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="E99" t="n">
-        <v>6.766465349086302</v>
+        <v>7.036525823518708</v>
       </c>
       <c r="F99" t="n">
-        <v>7.155388863827755</v>
+        <v>6.879412161042415</v>
       </c>
       <c r="G99" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="H99" t="n">
-        <v>5.150212148601946</v>
+        <v>4.910237968469839</v>
       </c>
       <c r="I99" t="n">
-        <v>23.69073351504199</v>
+        <v>24.92531420114916</v>
       </c>
       <c r="J99" t="n">
-        <v>0</v>
+        <v>0.1861872028258322</v>
       </c>
       <c r="K99" t="n">
-        <v>4.535282099548892</v>
+        <v>5.569182817693889</v>
       </c>
       <c r="L99" t="n">
-        <v>16.91156195178421</v>
+        <v>13.70314677153785</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>1.819422789837894</v>
+        <v>69.5288724871215</v>
       </c>
       <c r="B100" t="n">
-        <v>80</v>
+        <v>0</v>
       </c>
       <c r="C100" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="D100" t="n">
+        <v>0</v>
+      </c>
+      <c r="E100" t="n">
+        <v>7.036525823518708</v>
+      </c>
+      <c r="F100" t="n">
+        <v>6.879412161042429</v>
+      </c>
+      <c r="G100" t="n">
         <v>0.3</v>
       </c>
-      <c r="E100" t="n">
-        <v>5.995457690834369</v>
-      </c>
-      <c r="F100" t="n">
-        <v>8.08135548870519</v>
-      </c>
-      <c r="G100" t="n">
-        <v>0</v>
-      </c>
       <c r="H100" t="n">
-        <v>5.846909926368792</v>
+        <v>4.793680444460562</v>
       </c>
       <c r="I100" t="n">
-        <v>20.72742782212901</v>
+        <v>25.57445800156789</v>
       </c>
       <c r="J100" t="n">
-        <v>0</v>
+        <v>0.2724584114361717</v>
       </c>
       <c r="K100" t="n">
-        <v>5.378369430307161</v>
+        <v>5.404204350756454</v>
       </c>
       <c r="L100" t="n">
-        <v>14.1993225682646</v>
+        <v>14.13002829260943</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>-13.82660796280592</v>
+        <v>91.57591160279156</v>
       </c>
       <c r="B101" t="n">
         <v>0</v>
       </c>
       <c r="C101" t="n">
-        <v>-25</v>
+        <v>10</v>
       </c>
       <c r="D101" t="n">
+        <v>0</v>
+      </c>
+      <c r="E101" t="n">
+        <v>7.036525823518708</v>
+      </c>
+      <c r="F101" t="n">
+        <v>6.879412161042457</v>
+      </c>
+      <c r="G101" t="n">
         <v>0.4</v>
       </c>
-      <c r="E101" t="n">
-        <v>9.111589061977842</v>
-      </c>
-      <c r="F101" t="n">
-        <v>5.307534045233508</v>
-      </c>
-      <c r="G101" t="n">
-        <v>0</v>
-      </c>
       <c r="H101" t="n">
-        <v>2.697430408339546</v>
+        <v>4.698669450636105</v>
       </c>
       <c r="I101" t="n">
-        <v>50.09930411360449</v>
+        <v>26.13021459058483</v>
       </c>
       <c r="J101" t="n">
-        <v>0</v>
+        <v>0.3709916581317118</v>
       </c>
       <c r="K101" t="n">
-        <v>3.092067328860548</v>
+        <v>5.250672918035875</v>
       </c>
       <c r="L101" t="n">
-        <v>25.25640928190202</v>
+        <v>14.55217543507358</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>-13.79730942737848</v>
+        <v>195.769790155638</v>
       </c>
       <c r="B102" t="n">
         <v>0</v>
       </c>
       <c r="C102" t="n">
-        <v>-13.75</v>
+        <v>10</v>
       </c>
       <c r="D102" t="n">
-        <v>0.4</v>
+        <v>0</v>
       </c>
       <c r="E102" t="n">
-        <v>8.336803009365203</v>
+        <v>7.036525823518715</v>
       </c>
       <c r="F102" t="n">
-        <v>5.80241352427458</v>
+        <v>6.87941216104245</v>
       </c>
       <c r="G102" t="n">
-        <v>0</v>
+        <v>0.9</v>
       </c>
       <c r="H102" t="n">
-        <v>3.462688399984243</v>
+        <v>4.389800427566256</v>
       </c>
       <c r="I102" t="n">
-        <v>36.699255765129</v>
+        <v>28.12523679037499</v>
       </c>
       <c r="J102" t="n">
-        <v>0</v>
+        <v>0.9187962143520164</v>
       </c>
       <c r="K102" t="n">
-        <v>4.06456149042292</v>
+        <v>4.713439010305852</v>
       </c>
       <c r="L102" t="n">
-        <v>18.94038068030117</v>
+        <v>16.25424305335352</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>-13.14038874280583</v>
+        <v>28.98896336111186</v>
       </c>
       <c r="B103" t="n">
         <v>0</v>
       </c>
       <c r="C103" t="n">
-        <v>-2.5</v>
+        <v>10</v>
       </c>
       <c r="D103" t="n">
-        <v>0.4</v>
+        <v>0</v>
       </c>
       <c r="E103" t="n">
-        <v>7.514877068152784</v>
+        <v>7.036525823518705</v>
       </c>
       <c r="F103" t="n">
-        <v>6.439593552626725</v>
+        <v>6.879412161042408</v>
       </c>
       <c r="G103" t="n">
-        <v>0</v>
+        <v>0.1247653346366633</v>
       </c>
       <c r="H103" t="n">
-        <v>4.317420264889265</v>
+        <v>5.01422572594895</v>
       </c>
       <c r="I103" t="n">
-        <v>28.63990654464258</v>
+        <v>24.37434002473973</v>
       </c>
       <c r="J103" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="K103" t="n">
-        <v>5.055702035781158</v>
+        <v>5.778561248032205</v>
       </c>
       <c r="L103" t="n">
-        <v>15.12651732503968</v>
+        <v>13.19748050013088</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>-9.841728665707034</v>
+        <v>49.86104721298723</v>
       </c>
       <c r="B104" t="n">
         <v>0</v>
       </c>
       <c r="C104" t="n">
-        <v>8.75</v>
+        <v>10</v>
       </c>
       <c r="D104" t="n">
-        <v>0.4</v>
+        <v>0</v>
       </c>
       <c r="E104" t="n">
-        <v>6.689819231202722</v>
+        <v>7.036525823518712</v>
       </c>
       <c r="F104" t="n">
-        <v>7.23780541389895</v>
+        <v>6.879412161042455</v>
       </c>
       <c r="G104" t="n">
-        <v>0</v>
+        <v>0.2063981465460308</v>
       </c>
       <c r="H104" t="n">
-        <v>5.150212148607553</v>
+        <v>4.902195711594073</v>
       </c>
       <c r="I104" t="n">
-        <v>23.69073351504943</v>
+        <v>24.96900398019909</v>
       </c>
       <c r="J104" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="K104" t="n">
-        <v>6.01353974473447</v>
+        <v>5.540289473033624</v>
       </c>
       <c r="L104" t="n">
-        <v>12.67302773292558</v>
+        <v>13.77601630590739</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>2.692555536625074</v>
+        <v>73.82948992900793</v>
       </c>
       <c r="B105" t="n">
         <v>0</v>
       </c>
       <c r="C105" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="D105" t="n">
-        <v>0.4</v>
+        <v>0</v>
       </c>
       <c r="E105" t="n">
-        <v>5.947428973040717</v>
+        <v>7.036525823518715</v>
       </c>
       <c r="F105" t="n">
-        <v>8.14705842742524</v>
+        <v>6.879412161042474</v>
       </c>
       <c r="G105" t="n">
-        <v>0</v>
+        <v>0.3137697936590399</v>
       </c>
       <c r="H105" t="n">
-        <v>5.846909926368788</v>
+        <v>4.779478728641965</v>
       </c>
       <c r="I105" t="n">
-        <v>20.72742782212903</v>
+        <v>25.65596181732004</v>
       </c>
       <c r="J105" t="n">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="K105" t="n">
-        <v>6.810947385890589</v>
+        <v>5.358158620144749</v>
       </c>
       <c r="L105" t="n">
-        <v>11.16889058380411</v>
+        <v>14.25401270430055</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>-13.82660796281279</v>
+        <v>94.33705261420074</v>
       </c>
       <c r="B106" t="n">
-        <v>80</v>
+        <v>0</v>
       </c>
       <c r="C106" t="n">
-        <v>-25</v>
+        <v>10</v>
       </c>
       <c r="D106" t="n">
+        <v>0</v>
+      </c>
+      <c r="E106" t="n">
+        <v>7.036525823518714</v>
+      </c>
+      <c r="F106" t="n">
+        <v>6.879412161042461</v>
+      </c>
+      <c r="G106" t="n">
+        <v>0.4026174994879254</v>
+      </c>
+      <c r="H106" t="n">
+        <v>4.696410910174022</v>
+      </c>
+      <c r="I106" t="n">
+        <v>26.14373195327791</v>
+      </c>
+      <c r="J106" t="n">
         <v>0.4</v>
       </c>
-      <c r="E106" t="n">
-        <v>9.111589061977831</v>
-      </c>
-      <c r="F106" t="n">
-        <v>5.307534045233514</v>
-      </c>
-      <c r="G106" t="n">
-        <v>0</v>
-      </c>
-      <c r="H106" t="n">
-        <v>2.697430228538366</v>
-      </c>
-      <c r="I106" t="n">
-        <v>50.09929866258928</v>
-      </c>
-      <c r="J106" t="n">
-        <v>0</v>
-      </c>
       <c r="K106" t="n">
-        <v>1.851286178605729</v>
+        <v>5.210672537910132</v>
       </c>
       <c r="L106" t="n">
-        <v>45.4497384750269</v>
+        <v>14.66638237813964</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>-13.79730942738522</v>
+        <v>197.5197333722285</v>
       </c>
       <c r="B107" t="n">
-        <v>80</v>
+        <v>0</v>
       </c>
       <c r="C107" t="n">
-        <v>-13.75</v>
+        <v>10</v>
       </c>
       <c r="D107" t="n">
-        <v>0.4</v>
+        <v>0</v>
       </c>
       <c r="E107" t="n">
-        <v>8.336803009365196</v>
+        <v>7.036525823518709</v>
       </c>
       <c r="F107" t="n">
-        <v>5.802413524274586</v>
+        <v>6.87941216104239</v>
       </c>
       <c r="G107" t="n">
-        <v>0</v>
+        <v>0.9261043454272662</v>
       </c>
       <c r="H107" t="n">
-        <v>3.462688409456333</v>
+        <v>4.378071981065519</v>
       </c>
       <c r="I107" t="n">
-        <v>36.69925559789363</v>
+        <v>28.20731119596918</v>
       </c>
       <c r="J107" t="n">
-        <v>0</v>
+        <v>0.9</v>
       </c>
       <c r="K107" t="n">
-        <v>2.692712986680905</v>
+        <v>4.726652454008943</v>
       </c>
       <c r="L107" t="n">
-        <v>29.33723106999774</v>
+        <v>16.20755001913633</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>-13.14038874280593</v>
+        <v>6.834780035277051</v>
       </c>
       <c r="B108" t="n">
-        <v>80</v>
+        <v>0</v>
       </c>
       <c r="C108" t="n">
-        <v>-2.5</v>
+        <v>20</v>
       </c>
       <c r="D108" t="n">
-        <v>0.4</v>
+        <v>0.1</v>
       </c>
       <c r="E108" t="n">
-        <v>7.514877068152768</v>
+        <v>6.128497937407318</v>
       </c>
       <c r="F108" t="n">
-        <v>6.439593552626738</v>
+        <v>7.904787369190159</v>
       </c>
       <c r="G108" t="n">
         <v>0</v>
       </c>
       <c r="H108" t="n">
-        <v>4.317420265039076</v>
+        <v>5.846909926368788</v>
       </c>
       <c r="I108" t="n">
-        <v>28.63990654317487</v>
+        <v>20.72742782212903</v>
       </c>
       <c r="J108" t="n">
         <v>0</v>
       </c>
       <c r="K108" t="n">
-        <v>3.62178686100707</v>
+        <v>6.810947385913783</v>
       </c>
       <c r="L108" t="n">
-        <v>21.36238893698081</v>
+        <v>11.16889058376146</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>-9.841728665934587</v>
+        <v>5.274583490016099</v>
       </c>
       <c r="B109" t="n">
-        <v>80</v>
+        <v>0</v>
       </c>
       <c r="C109" t="n">
-        <v>8.75</v>
+        <v>20</v>
       </c>
       <c r="D109" t="n">
-        <v>0.4</v>
+        <v>0.2</v>
       </c>
       <c r="E109" t="n">
-        <v>6.689819231197401</v>
+        <v>6.054000358592873</v>
       </c>
       <c r="F109" t="n">
-        <v>7.2378054139025</v>
+        <v>8.002693397380355</v>
       </c>
       <c r="G109" t="n">
         <v>0</v>
       </c>
       <c r="H109" t="n">
-        <v>5.150212148608286</v>
+        <v>5.846909926368786</v>
       </c>
       <c r="I109" t="n">
-        <v>23.69073351504735</v>
+        <v>20.72742782212903</v>
       </c>
       <c r="J109" t="n">
         <v>0</v>
       </c>
       <c r="K109" t="n">
-        <v>4.535282099247598</v>
+        <v>6.810947385909925</v>
       </c>
       <c r="L109" t="n">
-        <v>16.91156195286188</v>
+        <v>11.16889058379427</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>0.6010567903846513</v>
+        <v>3.910921536253885</v>
       </c>
       <c r="B110" t="n">
-        <v>80</v>
+        <v>0</v>
       </c>
       <c r="C110" t="n">
         <v>20</v>
       </c>
       <c r="D110" t="n">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="E110" t="n">
-        <v>5.947428973040708</v>
+        <v>5.995457690847346</v>
       </c>
       <c r="F110" t="n">
-        <v>8.14705842742525</v>
+        <v>8.081355488661039</v>
       </c>
       <c r="G110" t="n">
         <v>0</v>
       </c>
       <c r="H110" t="n">
-        <v>5.846909926368793</v>
+        <v>5.84690992636879</v>
       </c>
       <c r="I110" t="n">
-        <v>20.72742782212901</v>
+        <v>20.72742782212902</v>
       </c>
       <c r="J110" t="n">
         <v>0</v>
       </c>
       <c r="K110" t="n">
-        <v>5.378369430307506</v>
+        <v>6.810947385881176</v>
       </c>
       <c r="L110" t="n">
-        <v>14.19932256826113</v>
+        <v>11.16889058380283</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>-17.15942453689336</v>
+        <v>2.692555536845356</v>
       </c>
       <c r="B111" t="n">
         <v>0</v>
       </c>
       <c r="C111" t="n">
-        <v>-25</v>
+        <v>20</v>
       </c>
       <c r="D111" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="E111" t="n">
-        <v>9.025705858535812</v>
+        <v>5.947428973040711</v>
       </c>
       <c r="F111" t="n">
-        <v>5.358184396907852</v>
+        <v>8.147058427425245</v>
       </c>
       <c r="G111" t="n">
         <v>0</v>
       </c>
       <c r="H111" t="n">
-        <v>2.69743040738629</v>
+        <v>5.846909926359623</v>
       </c>
       <c r="I111" t="n">
-        <v>50.09930408828735</v>
+        <v>20.72742782229992</v>
       </c>
       <c r="J111" t="n">
         <v>0</v>
       </c>
       <c r="K111" t="n">
-        <v>3.092067374784749</v>
+        <v>6.810947385890646</v>
       </c>
       <c r="L111" t="n">
-        <v>25.25640889612558</v>
+        <v>11.1688905838042</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>-17.07945699332591</v>
+        <v>-2.079471920009799</v>
       </c>
       <c r="B112" t="n">
         <v>0</v>
       </c>
       <c r="C112" t="n">
-        <v>-13.75</v>
+        <v>20</v>
       </c>
       <c r="D112" t="n">
-        <v>0.5</v>
+        <v>0.9</v>
       </c>
       <c r="E112" t="n">
-        <v>8.254569957830423</v>
+        <v>5.788470958957247</v>
       </c>
       <c r="F112" t="n">
-        <v>5.860419307620335</v>
+        <v>8.372370077823835</v>
       </c>
       <c r="G112" t="n">
         <v>0</v>
       </c>
       <c r="H112" t="n">
-        <v>3.462688387427111</v>
+        <v>5.846909926368789</v>
       </c>
       <c r="I112" t="n">
-        <v>36.69925599885713</v>
+        <v>20.72742782212902</v>
       </c>
       <c r="J112" t="n">
         <v>0</v>
       </c>
       <c r="K112" t="n">
-        <v>4.064561490841525</v>
+        <v>6.810947385874627</v>
       </c>
       <c r="L112" t="n">
-        <v>18.94038067857602</v>
+        <v>11.16889058380216</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>-16.23184919279053</v>
+        <v>27.62637003434606</v>
       </c>
       <c r="B113" t="n">
         <v>0</v>
       </c>
       <c r="C113" t="n">
-        <v>-2.5</v>
+        <v>20</v>
       </c>
       <c r="D113" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="E113" t="n">
-        <v>7.436891869892993</v>
+        <v>6.229814680542392</v>
       </c>
       <c r="F113" t="n">
-        <v>6.507411143664583</v>
+        <v>7.775428450084743</v>
       </c>
       <c r="G113" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="H113" t="n">
-        <v>4.317420265039443</v>
+        <v>5.709722682678406</v>
       </c>
       <c r="I113" t="n">
-        <v>28.63990654316924</v>
+        <v>21.24927763819725</v>
       </c>
       <c r="J113" t="n">
-        <v>0</v>
+        <v>0.1082177012392873</v>
       </c>
       <c r="K113" t="n">
-        <v>5.055702035797738</v>
+        <v>6.501604554939219</v>
       </c>
       <c r="L113" t="n">
-        <v>15.12651732498189</v>
+        <v>11.70764336776432</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>-12.17765130256971</v>
+        <v>45.98878045746835</v>
       </c>
       <c r="B114" t="n">
         <v>0</v>
       </c>
       <c r="C114" t="n">
-        <v>8.75</v>
+        <v>20</v>
       </c>
       <c r="D114" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="E114" t="n">
-        <v>6.625212417705308</v>
+        <v>6.229814680542415</v>
       </c>
       <c r="F114" t="n">
-        <v>7.308769470067114</v>
+        <v>7.775428450084248</v>
       </c>
       <c r="G114" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="H114" t="n">
-        <v>5.150212148578055</v>
+        <v>5.582196107608238</v>
       </c>
       <c r="I114" t="n">
-        <v>23.69073351535597</v>
+        <v>21.75916478669942</v>
       </c>
       <c r="J114" t="n">
-        <v>0</v>
+        <v>0.1861872028258322</v>
       </c>
       <c r="K114" t="n">
-        <v>6.013539744734474</v>
+        <v>6.311575079575896</v>
       </c>
       <c r="L114" t="n">
-        <v>12.67302773292558</v>
+        <v>12.06536120701531</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>1.586611517673222</v>
+        <v>66.10333155687294</v>
       </c>
       <c r="B115" t="n">
         <v>0</v>
@@ -4795,601 +4795,677 @@
         <v>20</v>
       </c>
       <c r="D115" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="E115" t="n">
-        <v>5.906819476058409</v>
+        <v>6.229814680542388</v>
       </c>
       <c r="F115" t="n">
-        <v>8.20345416460445</v>
+        <v>7.775428450084738</v>
       </c>
       <c r="G115" t="n">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="H115" t="n">
-        <v>5.846909926365421</v>
+        <v>5.467817013843073</v>
       </c>
       <c r="I115" t="n">
-        <v>20.72742782213875</v>
+        <v>22.23836450104402</v>
       </c>
       <c r="J115" t="n">
-        <v>0</v>
+        <v>0.2724584114361717</v>
       </c>
       <c r="K115" t="n">
-        <v>6.81094738588264</v>
+        <v>6.134000054261062</v>
       </c>
       <c r="L115" t="n">
-        <v>11.1688905838111</v>
+        <v>12.42013818746446</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>-17.15942453689986</v>
+        <v>87.92605840786248</v>
       </c>
       <c r="B116" t="n">
-        <v>80</v>
+        <v>0</v>
       </c>
       <c r="C116" t="n">
-        <v>-25</v>
+        <v>20</v>
       </c>
       <c r="D116" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="E116" t="n">
-        <v>9.025705858535805</v>
+        <v>6.229814680542417</v>
       </c>
       <c r="F116" t="n">
-        <v>5.358184396907858</v>
+        <v>7.775428450084322</v>
       </c>
       <c r="G116" t="n">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="H116" t="n">
-        <v>2.697430209526561</v>
+        <v>5.366971155165505</v>
       </c>
       <c r="I116" t="n">
-        <v>50.09929797621464</v>
+        <v>22.67925293210372</v>
       </c>
       <c r="J116" t="n">
-        <v>0</v>
+        <v>0.3709916581317118</v>
       </c>
       <c r="K116" t="n">
-        <v>1.851286213635065</v>
+        <v>5.961526264742207</v>
       </c>
       <c r="L116" t="n">
-        <v>45.44974127852272</v>
+        <v>12.78546215459656</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>-17.07945699333722</v>
+        <v>197.758045242448</v>
       </c>
       <c r="B117" t="n">
-        <v>80</v>
+        <v>0</v>
       </c>
       <c r="C117" t="n">
-        <v>-13.75</v>
+        <v>20</v>
       </c>
       <c r="D117" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="E117" t="n">
-        <v>8.254569957830412</v>
+        <v>6.229814680542415</v>
       </c>
       <c r="F117" t="n">
-        <v>5.860419307620341</v>
+        <v>7.775428450084292</v>
       </c>
       <c r="G117" t="n">
-        <v>0</v>
+        <v>0.9</v>
       </c>
       <c r="H117" t="n">
-        <v>3.462688417352492</v>
+        <v>5.013853272390429</v>
       </c>
       <c r="I117" t="n">
-        <v>36.69925545235069</v>
+        <v>24.37626844442449</v>
       </c>
       <c r="J117" t="n">
-        <v>0</v>
+        <v>0.9187962143520164</v>
       </c>
       <c r="K117" t="n">
-        <v>2.692712444544163</v>
+        <v>5.375148878582299</v>
       </c>
       <c r="L117" t="n">
-        <v>29.33723760304244</v>
+        <v>14.20800890067435</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>-16.23184919279023</v>
+        <v>29.59676576433829</v>
       </c>
       <c r="B118" t="n">
-        <v>80</v>
+        <v>0</v>
       </c>
       <c r="C118" t="n">
-        <v>-2.5</v>
+        <v>20</v>
       </c>
       <c r="D118" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="E118" t="n">
-        <v>7.436891869892984</v>
+        <v>6.229814680542383</v>
       </c>
       <c r="F118" t="n">
-        <v>6.507411143664591</v>
+        <v>7.775428450084793</v>
       </c>
       <c r="G118" t="n">
-        <v>0</v>
+        <v>0.1247653346366633</v>
       </c>
       <c r="H118" t="n">
-        <v>4.317420264970496</v>
+        <v>5.677040887610818</v>
       </c>
       <c r="I118" t="n">
-        <v>28.63990654387483</v>
+        <v>21.37759753844515</v>
       </c>
       <c r="J118" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="K118" t="n">
-        <v>3.621786836894442</v>
+        <v>6.523361592502432</v>
       </c>
       <c r="L118" t="n">
-        <v>21.362389064384</v>
+        <v>11.66804559417191</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>-12.17765130281764</v>
+        <v>48.00714090231821</v>
       </c>
       <c r="B119" t="n">
-        <v>80</v>
+        <v>0</v>
       </c>
       <c r="C119" t="n">
-        <v>8.75</v>
+        <v>20</v>
       </c>
       <c r="D119" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="E119" t="n">
-        <v>6.625212417706207</v>
+        <v>6.229814680542414</v>
       </c>
       <c r="F119" t="n">
-        <v>7.308769470065622</v>
+        <v>7.775428450084282</v>
       </c>
       <c r="G119" t="n">
-        <v>0</v>
+        <v>0.2063981465460308</v>
       </c>
       <c r="H119" t="n">
-        <v>5.150212148551963</v>
+        <v>5.574467231081983</v>
       </c>
       <c r="I119" t="n">
-        <v>23.69073351572435</v>
+        <v>21.79087610485098</v>
       </c>
       <c r="J119" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="K119" t="n">
-        <v>4.535282099548886</v>
+        <v>6.280953943054494</v>
       </c>
       <c r="L119" t="n">
-        <v>16.91156195178437</v>
+        <v>12.12507452459406</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>-0.5048872289825534</v>
+        <v>70.34975053173936</v>
       </c>
       <c r="B120" t="n">
-        <v>80</v>
+        <v>0</v>
       </c>
       <c r="C120" t="n">
         <v>20</v>
       </c>
       <c r="D120" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="E120" t="n">
-        <v>5.9068194760584</v>
+        <v>6.229814680542414</v>
       </c>
       <c r="F120" t="n">
-        <v>8.203454164604464</v>
+        <v>7.775428450084324</v>
       </c>
       <c r="G120" t="n">
-        <v>0</v>
+        <v>0.3137697936590399</v>
       </c>
       <c r="H120" t="n">
-        <v>5.846909926368777</v>
+        <v>5.453144591001693</v>
       </c>
       <c r="I120" t="n">
-        <v>20.72742782212905</v>
+        <v>22.30141150939614</v>
       </c>
       <c r="J120" t="n">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="K120" t="n">
-        <v>5.378369430307496</v>
+        <v>6.083014358416881</v>
       </c>
       <c r="L120" t="n">
-        <v>14.1993225682609</v>
+        <v>12.52592282596386</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>-20.45343309450399</v>
+        <v>90.85820507627585</v>
       </c>
       <c r="B121" t="n">
         <v>0</v>
       </c>
       <c r="C121" t="n">
-        <v>-25</v>
+        <v>20</v>
       </c>
       <c r="D121" t="n">
-        <v>0.6</v>
+        <v>0</v>
       </c>
       <c r="E121" t="n">
-        <v>8.950992434801035</v>
+        <v>6.229814680542382</v>
       </c>
       <c r="F121" t="n">
-        <v>5.40304134680026</v>
+        <v>7.775428450084776</v>
       </c>
       <c r="G121" t="n">
-        <v>0</v>
+        <v>0.4026174994879254</v>
       </c>
       <c r="H121" t="n">
-        <v>2.69743016123039</v>
+        <v>5.364503824149426</v>
       </c>
       <c r="I121" t="n">
-        <v>50.09929651701572</v>
+        <v>22.69026561983227</v>
       </c>
       <c r="J121" t="n">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="K121" t="n">
-        <v>3.092067365683372</v>
+        <v>5.916680425885447</v>
       </c>
       <c r="L121" t="n">
-        <v>25.2564089897531</v>
+        <v>12.8840308499482</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>-20.32021007754235</v>
+        <v>199.6739991890043</v>
       </c>
       <c r="B122" t="n">
         <v>0</v>
       </c>
       <c r="C122" t="n">
-        <v>-13.75</v>
+        <v>20</v>
       </c>
       <c r="D122" t="n">
-        <v>0.6</v>
+        <v>0</v>
       </c>
       <c r="E122" t="n">
-        <v>8.182740097315353</v>
+        <v>6.22981468054238</v>
       </c>
       <c r="F122" t="n">
-        <v>5.912045884180045</v>
+        <v>7.7754284500848</v>
       </c>
       <c r="G122" t="n">
-        <v>0</v>
+        <v>0.9261043454272662</v>
       </c>
       <c r="H122" t="n">
-        <v>3.462688406611163</v>
+        <v>5.000219964684943</v>
       </c>
       <c r="I122" t="n">
-        <v>36.69925565148029</v>
+        <v>24.44707451116663</v>
       </c>
       <c r="J122" t="n">
-        <v>0</v>
+        <v>0.9</v>
       </c>
       <c r="K122" t="n">
-        <v>4.064561490857447</v>
+        <v>5.389450425310828</v>
       </c>
       <c r="L122" t="n">
-        <v>18.94038067850483</v>
+        <v>14.16951723043</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>-19.26395571834507</v>
+        <v>20.77610213266333</v>
       </c>
       <c r="B123" t="n">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="C123" t="n">
-        <v>-2.5</v>
+        <v>0</v>
       </c>
       <c r="D123" t="n">
-        <v>0.6</v>
+        <v>0</v>
       </c>
       <c r="E123" t="n">
-        <v>7.368807783687821</v>
+        <v>7.837064168615003</v>
       </c>
       <c r="F123" t="n">
-        <v>6.567799866803471</v>
+        <v>6.173805682149559</v>
       </c>
       <c r="G123" t="n">
-        <v>0</v>
+        <v>0.1189512132472919</v>
       </c>
       <c r="H123" t="n">
-        <v>4.317420265039444</v>
+        <v>4.308972894003879</v>
       </c>
       <c r="I123" t="n">
-        <v>28.63990654316963</v>
+        <v>28.70126676014912</v>
       </c>
       <c r="J123" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="K123" t="n">
-        <v>5.055702035796507</v>
+        <v>3.770437980766415</v>
       </c>
       <c r="L123" t="n">
-        <v>15.12651732499019</v>
+        <v>20.4814558693205</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>-14.39045002263121</v>
+        <v>30.26703441387749</v>
       </c>
       <c r="B124" t="n">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="C124" t="n">
-        <v>8.75</v>
+        <v>0</v>
       </c>
       <c r="D124" t="n">
-        <v>0.6</v>
+        <v>0</v>
       </c>
       <c r="E124" t="n">
-        <v>6.569613026694836</v>
+        <v>7.837064168615002</v>
       </c>
       <c r="F124" t="n">
-        <v>7.370966470469857</v>
+        <v>6.173805682149557</v>
       </c>
       <c r="G124" t="n">
-        <v>0</v>
+        <v>0.1701643100102089</v>
       </c>
       <c r="H124" t="n">
-        <v>5.150212148567443</v>
+        <v>4.244175767458287</v>
       </c>
       <c r="I124" t="n">
-        <v>23.69073351560511</v>
+        <v>29.18131136449999</v>
       </c>
       <c r="J124" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="K124" t="n">
-        <v>6.013539744734474</v>
+        <v>3.688256945374647</v>
       </c>
       <c r="L124" t="n">
-        <v>12.6730277329261</v>
+        <v>20.95905522000981</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>0.5706154448558407</v>
+        <v>51.19915313046028</v>
       </c>
       <c r="B125" t="n">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="C125" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="D125" t="n">
-        <v>0.6</v>
+        <v>0</v>
       </c>
       <c r="E125" t="n">
-        <v>5.871708818229415</v>
+        <v>7.837064168614999</v>
       </c>
       <c r="F125" t="n">
-        <v>8.252848844151535</v>
+        <v>6.173805682149546</v>
       </c>
       <c r="G125" t="n">
-        <v>0</v>
+        <v>0.3214442565952542</v>
       </c>
       <c r="H125" t="n">
-        <v>5.846909926368549</v>
+        <v>4.093997882615534</v>
       </c>
       <c r="I125" t="n">
-        <v>20.72742782212972</v>
+        <v>30.3619160937488</v>
       </c>
       <c r="J125" t="n">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="K125" t="n">
-        <v>6.810947385890133</v>
+        <v>3.630536246129327</v>
       </c>
       <c r="L125" t="n">
-        <v>11.16889058380323</v>
+        <v>21.30839062991481</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>-20.4534330945107</v>
+        <v>58.88742559902328</v>
       </c>
       <c r="B126" t="n">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="C126" t="n">
-        <v>-25</v>
+        <v>0</v>
       </c>
       <c r="D126" t="n">
-        <v>0.6</v>
+        <v>0</v>
       </c>
       <c r="E126" t="n">
-        <v>8.950992434801021</v>
+        <v>7.837064168615</v>
       </c>
       <c r="F126" t="n">
-        <v>5.403041346800268</v>
+        <v>6.17380568214956</v>
       </c>
       <c r="G126" t="n">
-        <v>0</v>
+        <v>0.3720151345183279</v>
       </c>
       <c r="H126" t="n">
-        <v>2.697430399040367</v>
+        <v>4.053242978902852</v>
       </c>
       <c r="I126" t="n">
-        <v>50.09930386271207</v>
+        <v>30.69998519193069</v>
       </c>
       <c r="J126" t="n">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="K126" t="n">
-        <v>1.851286189824377</v>
+        <v>3.586463213376641</v>
       </c>
       <c r="L126" t="n">
-        <v>45.44973950183766</v>
+        <v>21.58328154599323</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>-20.32021007754239</v>
+        <v>122.9848839959848</v>
       </c>
       <c r="B127" t="n">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="C127" t="n">
-        <v>-13.75</v>
+        <v>0</v>
       </c>
       <c r="D127" t="n">
-        <v>0.6</v>
+        <v>0</v>
       </c>
       <c r="E127" t="n">
-        <v>8.182740097315337</v>
+        <v>7.837064168615003</v>
       </c>
       <c r="F127" t="n">
-        <v>5.912045884180055</v>
+        <v>6.173805682149572</v>
       </c>
       <c r="G127" t="n">
-        <v>0</v>
+        <v>0.9137793267857967</v>
       </c>
       <c r="H127" t="n">
-        <v>3.462688382524524</v>
+        <v>3.761181232691156</v>
       </c>
       <c r="I127" t="n">
-        <v>36.69925607024634</v>
+        <v>33.37985343681321</v>
       </c>
       <c r="J127" t="n">
-        <v>0</v>
+        <v>0.9</v>
       </c>
       <c r="K127" t="n">
-        <v>2.692712358760854</v>
+        <v>3.453741272603847</v>
       </c>
       <c r="L127" t="n">
-        <v>29.33723836009671</v>
+        <v>22.45695698888139</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>-19.26395571816234</v>
+        <v>1.835788085431368</v>
       </c>
       <c r="B128" t="n">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="C128" t="n">
-        <v>-2.5</v>
+        <v>-25</v>
       </c>
       <c r="D128" t="n">
-        <v>0.6</v>
+        <v>0</v>
       </c>
       <c r="E128" t="n">
-        <v>7.368807783691736</v>
+        <v>9.699347069291392</v>
       </c>
       <c r="F128" t="n">
-        <v>6.567799866801868</v>
+        <v>4.985069224042763</v>
       </c>
       <c r="G128" t="n">
-        <v>0</v>
+        <v>0.1189512132472919</v>
       </c>
       <c r="H128" t="n">
-        <v>4.317420248391923</v>
+        <v>2.681662652113733</v>
       </c>
       <c r="I128" t="n">
-        <v>28.63990670568491</v>
+        <v>50.50392244803923</v>
       </c>
       <c r="J128" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="K128" t="n">
-        <v>3.62178683918326</v>
+        <v>1.908379287040441</v>
       </c>
       <c r="L128" t="n">
-        <v>21.36238905515345</v>
+        <v>43.73432903618903</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>-14.39045002236904</v>
+        <v>2.634739230819063</v>
       </c>
       <c r="B129" t="n">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="C129" t="n">
-        <v>8.75</v>
+        <v>-25</v>
       </c>
       <c r="D129" t="n">
-        <v>0.6</v>
+        <v>0</v>
       </c>
       <c r="E129" t="n">
-        <v>6.569613026694827</v>
+        <v>9.699347069291383</v>
       </c>
       <c r="F129" t="n">
-        <v>7.370966470469866</v>
+        <v>4.985069224042769</v>
       </c>
       <c r="G129" t="n">
-        <v>0</v>
+        <v>0.1701643100102089</v>
       </c>
       <c r="H129" t="n">
-        <v>5.15021214860894</v>
+        <v>2.675665367384411</v>
       </c>
       <c r="I129" t="n">
-        <v>23.69073351504542</v>
+        <v>50.65999279092324</v>
       </c>
       <c r="J129" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="K129" t="n">
-        <v>4.535282099181747</v>
+        <v>1.904998512896706</v>
       </c>
       <c r="L129" t="n">
-        <v>16.91156195302867</v>
+        <v>43.83169431140891</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>-1.520883301396249</v>
+        <v>4.564451747701021</v>
       </c>
       <c r="B130" t="n">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="C130" t="n">
-        <v>20</v>
+        <v>-25</v>
       </c>
       <c r="D130" t="n">
-        <v>0.6</v>
+        <v>0</v>
       </c>
       <c r="E130" t="n">
-        <v>5.871708818229411</v>
+        <v>9.699347069291406</v>
       </c>
       <c r="F130" t="n">
-        <v>8.25284884415154</v>
+        <v>4.98506922404275</v>
       </c>
       <c r="G130" t="n">
-        <v>0</v>
+        <v>0.3214442565952542</v>
       </c>
       <c r="H130" t="n">
-        <v>5.846909926368552</v>
+        <v>2.65998867903058</v>
       </c>
       <c r="I130" t="n">
-        <v>20.7274278221297</v>
+        <v>51.07378872710613</v>
       </c>
       <c r="J130" t="n">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="K130" t="n">
-        <v>5.37836943030751</v>
+        <v>1.901669738753149</v>
       </c>
       <c r="L130" t="n">
-        <v>14.19932256826136</v>
+        <v>43.92805650531952</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="n">
+        <v>5.247608665199103</v>
+      </c>
+      <c r="B131" t="n">
+        <v>90</v>
+      </c>
+      <c r="C131" t="n">
+        <v>-25</v>
+      </c>
+      <c r="D131" t="n">
+        <v>0</v>
+      </c>
+      <c r="E131" t="n">
+        <v>9.699347069291386</v>
+      </c>
+      <c r="F131" t="n">
+        <v>4.98506922404277</v>
+      </c>
+      <c r="G131" t="n">
+        <v>0.3720151345183279</v>
+      </c>
+      <c r="H131" t="n">
+        <v>2.6552967046603</v>
+      </c>
+      <c r="I131" t="n">
+        <v>51.19931357277213</v>
+      </c>
+      <c r="J131" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="K131" t="n">
+        <v>1.898391433030046</v>
+      </c>
+      <c r="L131" t="n">
+        <v>44.02344164232167</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="n">
+        <v>10.86255706230083</v>
+      </c>
+      <c r="B132" t="n">
+        <v>90</v>
+      </c>
+      <c r="C132" t="n">
+        <v>-25</v>
+      </c>
+      <c r="D132" t="n">
+        <v>0</v>
+      </c>
+      <c r="E132" t="n">
+        <v>9.699347069291388</v>
+      </c>
+      <c r="F132" t="n">
+        <v>4.985069224042767</v>
+      </c>
+      <c r="G132" t="n">
+        <v>0.9137793267857967</v>
+      </c>
+      <c r="H132" t="n">
+        <v>2.615721871101734</v>
+      </c>
+      <c r="I132" t="n">
+        <v>52.29043361348931</v>
+      </c>
+      <c r="J132" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="K132" t="n">
+        <v>1.882707929980548</v>
+      </c>
+      <c r="L132" t="n">
+        <v>44.48654708292874</v>
       </c>
     </row>
   </sheetData>

--- a/simulatedData/dataset_hypothetical.xlsx
+++ b/simulatedData/dataset_hypothetical.xlsx
@@ -492,7 +492,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>5.512980572083857e-12</v>
+        <v>5.443484845281919e-12</v>
       </c>
       <c r="B2" t="n">
         <v>0</v>
@@ -504,28 +504,28 @@
         <v>0</v>
       </c>
       <c r="E2" t="n">
-        <v>9.699347069291397</v>
+        <v>9.699347069291393</v>
       </c>
       <c r="F2" t="n">
-        <v>4.985069224042763</v>
+        <v>4.985069224042767</v>
       </c>
       <c r="G2" t="n">
         <v>0</v>
       </c>
       <c r="H2" t="n">
-        <v>2.69743038542935</v>
+        <v>2.697430405916348</v>
       </c>
       <c r="I2" t="n">
-        <v>50.0993034714063</v>
+        <v>50.0993040483645</v>
       </c>
       <c r="J2" t="n">
         <v>0</v>
       </c>
       <c r="K2" t="n">
-        <v>3.092067173384319</v>
+        <v>3.092067302409011</v>
       </c>
       <c r="L2" t="n">
-        <v>25.25641044512075</v>
+        <v>25.25640953197178</v>
       </c>
     </row>
     <row r="3">
@@ -542,28 +542,28 @@
         <v>0</v>
       </c>
       <c r="E3" t="n">
-        <v>9.63035488551003</v>
+        <v>9.630354885510028</v>
       </c>
       <c r="F3" t="n">
-        <v>5.020873794760699</v>
+        <v>5.020873794760672</v>
       </c>
       <c r="G3" t="n">
         <v>0</v>
       </c>
       <c r="H3" t="n">
-        <v>2.758249423216762</v>
+        <v>2.758249353703567</v>
       </c>
       <c r="I3" t="n">
-        <v>48.61131297180568</v>
+        <v>48.61131064316509</v>
       </c>
       <c r="J3" t="n">
         <v>0</v>
       </c>
       <c r="K3" t="n">
-        <v>3.176064831617197</v>
+        <v>3.176064903438797</v>
       </c>
       <c r="L3" t="n">
-        <v>24.5436117665439</v>
+        <v>24.54361124311865</v>
       </c>
     </row>
     <row r="4">
@@ -583,25 +583,25 @@
         <v>9.560827209729428</v>
       </c>
       <c r="F4" t="n">
-        <v>5.057481072452409</v>
+        <v>5.057481072452389</v>
       </c>
       <c r="G4" t="n">
         <v>0</v>
       </c>
       <c r="H4" t="n">
-        <v>2.82085533822959</v>
+        <v>2.820855337202761</v>
       </c>
       <c r="I4" t="n">
-        <v>47.18827644611995</v>
+        <v>47.18827641641769</v>
       </c>
       <c r="J4" t="n">
         <v>0</v>
       </c>
       <c r="K4" t="n">
-        <v>3.260709249356306</v>
+        <v>3.260709315896745</v>
       </c>
       <c r="L4" t="n">
-        <v>23.86623886383631</v>
+        <v>23.86623840568347</v>
       </c>
     </row>
     <row r="5">
@@ -621,25 +621,25 @@
         <v>9.490772943835177</v>
       </c>
       <c r="F5" t="n">
-        <v>5.094910212584622</v>
+        <v>5.094910212584586</v>
       </c>
       <c r="G5" t="n">
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>2.885113010565214</v>
+        <v>2.88511300332616</v>
       </c>
       <c r="I5" t="n">
-        <v>45.82807871494958</v>
+        <v>45.82807847675473</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>3.345941090590222</v>
+        <v>3.345941141093194</v>
       </c>
       <c r="L5" t="n">
-        <v>23.22209150109784</v>
+        <v>23.22209118380449</v>
       </c>
     </row>
     <row r="6">
@@ -656,28 +656,28 @@
         <v>0</v>
       </c>
       <c r="E6" t="n">
-        <v>9.420201171386378</v>
+        <v>9.420201171386379</v>
       </c>
       <c r="F6" t="n">
-        <v>5.133180979166142</v>
+        <v>5.133180979166139</v>
       </c>
       <c r="G6" t="n">
         <v>0</v>
       </c>
       <c r="H6" t="n">
-        <v>2.950892882690657</v>
+        <v>2.950892880225108</v>
       </c>
       <c r="I6" t="n">
-        <v>44.5284663082974</v>
+        <v>44.52846622806055</v>
       </c>
       <c r="J6" t="n">
         <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>3.431702821871986</v>
+        <v>3.431702862494683</v>
       </c>
       <c r="L6" t="n">
-        <v>22.60912863329828</v>
+        <v>22.60912837113162</v>
       </c>
     </row>
     <row r="7">
@@ -694,28 +694,28 @@
         <v>0</v>
       </c>
       <c r="E7" t="n">
-        <v>9.349121163616877</v>
+        <v>9.349121163616873</v>
       </c>
       <c r="F7" t="n">
-        <v>5.172313763739869</v>
+        <v>5.172313763739848</v>
       </c>
       <c r="G7" t="n">
         <v>0</v>
       </c>
       <c r="H7" t="n">
-        <v>3.018070959187208</v>
+        <v>3.01807095925132</v>
       </c>
       <c r="I7" t="n">
-        <v>43.2870928103194</v>
+        <v>43.28709281230567</v>
       </c>
       <c r="J7" t="n">
         <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>3.517939749213151</v>
+        <v>3.517939746769324</v>
       </c>
       <c r="L7" t="n">
-        <v>22.02544939518506</v>
+        <v>22.02544941102833</v>
       </c>
     </row>
     <row r="8">
@@ -732,33 +732,33 @@
         <v>0</v>
       </c>
       <c r="E8" t="n">
-        <v>9.277542385800684</v>
+        <v>9.277542385800682</v>
       </c>
       <c r="F8" t="n">
-        <v>5.21232960476861</v>
+        <v>5.212329604768589</v>
       </c>
       <c r="G8" t="n">
         <v>0</v>
       </c>
       <c r="H8" t="n">
-        <v>3.086528906612338</v>
+        <v>3.086528906879938</v>
       </c>
       <c r="I8" t="n">
-        <v>42.10156260324491</v>
+        <v>42.10156261211326</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>3.604599176807855</v>
+        <v>3.604599169038484</v>
       </c>
       <c r="L8" t="n">
-        <v>21.46928765764942</v>
+        <v>21.46928770458955</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>1.615375460547206e-11</v>
+        <v>4.771601926726869e-12</v>
       </c>
       <c r="B9" t="n">
         <v>0</v>
@@ -770,33 +770,33 @@
         <v>0</v>
       </c>
       <c r="E9" t="n">
-        <v>9.205474504005355</v>
+        <v>9.205474504005354</v>
       </c>
       <c r="F9" t="n">
-        <v>5.253250207385433</v>
+        <v>5.253250207385437</v>
       </c>
       <c r="G9" t="n">
         <v>0</v>
       </c>
       <c r="H9" t="n">
-        <v>3.156153512598828</v>
+        <v>3.156153997553547</v>
       </c>
       <c r="I9" t="n">
-        <v>40.9694764901717</v>
+        <v>40.96946516035371</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
       </c>
       <c r="K9" t="n">
-        <v>3.691630534726485</v>
+        <v>3.691630532625133</v>
       </c>
       <c r="L9" t="n">
-        <v>20.93900050172503</v>
+        <v>20.93900051358815</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>1.611868224115192e-11</v>
+        <v>4.757130086568783e-12</v>
       </c>
       <c r="B10" t="n">
         <v>0</v>
@@ -811,30 +811,30 @@
         <v>9.132927392258562</v>
       </c>
       <c r="F10" t="n">
-        <v>5.295097963471854</v>
+        <v>5.295097963471852</v>
       </c>
       <c r="G10" t="n">
         <v>0</v>
       </c>
       <c r="H10" t="n">
-        <v>3.226838708796441</v>
+        <v>3.226839002257657</v>
       </c>
       <c r="I10" t="n">
-        <v>39.88840949574709</v>
+        <v>39.88840321610132</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
       </c>
       <c r="K10" t="n">
-        <v>3.778985064195272</v>
+        <v>3.778985068429549</v>
       </c>
       <c r="L10" t="n">
-        <v>20.43306025874206</v>
+        <v>20.43306023696256</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>4.740829331029515e-12</v>
+        <v>1.607854903206587e-11</v>
       </c>
       <c r="B11" t="n">
         <v>0</v>
@@ -849,25 +849,25 @@
         <v>9.059911140154993</v>
       </c>
       <c r="F11" t="n">
-        <v>5.337895972019203</v>
+        <v>5.337895972019213</v>
       </c>
       <c r="G11" t="n">
         <v>0</v>
       </c>
       <c r="H11" t="n">
-        <v>3.298482028508494</v>
+        <v>3.298481770332996</v>
       </c>
       <c r="I11" t="n">
-        <v>38.85601511690004</v>
+        <v>38.85602027941138</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
       </c>
       <c r="K11" t="n">
-        <v>3.866615747698372</v>
+        <v>3.866615740128793</v>
       </c>
       <c r="L11" t="n">
-        <v>19.95004562846234</v>
+        <v>19.9500456629309</v>
       </c>
     </row>
     <row r="12">
@@ -884,28 +884,28 @@
         <v>0</v>
       </c>
       <c r="E12" t="n">
-        <v>8.986436060932464</v>
+        <v>8.986436060932469</v>
       </c>
       <c r="F12" t="n">
-        <v>5.381668059720168</v>
+        <v>5.38166805972018</v>
       </c>
       <c r="G12" t="n">
         <v>0</v>
       </c>
       <c r="H12" t="n">
-        <v>3.370986326462548</v>
+        <v>3.370986326460237</v>
       </c>
       <c r="I12" t="n">
-        <v>37.8699922225055</v>
+        <v>37.86999222242693</v>
       </c>
       <c r="J12" t="n">
         <v>0</v>
       </c>
       <c r="K12" t="n">
-        <v>3.954477138722531</v>
+        <v>3.954477139618122</v>
       </c>
       <c r="L12" t="n">
-        <v>19.48863399885695</v>
+        <v>19.48863399476637</v>
       </c>
     </row>
     <row r="13">
@@ -925,25 +925,25 @@
         <v>8.912512700048374</v>
       </c>
       <c r="F13" t="n">
-        <v>5.426438801725505</v>
+        <v>5.426438801725501</v>
       </c>
       <c r="G13" t="n">
         <v>0</v>
       </c>
       <c r="H13" t="n">
-        <v>3.444260067875105</v>
+        <v>3.444260067874878</v>
       </c>
       <c r="I13" t="n">
-        <v>36.92809202184588</v>
+        <v>36.92809202183857</v>
       </c>
       <c r="J13" t="n">
         <v>0</v>
       </c>
       <c r="K13" t="n">
-        <v>4.042525290505201</v>
+        <v>4.042525290504308</v>
       </c>
       <c r="L13" t="n">
-        <v>19.04759385653467</v>
+        <v>19.0475938565376</v>
       </c>
     </row>
     <row r="14">
@@ -960,33 +960,33 @@
         <v>0</v>
       </c>
       <c r="E14" t="n">
-        <v>8.838151844289545</v>
+        <v>8.838151844289541</v>
       </c>
       <c r="F14" t="n">
-        <v>5.47223354249082</v>
+        <v>5.472233542490808</v>
       </c>
       <c r="G14" t="n">
         <v>0</v>
       </c>
       <c r="H14" t="n">
-        <v>3.51821573641599</v>
+        <v>3.518216099303301</v>
       </c>
       <c r="I14" t="n">
-        <v>36.02815393731253</v>
+        <v>36.02814793334121</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
       </c>
       <c r="K14" t="n">
-        <v>4.130717623279303</v>
+        <v>4.130717622989087</v>
       </c>
       <c r="L14" t="n">
-        <v>18.62577808350046</v>
+        <v>18.62577808474621</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>1.586863780719597e-11</v>
+        <v>4.657786957480437e-12</v>
       </c>
       <c r="B15" t="n">
         <v>0</v>
@@ -998,33 +998,33 @@
         <v>0</v>
       </c>
       <c r="E15" t="n">
-        <v>8.763364531451209</v>
+        <v>8.763364531451213</v>
       </c>
       <c r="F15" t="n">
-        <v>5.519078416623445</v>
+        <v>5.519078416623477</v>
       </c>
       <c r="G15" t="n">
         <v>0</v>
       </c>
       <c r="H15" t="n">
-        <v>3.592771068345179</v>
+        <v>3.592771760862532</v>
       </c>
       <c r="I15" t="n">
-        <v>35.16808564140039</v>
+        <v>35.16807492260258</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
       </c>
       <c r="K15" t="n">
-        <v>4.219012847189298</v>
+        <v>4.219012847104465</v>
       </c>
       <c r="L15" t="n">
-        <v>18.22211753388449</v>
+        <v>18.22211753419642</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>4.632685396169775e-12</v>
+        <v>1.580413030208249e-11</v>
       </c>
       <c r="B16" t="n">
         <v>0</v>
@@ -1036,28 +1036,28 @@
         <v>0</v>
       </c>
       <c r="E16" t="n">
-        <v>8.688162060623027</v>
+        <v>8.688162060623023</v>
       </c>
       <c r="F16" t="n">
-        <v>5.567000369624424</v>
+        <v>5.567000369624425</v>
       </c>
       <c r="G16" t="n">
         <v>0</v>
       </c>
       <c r="H16" t="n">
-        <v>3.667848520867208</v>
+        <v>3.667848486320693</v>
       </c>
       <c r="I16" t="n">
-        <v>34.34587579881062</v>
+        <v>34.34587631889599</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
       </c>
       <c r="K16" t="n">
-        <v>4.307370868128792</v>
+        <v>4.307370868235205</v>
       </c>
       <c r="L16" t="n">
-        <v>17.83561520763794</v>
+        <v>17.83561520735162</v>
       </c>
     </row>
     <row r="17">
@@ -1074,28 +1074,28 @@
         <v>0</v>
       </c>
       <c r="E17" t="n">
-        <v>8.612556003123021</v>
+        <v>8.61255600312302</v>
       </c>
       <c r="F17" t="n">
-        <v>5.616027178402847</v>
+        <v>5.616027178402867</v>
       </c>
       <c r="G17" t="n">
         <v>0</v>
       </c>
       <c r="H17" t="n">
-        <v>3.743371842357093</v>
+        <v>3.743371850910907</v>
       </c>
       <c r="I17" t="n">
-        <v>33.55964164941631</v>
+        <v>33.55964152193394</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
       </c>
       <c r="K17" t="n">
-        <v>4.395752719513276</v>
+        <v>4.395752719586175</v>
       </c>
       <c r="L17" t="n">
-        <v>17.46534079616599</v>
+        <v>17.46534079596972</v>
       </c>
     </row>
     <row r="18">
@@ -1112,28 +1112,28 @@
         <v>0</v>
       </c>
       <c r="E18" t="n">
-        <v>8.53655821412304</v>
+        <v>8.536558214123042</v>
       </c>
       <c r="F18" t="n">
-        <v>5.666187471420748</v>
+        <v>5.666187471420737</v>
       </c>
       <c r="G18" t="n">
         <v>0</v>
       </c>
       <c r="H18" t="n">
-        <v>3.819270954890266</v>
+        <v>3.819270939230787</v>
       </c>
       <c r="I18" t="n">
-        <v>32.80755260969687</v>
+        <v>32.80755282507882</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
       </c>
       <c r="K18" t="n">
-        <v>4.484120483205356</v>
+        <v>4.484120482968211</v>
       </c>
       <c r="L18" t="n">
-        <v>17.11042571753297</v>
+        <v>17.11042571830219</v>
       </c>
     </row>
     <row r="19">
@@ -1150,28 +1150,28 @@
         <v>0</v>
       </c>
       <c r="E19" t="n">
-        <v>8.460180845012575</v>
+        <v>8.460180845012571</v>
       </c>
       <c r="F19" t="n">
-        <v>5.717510748302256</v>
+        <v>5.717510748302229</v>
       </c>
       <c r="G19" t="n">
         <v>0</v>
       </c>
       <c r="H19" t="n">
-        <v>3.895478511670832</v>
+        <v>3.895478513272141</v>
       </c>
       <c r="I19" t="n">
-        <v>32.08787906372914</v>
+        <v>32.08787904216323</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
       </c>
       <c r="K19" t="n">
-        <v>4.57243723482427</v>
+        <v>4.572437234826272</v>
       </c>
       <c r="L19" t="n">
-        <v>16.77005847775977</v>
+        <v>16.77005847775497</v>
       </c>
     </row>
     <row r="20">
@@ -1188,28 +1188,28 @@
         <v>0</v>
       </c>
       <c r="E20" t="n">
-        <v>8.383436356550771</v>
+        <v>8.383436356550773</v>
       </c>
       <c r="F20" t="n">
-        <v>5.770027398716886</v>
+        <v>5.770027398716848</v>
       </c>
       <c r="G20" t="n">
         <v>0</v>
       </c>
       <c r="H20" t="n">
-        <v>3.971930492949263</v>
+        <v>3.971930492951591</v>
       </c>
       <c r="I20" t="n">
-        <v>31.39897843768169</v>
+        <v>31.39897843765132</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
       </c>
       <c r="K20" t="n">
-        <v>4.660666984006019</v>
+        <v>4.660666984094037</v>
       </c>
       <c r="L20" t="n">
-        <v>16.44348043496179</v>
+        <v>16.44348043465661</v>
       </c>
     </row>
     <row r="21">
@@ -1229,25 +1229,25 @@
         <v>8.30633753286056</v>
       </c>
       <c r="F21" t="n">
-        <v>5.823768720316768</v>
+        <v>5.823768720316807</v>
       </c>
       <c r="G21" t="n">
         <v>0</v>
       </c>
       <c r="H21" t="n">
-        <v>4.048565931560494</v>
+        <v>4.048565932038013</v>
       </c>
       <c r="I21" t="n">
-        <v>30.73929403167219</v>
+        <v>30.73929402712836</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
       </c>
       <c r="K21" t="n">
-        <v>4.748774623882341</v>
+        <v>4.74877462388235</v>
       </c>
       <c r="L21" t="n">
-        <v>16.12998188670693</v>
+        <v>16.12998188670748</v>
       </c>
     </row>
     <row r="22">
@@ -1264,28 +1264,28 @@
         <v>0</v>
       </c>
       <c r="E22" t="n">
-        <v>8.228897496322057</v>
+        <v>8.228897496322054</v>
       </c>
       <c r="F22" t="n">
-        <v>5.878766935474659</v>
+        <v>5.8787669354746</v>
       </c>
       <c r="G22" t="n">
         <v>0</v>
       </c>
       <c r="H22" t="n">
-        <v>4.125326703088624</v>
+        <v>4.125326786189955</v>
       </c>
       <c r="I22" t="n">
-        <v>30.10735244292725</v>
+        <v>30.10735151929713</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
       </c>
       <c r="K22" t="n">
-        <v>4.836725883699709</v>
+        <v>4.836725883699718</v>
       </c>
       <c r="L22" t="n">
-        <v>15.82889847330952</v>
+        <v>15.82889847330988</v>
       </c>
     </row>
     <row r="23">
@@ -1305,25 +1305,25 @@
         <v>8.151129723426582</v>
       </c>
       <c r="F23" t="n">
-        <v>5.935055206531888</v>
+        <v>5.935055206531922</v>
       </c>
       <c r="G23" t="n">
         <v>0</v>
       </c>
       <c r="H23" t="n">
-        <v>4.202157642877698</v>
+        <v>4.202157636599373</v>
       </c>
       <c r="I23" t="n">
-        <v>29.50175727088129</v>
+        <v>29.50175733780496</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
       </c>
       <c r="K23" t="n">
-        <v>4.924487287408027</v>
+        <v>4.924487287391338</v>
       </c>
       <c r="L23" t="n">
-        <v>15.53960786203673</v>
+        <v>15.53960786209036</v>
       </c>
     </row>
     <row r="24">
@@ -1340,28 +1340,28 @@
         <v>0</v>
       </c>
       <c r="E24" t="n">
-        <v>8.073048061657222</v>
+        <v>8.073048061657223</v>
       </c>
       <c r="F24" t="n">
-        <v>5.992667649224881</v>
+        <v>5.992667649224857</v>
       </c>
       <c r="G24" t="n">
         <v>0</v>
       </c>
       <c r="H24" t="n">
-        <v>4.279005677896204</v>
+        <v>4.279005674422212</v>
       </c>
       <c r="I24" t="n">
-        <v>28.92119351470508</v>
+        <v>28.92119355072527</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
       </c>
       <c r="K24" t="n">
-        <v>5.01202611496033</v>
+        <v>5.012026114971531</v>
       </c>
       <c r="L24" t="n">
-        <v>15.261526698943</v>
+        <v>15.26152669890068</v>
       </c>
     </row>
     <row r="25">
@@ -1378,28 +1378,28 @@
         <v>0</v>
       </c>
       <c r="E25" t="n">
-        <v>7.994666747465937</v>
+        <v>7.994666747465935</v>
       </c>
       <c r="F25" t="n">
-        <v>6.051639343908534</v>
+        <v>6.051639343908493</v>
       </c>
       <c r="G25" t="n">
         <v>0</v>
       </c>
       <c r="H25" t="n">
-        <v>4.355820388122174</v>
+        <v>4.355820387296889</v>
       </c>
       <c r="I25" t="n">
-        <v>28.36441613992006</v>
+        <v>28.3644161481989</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
       </c>
       <c r="K25" t="n">
-        <v>5.099310367626974</v>
+        <v>5.099310367635607</v>
       </c>
       <c r="L25" t="n">
-        <v>14.99410780128293</v>
+        <v>14.99410780125049</v>
       </c>
     </row>
     <row r="26">
@@ -1416,28 +1416,28 @@
         <v>0</v>
       </c>
       <c r="E26" t="n">
-        <v>7.916000425422451</v>
+        <v>7.916000425422448</v>
       </c>
       <c r="F26" t="n">
-        <v>6.112006344143049</v>
+        <v>6.112006344143065</v>
       </c>
       <c r="G26" t="n">
         <v>0</v>
       </c>
       <c r="H26" t="n">
-        <v>4.432553509000461</v>
+        <v>4.432553505047626</v>
       </c>
       <c r="I26" t="n">
-        <v>27.83025045929205</v>
+        <v>27.83025049707959</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
       </c>
       <c r="K26" t="n">
-        <v>5.186308736296866</v>
+        <v>5.186308736294465</v>
       </c>
       <c r="L26" t="n">
-        <v>14.73683757299216</v>
+        <v>14.73683757300254</v>
       </c>
     </row>
     <row r="27">
@@ -1454,28 +1454,28 @@
         <v>0</v>
       </c>
       <c r="E27" t="n">
-        <v>7.837064168615009</v>
+        <v>7.837064168615004</v>
       </c>
       <c r="F27" t="n">
-        <v>6.173805682149561</v>
+        <v>6.173805682149499</v>
       </c>
       <c r="G27" t="n">
         <v>0</v>
       </c>
       <c r="H27" t="n">
-        <v>4.509158846922761</v>
+        <v>4.509158846994181</v>
       </c>
       <c r="I27" t="n">
-        <v>27.31758801190363</v>
+        <v>27.31758801123689</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
       </c>
       <c r="K27" t="n">
-        <v>5.272990572696988</v>
+        <v>5.27299057269192</v>
       </c>
       <c r="L27" t="n">
-        <v>14.48923362418039</v>
+        <v>14.48923362419971</v>
       </c>
     </row>
     <row r="28">
@@ -1492,28 +1492,28 @@
         <v>0</v>
       </c>
       <c r="E28" t="n">
-        <v>7.757873500388881</v>
+        <v>7.757873500388883</v>
       </c>
       <c r="F28" t="n">
-        <v>6.23707537056989</v>
+        <v>6.237075370569893</v>
       </c>
       <c r="G28" t="n">
         <v>0</v>
       </c>
       <c r="H28" t="n">
-        <v>4.585592154086891</v>
+        <v>4.585592156148826</v>
       </c>
       <c r="I28" t="n">
-        <v>26.82538304788634</v>
+        <v>26.82538302991853</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
       </c>
       <c r="K28" t="n">
-        <v>5.359325863194083</v>
+        <v>5.359325863191454</v>
       </c>
       <c r="L28" t="n">
-        <v>14.25084257790937</v>
+        <v>14.25084257792133</v>
       </c>
     </row>
     <row r="29">
@@ -1530,28 +1530,28 @@
         <v>0</v>
       </c>
       <c r="E29" t="n">
-        <v>7.678444417513585</v>
+        <v>7.678444417513592</v>
       </c>
       <c r="F29" t="n">
-        <v>6.301854399891663</v>
+        <v>6.301854399891735</v>
       </c>
       <c r="G29" t="n">
         <v>0</v>
       </c>
       <c r="H29" t="n">
-        <v>4.661811018407692</v>
+        <v>4.661811017948281</v>
       </c>
       <c r="I29" t="n">
-        <v>26.35264904849958</v>
+        <v>26.35264905238753</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
       </c>
       <c r="K29" t="n">
-        <v>5.445285204849962</v>
+        <v>5.445285204849969</v>
       </c>
       <c r="L29" t="n">
-        <v>14.02123804899962</v>
+        <v>14.02123804899875</v>
       </c>
     </row>
     <row r="30">
@@ -1571,25 +1571,25 @@
         <v>7.598793414876552</v>
       </c>
       <c r="F30" t="n">
-        <v>6.368182730810259</v>
+        <v>6.368182730810237</v>
       </c>
       <c r="G30" t="n">
         <v>0</v>
       </c>
       <c r="H30" t="n">
-        <v>4.737774732483755</v>
+        <v>4.737774732130628</v>
       </c>
       <c r="I30" t="n">
-        <v>25.89845560569227</v>
+        <v>25.8984556086091</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
       </c>
       <c r="K30" t="n">
-        <v>5.530839783609424</v>
+        <v>5.530839783609429</v>
       </c>
       <c r="L30" t="n">
-        <v>13.80001878022639</v>
+        <v>13.8000187802265</v>
       </c>
     </row>
     <row r="31">
@@ -1609,30 +1609,30 @@
         <v>7.518937511806604</v>
       </c>
       <c r="F31" t="n">
-        <v>6.436101280702517</v>
+        <v>6.436101280702531</v>
       </c>
       <c r="G31" t="n">
         <v>0</v>
       </c>
       <c r="H31" t="n">
-        <v>4.813444211282237</v>
+        <v>4.813444211286638</v>
       </c>
       <c r="I31" t="n">
-        <v>25.46192506409847</v>
+        <v>25.46192506406228</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
       </c>
       <c r="K31" t="n">
-        <v>5.615961354369177</v>
+        <v>5.615961354369178</v>
       </c>
       <c r="L31" t="n">
-        <v>13.58680692298745</v>
+        <v>13.58680692298771</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>1.418159695979697e-11</v>
+        <v>8.937688241234482e-12</v>
       </c>
       <c r="B32" t="n">
         <v>0</v>
@@ -1644,33 +1644,33 @@
         <v>0</v>
       </c>
       <c r="E32" t="n">
-        <v>7.43889428013757</v>
+        <v>7.438894280137573</v>
       </c>
       <c r="F32" t="n">
-        <v>6.505651903280182</v>
+        <v>6.505651903280183</v>
       </c>
       <c r="G32" t="n">
         <v>0</v>
       </c>
       <c r="H32" t="n">
-        <v>4.888781886760984</v>
+        <v>4.888781886761088</v>
       </c>
       <c r="I32" t="n">
-        <v>25.04222956274659</v>
+        <v>25.04222956274972</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
       </c>
       <c r="K32" t="n">
-        <v>5.700622222755028</v>
+        <v>5.70062222275502</v>
       </c>
       <c r="L32" t="n">
-        <v>13.38124645038788</v>
+        <v>13.3812464503874</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>0.2416149156737015</v>
+        <v>0.241614915920489</v>
       </c>
       <c r="B33" t="n">
         <v>0</v>
@@ -1682,33 +1682,33 @@
         <v>0</v>
       </c>
       <c r="E33" t="n">
-        <v>7.358681874128892</v>
+        <v>7.358681874128894</v>
       </c>
       <c r="F33" t="n">
-        <v>6.576877360362939</v>
+        <v>6.576877360362941</v>
       </c>
       <c r="G33" t="n">
         <v>0</v>
       </c>
       <c r="H33" t="n">
-        <v>4.960086384449329</v>
+        <v>4.960086384437963</v>
       </c>
       <c r="I33" t="n">
-        <v>24.65800819910117</v>
+        <v>24.6580081992406</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
       </c>
       <c r="K33" t="n">
-        <v>5.784795228444019</v>
+        <v>5.784795228443813</v>
       </c>
       <c r="L33" t="n">
-        <v>13.18300169178787</v>
+        <v>13.18300169179237</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>0.545486432314442</v>
+        <v>0.5454864322902875</v>
       </c>
       <c r="B34" t="n">
         <v>0</v>
@@ -1720,33 +1720,33 @@
         <v>0</v>
       </c>
       <c r="E34" t="n">
-        <v>7.278319062367192</v>
+        <v>7.278319062367198</v>
       </c>
       <c r="F34" t="n">
-        <v>6.649821284579757</v>
+        <v>6.649821284579734</v>
       </c>
       <c r="G34" t="n">
         <v>0</v>
       </c>
       <c r="H34" t="n">
-        <v>5.02997695411799</v>
+        <v>5.029976954118224</v>
       </c>
       <c r="I34" t="n">
-        <v>24.29307441699436</v>
+        <v>24.29307441699305</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
       </c>
       <c r="K34" t="n">
-        <v>5.868453729884763</v>
+        <v>5.868453729884766</v>
       </c>
       <c r="L34" t="n">
-        <v>12.9917559787475</v>
+        <v>12.99175597874675</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>0.8714397698282672</v>
+        <v>0.8714397699293456</v>
       </c>
       <c r="B35" t="n">
         <v>0</v>
@@ -1761,30 +1761,30 @@
         <v>7.197825261779796</v>
       </c>
       <c r="F35" t="n">
-        <v>6.724528131648263</v>
+        <v>6.724528131648237</v>
       </c>
       <c r="G35" t="n">
         <v>0</v>
       </c>
       <c r="H35" t="n">
-        <v>5.099017878523849</v>
+        <v>5.099017878520635</v>
       </c>
       <c r="I35" t="n">
-        <v>23.94338537308727</v>
+        <v>23.94338537308721</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
       </c>
       <c r="K35" t="n">
-        <v>5.951571590283761</v>
+        <v>5.951571590284007</v>
       </c>
       <c r="L35" t="n">
-        <v>12.80721039317958</v>
+        <v>12.80721039317575</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>1.220056913693688</v>
+        <v>1.220056913541201</v>
       </c>
       <c r="B36" t="n">
         <v>0</v>
@@ -1796,33 +1796,33 @@
         <v>0</v>
       </c>
       <c r="E36" t="n">
-        <v>7.117220573898448</v>
+        <v>7.11722057389845</v>
       </c>
       <c r="F36" t="n">
-        <v>6.80104312071458</v>
+        <v>6.801043120714596</v>
       </c>
       <c r="G36" t="n">
         <v>0</v>
       </c>
       <c r="H36" t="n">
-        <v>5.167161373423991</v>
+        <v>5.167161373426362</v>
       </c>
       <c r="I36" t="n">
-        <v>23.60829563425076</v>
+        <v>23.60829563424215</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
       </c>
       <c r="K36" t="n">
-        <v>6.034123164740941</v>
+        <v>6.034123164740935</v>
       </c>
       <c r="L36" t="n">
-        <v>12.62908260930837</v>
+        <v>12.6290826093082</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>1.623790945734489</v>
+        <v>1.623790945521175</v>
       </c>
       <c r="B37" t="n">
         <v>0</v>
@@ -1834,33 +1834,33 @@
         <v>0</v>
       </c>
       <c r="E37" t="n">
-        <v>7.036525823518714</v>
+        <v>7.036525823518708</v>
       </c>
       <c r="F37" t="n">
-        <v>6.879412161042477</v>
+        <v>6.879412161042447</v>
       </c>
       <c r="G37" t="n">
         <v>0</v>
       </c>
       <c r="H37" t="n">
-        <v>5.23436232746914</v>
+        <v>5.234362327483366</v>
       </c>
       <c r="I37" t="n">
-        <v>23.28719013934224</v>
+        <v>23.28719013922633</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
       </c>
       <c r="K37" t="n">
-        <v>6.114834605629501</v>
+        <v>6.114834605629484</v>
       </c>
       <c r="L37" t="n">
-        <v>12.45969049902879</v>
+        <v>12.45969049902903</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>2.186736238782685</v>
+        <v>2.186736238823471</v>
       </c>
       <c r="B38" t="n">
         <v>0</v>
@@ -1872,33 +1872,33 @@
         <v>0</v>
       </c>
       <c r="E38" t="n">
-        <v>6.955762599907265</v>
+        <v>6.955762599907269</v>
       </c>
       <c r="F38" t="n">
-        <v>6.959681763129194</v>
+        <v>6.959681763129237</v>
       </c>
       <c r="G38" t="n">
         <v>0</v>
       </c>
       <c r="H38" t="n">
-        <v>5.300578531506626</v>
+        <v>5.300578531505893</v>
       </c>
       <c r="I38" t="n">
-        <v>22.97948170839178</v>
+        <v>22.97948170839738</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
       </c>
       <c r="K38" t="n">
-        <v>6.18958445574463</v>
+        <v>6.189584455744591</v>
       </c>
       <c r="L38" t="n">
-        <v>12.30684554192779</v>
+        <v>12.30684554192704</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>2.782187956903099</v>
+        <v>2.782187956015926</v>
       </c>
       <c r="B39" t="n">
         <v>0</v>
@@ -1910,33 +1910,33 @@
         <v>0</v>
       </c>
       <c r="E39" t="n">
-        <v>6.87495330071666</v>
+        <v>6.874953300716663</v>
       </c>
       <c r="F39" t="n">
-        <v>7.041898932091645</v>
+        <v>7.041898932091689</v>
       </c>
       <c r="G39" t="n">
         <v>0</v>
       </c>
       <c r="H39" t="n">
-        <v>5.365770894385467</v>
+        <v>5.365770894360369</v>
       </c>
       <c r="I39" t="n">
-        <v>22.68460880172402</v>
+        <v>22.68460880226144</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
       </c>
       <c r="K39" t="n">
-        <v>6.263269000128879</v>
+        <v>6.263269000125094</v>
       </c>
       <c r="L39" t="n">
-        <v>12.15983351180069</v>
+        <v>12.15983351180907</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>3.41023342062372</v>
+        <v>3.410233420704634</v>
       </c>
       <c r="B40" t="n">
         <v>0</v>
@@ -1948,33 +1948,33 @@
         <v>0</v>
       </c>
       <c r="E40" t="n">
-        <v>6.794121178772661</v>
+        <v>6.794121178772662</v>
       </c>
       <c r="F40" t="n">
-        <v>7.126111040903412</v>
+        <v>7.126111040903421</v>
       </c>
       <c r="G40" t="n">
         <v>0</v>
       </c>
       <c r="H40" t="n">
-        <v>5.429903636838494</v>
+        <v>5.429903636832283</v>
       </c>
       <c r="I40" t="n">
-        <v>22.40203352792259</v>
+        <v>22.40203352797043</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
       </c>
       <c r="K40" t="n">
-        <v>6.335855434439938</v>
+        <v>6.335855434439985</v>
       </c>
       <c r="L40" t="n">
-        <v>12.01843247146544</v>
+        <v>12.01843247146348</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>4.070748177713827</v>
+        <v>4.070748177683578</v>
       </c>
       <c r="B41" t="n">
         <v>0</v>
@@ -1986,16 +1986,16 @@
         <v>0</v>
       </c>
       <c r="E41" t="n">
-        <v>6.713290391905609</v>
+        <v>6.713290391905606</v>
       </c>
       <c r="F41" t="n">
-        <v>7.212365680779611</v>
+        <v>7.212365680779768</v>
       </c>
       <c r="G41" t="n">
         <v>0</v>
       </c>
       <c r="H41" t="n">
-        <v>5.492944454476768</v>
+        <v>5.492944454476767</v>
       </c>
       <c r="I41" t="n">
         <v>22.13123990479459</v>
@@ -2004,15 +2004,15 @@
         <v>0</v>
       </c>
       <c r="K41" t="n">
-        <v>6.407313127950522</v>
+        <v>6.407313127951696</v>
       </c>
       <c r="L41" t="n">
-        <v>11.88242981402953</v>
+        <v>11.88242981403002</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>4.763381315069029</v>
+        <v>4.763381315114865</v>
       </c>
       <c r="B42" t="n">
         <v>0</v>
@@ -2024,33 +2024,33 @@
         <v>0</v>
       </c>
       <c r="E42" t="n">
-        <v>6.632486056001337</v>
+        <v>6.63248605600134</v>
       </c>
       <c r="F42" t="n">
-        <v>7.300710485690455</v>
+        <v>7.300710485690381</v>
       </c>
       <c r="G42" t="n">
         <v>0</v>
       </c>
       <c r="H42" t="n">
-        <v>5.554864643466562</v>
+        <v>5.554864643466563</v>
       </c>
       <c r="I42" t="n">
-        <v>21.87173236185276</v>
+        <v>21.87173236185275</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
       </c>
       <c r="K42" t="n">
-        <v>6.477613773440733</v>
+        <v>6.477613773438917</v>
       </c>
       <c r="L42" t="n">
-        <v>11.75162156798588</v>
+        <v>11.75162156798551</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>5.487543079383201</v>
+        <v>5.487543079605482</v>
       </c>
       <c r="B43" t="n">
         <v>0</v>
@@ -2065,30 +2065,30 @@
         <v>6.551734301450765</v>
       </c>
       <c r="F43" t="n">
-        <v>7.391192927639299</v>
+        <v>7.391192927639349</v>
       </c>
       <c r="G43" t="n">
         <v>0</v>
       </c>
       <c r="H43" t="n">
-        <v>5.61563918274426</v>
+        <v>5.615639182744262</v>
       </c>
       <c r="I43" t="n">
-        <v>21.62303447646442</v>
+        <v>21.6230344764644</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
       </c>
       <c r="K43" t="n">
-        <v>6.546731516664598</v>
+        <v>6.546731516644604</v>
       </c>
       <c r="L43" t="n">
-        <v>11.62581178152684</v>
+        <v>11.62581178154423</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>6.242395040274257</v>
+        <v>6.242395040237359</v>
       </c>
       <c r="B44" t="n">
         <v>0</v>
@@ -2100,33 +2100,33 @@
         <v>0</v>
       </c>
       <c r="E44" t="n">
-        <v>6.471062333178517</v>
+        <v>6.471062333178566</v>
       </c>
       <c r="F44" t="n">
-        <v>7.483860078972318</v>
+        <v>7.483860078971662</v>
       </c>
       <c r="G44" t="n">
         <v>0</v>
       </c>
       <c r="H44" t="n">
-        <v>5.675246769240776</v>
+        <v>5.675246769240775</v>
       </c>
       <c r="I44" t="n">
-        <v>21.38468792566679</v>
+        <v>21.38468792566678</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
       </c>
       <c r="K44" t="n">
-        <v>6.614643061932762</v>
+        <v>6.614643061934336</v>
       </c>
       <c r="L44" t="n">
-        <v>11.50481198234194</v>
+        <v>11.50481198234488</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>7.026842960152629</v>
+        <v>7.026842960284902</v>
       </c>
       <c r="B45" t="n">
         <v>0</v>
@@ -2138,16 +2138,16 @@
         <v>0</v>
       </c>
       <c r="E45" t="n">
-        <v>6.390498494430958</v>
+        <v>6.390498494430956</v>
       </c>
       <c r="F45" t="n">
-        <v>7.578758337568981</v>
+        <v>7.578758337568939</v>
       </c>
       <c r="G45" t="n">
         <v>0</v>
       </c>
       <c r="H45" t="n">
-        <v>5.733669804229781</v>
+        <v>5.733669804229779</v>
       </c>
       <c r="I45" t="n">
         <v>21.15625163373845</v>
@@ -2156,15 +2156,15 @@
         <v>0</v>
       </c>
       <c r="K45" t="n">
-        <v>6.681327751021728</v>
+        <v>6.681327750997908</v>
       </c>
       <c r="L45" t="n">
-        <v>11.38844070853454</v>
+        <v>11.38844070855768</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>7.839532457618419</v>
+        <v>7.839532457461945</v>
       </c>
       <c r="B46" t="n">
         <v>0</v>
@@ -2176,16 +2176,16 @@
         <v>0</v>
       </c>
       <c r="E46" t="n">
-        <v>6.310072334498395</v>
+        <v>6.31007233449836</v>
       </c>
       <c r="F46" t="n">
-        <v>7.675933110356115</v>
+        <v>7.675933110356645</v>
       </c>
       <c r="G46" t="n">
         <v>0</v>
       </c>
       <c r="H46" t="n">
-        <v>5.79089433104874</v>
+        <v>5.790894331048739</v>
       </c>
       <c r="I46" t="n">
         <v>20.93730109162667</v>
@@ -2194,15 +2194,15 @@
         <v>0</v>
       </c>
       <c r="K46" t="n">
-        <v>6.746767613261202</v>
+        <v>6.746767613246317</v>
       </c>
       <c r="L46" t="n">
-        <v>11.27652310557143</v>
+        <v>11.27652310559494</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>8.678847465526299</v>
+        <v>8.678847466207028</v>
       </c>
       <c r="B47" t="n">
         <v>0</v>
@@ -2214,33 +2214,33 @@
         <v>0</v>
       </c>
       <c r="E47" t="n">
-        <v>6.22981468054239</v>
+        <v>6.229814680542417</v>
       </c>
       <c r="F47" t="n">
-        <v>7.77542845008473</v>
+        <v>7.775428450084272</v>
       </c>
       <c r="G47" t="n">
         <v>0</v>
       </c>
       <c r="H47" t="n">
-        <v>5.846909926361429</v>
+        <v>5.84690992636139</v>
       </c>
       <c r="I47" t="n">
-        <v>20.72742782215026</v>
+        <v>20.72742782215037</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
       </c>
       <c r="K47" t="n">
-        <v>6.810947385913788</v>
+        <v>6.810947385861487</v>
       </c>
       <c r="L47" t="n">
-        <v>11.16889058376146</v>
+        <v>11.16889058381805</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>-3.538937443682084</v>
+        <v>-3.538937443681989</v>
       </c>
       <c r="B48" t="n">
         <v>0</v>
@@ -2252,28 +2252,28 @@
         <v>0.1</v>
       </c>
       <c r="E48" t="n">
-        <v>9.489621785789449</v>
+        <v>9.489621785789451</v>
       </c>
       <c r="F48" t="n">
-        <v>5.095529895621963</v>
+        <v>5.095529895621962</v>
       </c>
       <c r="G48" t="n">
         <v>0</v>
       </c>
       <c r="H48" t="n">
-        <v>2.697430303624302</v>
+        <v>2.697430126586939</v>
       </c>
       <c r="I48" t="n">
-        <v>50.09930096397862</v>
+        <v>50.09929523907</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
       </c>
       <c r="K48" t="n">
-        <v>3.092067073281464</v>
+        <v>3.092067197337133</v>
       </c>
       <c r="L48" t="n">
-        <v>25.25641123572337</v>
+        <v>25.25641030724787</v>
       </c>
     </row>
     <row r="49">
@@ -2293,30 +2293,30 @@
         <v>9.334823541325351</v>
       </c>
       <c r="F49" t="n">
-        <v>5.180257545197659</v>
+        <v>5.18025754519766</v>
       </c>
       <c r="G49" t="n">
         <v>0</v>
       </c>
       <c r="H49" t="n">
-        <v>2.697430405444766</v>
+        <v>2.697430397701317</v>
       </c>
       <c r="I49" t="n">
-        <v>50.09930403406669</v>
+        <v>50.09930382112732</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
       </c>
       <c r="K49" t="n">
-        <v>3.09206716885968</v>
+        <v>3.09206729904317</v>
       </c>
       <c r="L49" t="n">
-        <v>25.25641047059553</v>
+        <v>25.25640955378933</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>-10.4495882656387</v>
+        <v>-10.44958826563855</v>
       </c>
       <c r="B50" t="n">
         <v>0</v>
@@ -2337,24 +2337,24 @@
         <v>0</v>
       </c>
       <c r="H50" t="n">
-        <v>2.697430408004275</v>
+        <v>2.697430403631818</v>
       </c>
       <c r="I50" t="n">
-        <v>50.09930410377088</v>
+        <v>50.09930398475608</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
       </c>
       <c r="K50" t="n">
-        <v>3.09206707396437</v>
+        <v>3.092067333040089</v>
       </c>
       <c r="L50" t="n">
-        <v>25.25641123187271</v>
+        <v>25.25640925531289</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>-13.82660796280592</v>
+        <v>-13.82660796280627</v>
       </c>
       <c r="B51" t="n">
         <v>0</v>
@@ -2366,33 +2366,33 @@
         <v>0.4</v>
       </c>
       <c r="E51" t="n">
-        <v>9.111589061977844</v>
+        <v>9.111589061977837</v>
       </c>
       <c r="F51" t="n">
-        <v>5.307534045233507</v>
+        <v>5.307534045233512</v>
       </c>
       <c r="G51" t="n">
         <v>0</v>
       </c>
       <c r="H51" t="n">
-        <v>2.697430287309031</v>
+        <v>2.697430393490434</v>
       </c>
       <c r="I51" t="n">
-        <v>50.09930053925707</v>
+        <v>50.09930370514866</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
       </c>
       <c r="K51" t="n">
-        <v>3.092067364570417</v>
+        <v>3.092067092660014</v>
       </c>
       <c r="L51" t="n">
-        <v>25.25640899724515</v>
+        <v>25.25641112531996</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>-30.14449406562217</v>
+        <v>-30.144494065624</v>
       </c>
       <c r="B52" t="n">
         <v>0</v>
@@ -2404,33 +2404,33 @@
         <v>0.9</v>
       </c>
       <c r="E52" t="n">
-        <v>8.771892049491537</v>
+        <v>8.771892049491504</v>
       </c>
       <c r="F52" t="n">
-        <v>5.513696461027553</v>
+        <v>5.513696461027649</v>
       </c>
       <c r="G52" t="n">
         <v>0</v>
       </c>
       <c r="H52" t="n">
-        <v>2.697430374105616</v>
+        <v>2.697430306331713</v>
       </c>
       <c r="I52" t="n">
-        <v>50.09930313708208</v>
+        <v>50.0993010591862</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
       </c>
       <c r="K52" t="n">
-        <v>3.092067061509431</v>
+        <v>3.092067080735457</v>
       </c>
       <c r="L52" t="n">
-        <v>25.25641130165692</v>
+        <v>25.25641119353691</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>2.102152324627045</v>
+        <v>2.102152324628775</v>
       </c>
       <c r="B53" t="n">
         <v>0</v>
@@ -2442,33 +2442,33 @@
         <v>0</v>
       </c>
       <c r="E53" t="n">
-        <v>9.699347069291402</v>
+        <v>9.699347069291424</v>
       </c>
       <c r="F53" t="n">
-        <v>4.985069224042757</v>
+        <v>4.985069224042792</v>
       </c>
       <c r="G53" t="n">
         <v>0.1</v>
       </c>
       <c r="H53" t="n">
-        <v>2.683989998574897</v>
+        <v>2.683989998574929</v>
       </c>
       <c r="I53" t="n">
-        <v>50.44368285083736</v>
+        <v>50.44368285083699</v>
       </c>
       <c r="J53" t="n">
         <v>0.1082177012392873</v>
       </c>
       <c r="K53" t="n">
-        <v>3.070883992165573</v>
+        <v>3.070883992165514</v>
       </c>
       <c r="L53" t="n">
-        <v>25.44301119189033</v>
+        <v>25.4430111918928</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>3.839251524594191</v>
+        <v>3.839251524612708</v>
       </c>
       <c r="B54" t="n">
         <v>0</v>
@@ -2483,30 +2483,30 @@
         <v>9.69934706929139</v>
       </c>
       <c r="F54" t="n">
-        <v>4.98506922404277</v>
+        <v>4.985069224042768</v>
       </c>
       <c r="G54" t="n">
         <v>0.2</v>
       </c>
       <c r="H54" t="n">
-        <v>2.672349906452419</v>
+        <v>2.672349906452221</v>
       </c>
       <c r="I54" t="n">
-        <v>50.74679737773776</v>
+        <v>50.74679737773828</v>
       </c>
       <c r="J54" t="n">
         <v>0.1861872028258322</v>
       </c>
       <c r="K54" t="n">
-        <v>3.056952118327394</v>
+        <v>3.056952118327383</v>
       </c>
       <c r="L54" t="n">
-        <v>25.56730559354525</v>
+        <v>25.56730559354667</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>5.484213403585476</v>
+        <v>5.484213403597066</v>
       </c>
       <c r="B55" t="n">
         <v>0</v>
@@ -2518,33 +2518,33 @@
         <v>0</v>
       </c>
       <c r="E55" t="n">
-        <v>9.699347069291393</v>
+        <v>9.699347069291395</v>
       </c>
       <c r="F55" t="n">
-        <v>4.985069224042768</v>
+        <v>4.985069224042769</v>
       </c>
       <c r="G55" t="n">
         <v>0.3</v>
       </c>
       <c r="H55" t="n">
-        <v>2.662052797422557</v>
+        <v>2.662052797422408</v>
       </c>
       <c r="I55" t="n">
-        <v>51.01881471155225</v>
+        <v>51.01881471155315</v>
       </c>
       <c r="J55" t="n">
         <v>0.2724584114361717</v>
       </c>
       <c r="K55" t="n">
-        <v>3.042562690630358</v>
+        <v>3.042562690630355</v>
       </c>
       <c r="L55" t="n">
-        <v>25.69701456619961</v>
+        <v>25.69701456619964</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>7.078163436590854</v>
+        <v>7.078163436514869</v>
       </c>
       <c r="B56" t="n">
         <v>0</v>
@@ -2556,33 +2556,33 @@
         <v>0</v>
       </c>
       <c r="E56" t="n">
-        <v>9.699347069291413</v>
+        <v>9.699347069291395</v>
       </c>
       <c r="F56" t="n">
-        <v>4.985069224042746</v>
+        <v>4.985069224042767</v>
       </c>
       <c r="G56" t="n">
         <v>0.4</v>
       </c>
       <c r="H56" t="n">
-        <v>2.652798813905597</v>
+        <v>2.652798813906231</v>
       </c>
       <c r="I56" t="n">
-        <v>51.26646119328322</v>
+        <v>51.26646119326673</v>
       </c>
       <c r="J56" t="n">
         <v>0.3709916581317118</v>
       </c>
       <c r="K56" t="n">
-        <v>3.027211975723692</v>
+        <v>3.027211975723695</v>
       </c>
       <c r="L56" t="n">
-        <v>25.83690649497285</v>
+        <v>25.83690649497283</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>14.09452555419575</v>
+        <v>14.09452555419547</v>
       </c>
       <c r="B57" t="n">
         <v>0</v>
@@ -2594,25 +2594,25 @@
         <v>0</v>
       </c>
       <c r="E57" t="n">
-        <v>9.699347069291418</v>
+        <v>9.699347069291392</v>
       </c>
       <c r="F57" t="n">
-        <v>4.985069224042745</v>
+        <v>4.985069224042769</v>
       </c>
       <c r="G57" t="n">
         <v>0.9</v>
       </c>
       <c r="H57" t="n">
-        <v>2.616554302275603</v>
+        <v>2.616554302275604</v>
       </c>
       <c r="I57" t="n">
-        <v>52.26686362450164</v>
+        <v>52.2668636245016</v>
       </c>
       <c r="J57" t="n">
         <v>0.9187962143520164</v>
       </c>
       <c r="K57" t="n">
-        <v>2.955899517665744</v>
+        <v>2.955899517665743</v>
       </c>
       <c r="L57" t="n">
         <v>26.50814840086409</v>
@@ -2620,7 +2620,7 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>2.388112351066671</v>
+        <v>2.388112351156182</v>
       </c>
       <c r="B58" t="n">
         <v>0</v>
@@ -2632,33 +2632,33 @@
         <v>0</v>
       </c>
       <c r="E58" t="n">
-        <v>9.699347069291413</v>
+        <v>9.699347069291422</v>
       </c>
       <c r="F58" t="n">
-        <v>4.985069224042779</v>
+        <v>4.985069224042783</v>
       </c>
       <c r="G58" t="n">
         <v>0.1247653346366633</v>
       </c>
       <c r="H58" t="n">
-        <v>2.680960870595422</v>
+        <v>2.680960870590401</v>
       </c>
       <c r="I58" t="n">
-        <v>50.52212255324282</v>
+        <v>50.52212255331549</v>
       </c>
       <c r="J58" t="n">
         <v>0.1</v>
       </c>
       <c r="K58" t="n">
-        <v>3.072411329380366</v>
+        <v>3.072411329380817</v>
       </c>
       <c r="L58" t="n">
-        <v>25.42946125386938</v>
+        <v>25.42946125384874</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>3.993545822174557</v>
+        <v>3.993545822059574</v>
       </c>
       <c r="B59" t="n">
         <v>0</v>
@@ -2670,16 +2670,16 @@
         <v>0</v>
       </c>
       <c r="E59" t="n">
-        <v>9.699347069291406</v>
+        <v>9.699347069291415</v>
       </c>
       <c r="F59" t="n">
-        <v>4.985069224042771</v>
+        <v>4.985069224042745</v>
       </c>
       <c r="G59" t="n">
         <v>0.2063981465460308</v>
       </c>
       <c r="H59" t="n">
-        <v>2.671654675914092</v>
+        <v>2.671654675914093</v>
       </c>
       <c r="I59" t="n">
         <v>50.76504750905971</v>
@@ -2688,15 +2688,15 @@
         <v>0.2</v>
       </c>
       <c r="K59" t="n">
-        <v>3.054581008433848</v>
+        <v>3.054581008435064</v>
       </c>
       <c r="L59" t="n">
-        <v>25.58858546719811</v>
+        <v>25.58858546705819</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>5.782095715150174</v>
+        <v>5.782095715022011</v>
       </c>
       <c r="B60" t="n">
         <v>0</v>
@@ -2711,30 +2711,30 @@
         <v>9.699347069291395</v>
       </c>
       <c r="F60" t="n">
-        <v>4.985069224042769</v>
+        <v>4.985069224042764</v>
       </c>
       <c r="G60" t="n">
         <v>0.3137697936590399</v>
       </c>
       <c r="H60" t="n">
-        <v>2.660722059192307</v>
+        <v>2.660722059192303</v>
       </c>
       <c r="I60" t="n">
-        <v>51.05423924417278</v>
+        <v>51.05423924417285</v>
       </c>
       <c r="J60" t="n">
         <v>0.3</v>
       </c>
       <c r="K60" t="n">
-        <v>3.038164646011364</v>
+        <v>3.038164646143399</v>
       </c>
       <c r="L60" t="n">
-        <v>25.73693289736029</v>
+        <v>25.73693290014568</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>7.248230992216799</v>
+        <v>7.248230992216659</v>
       </c>
       <c r="B61" t="n">
         <v>0</v>
@@ -2746,33 +2746,33 @@
         <v>0</v>
       </c>
       <c r="E61" t="n">
-        <v>9.699347069291408</v>
+        <v>9.699347069291395</v>
       </c>
       <c r="F61" t="n">
-        <v>4.985069224042771</v>
+        <v>4.98506922404277</v>
       </c>
       <c r="G61" t="n">
         <v>0.4026174994879254</v>
       </c>
       <c r="H61" t="n">
-        <v>2.652568566175737</v>
+        <v>2.652568566175738</v>
       </c>
       <c r="I61" t="n">
-        <v>51.27266195917268</v>
+        <v>51.27266195917266</v>
       </c>
       <c r="J61" t="n">
         <v>0.4</v>
       </c>
       <c r="K61" t="n">
-        <v>3.022883063824818</v>
+        <v>3.022883063824821</v>
       </c>
       <c r="L61" t="n">
-        <v>25.87664304552224</v>
+        <v>25.87664304552222</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>14.22767596066131</v>
+        <v>14.2276759606621</v>
       </c>
       <c r="B62" t="n">
         <v>0</v>
@@ -2784,33 +2784,33 @@
         <v>0</v>
       </c>
       <c r="E62" t="n">
-        <v>9.699347069291395</v>
+        <v>9.699347069291415</v>
       </c>
       <c r="F62" t="n">
-        <v>4.985069224042768</v>
+        <v>4.98506922404278</v>
       </c>
       <c r="G62" t="n">
         <v>0.9261043454272662</v>
       </c>
       <c r="H62" t="n">
-        <v>2.614983040688908</v>
+        <v>2.614983040688909</v>
       </c>
       <c r="I62" t="n">
-        <v>52.31137641976962</v>
+        <v>52.31137641976959</v>
       </c>
       <c r="J62" t="n">
         <v>0.9</v>
       </c>
       <c r="K62" t="n">
-        <v>2.958056868950862</v>
+        <v>2.958056868950858</v>
       </c>
       <c r="L62" t="n">
-        <v>26.48730884250889</v>
+        <v>26.48730884250892</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>-3.556607353125177</v>
+        <v>-3.556607353125074</v>
       </c>
       <c r="B63" t="n">
         <v>0</v>
@@ -2822,7 +2822,7 @@
         <v>0.1</v>
       </c>
       <c r="E63" t="n">
-        <v>8.419262476514666</v>
+        <v>8.419262476514668</v>
       </c>
       <c r="F63" t="n">
         <v>5.745391646600253</v>
@@ -2831,24 +2831,24 @@
         <v>0</v>
       </c>
       <c r="H63" t="n">
-        <v>3.743371491908506</v>
+        <v>3.743371734523987</v>
       </c>
       <c r="I63" t="n">
-        <v>33.55964653086292</v>
+        <v>33.55964318988732</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
       </c>
       <c r="K63" t="n">
-        <v>4.395752719775719</v>
+        <v>4.395752719922317</v>
       </c>
       <c r="L63" t="n">
-        <v>17.46534079526109</v>
+        <v>17.46534079469805</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>-6.994453390141751</v>
+        <v>-6.99445339015288</v>
       </c>
       <c r="B64" t="n">
         <v>0</v>
@@ -2869,19 +2869,19 @@
         <v>0</v>
       </c>
       <c r="H64" t="n">
-        <v>3.743371856014079</v>
+        <v>3.743371856454088</v>
       </c>
       <c r="I64" t="n">
-        <v>33.55964144845556</v>
+        <v>33.55964144214902</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
       </c>
       <c r="K64" t="n">
-        <v>4.395752719914819</v>
+        <v>4.395752719922316</v>
       </c>
       <c r="L64" t="n">
-        <v>17.46534079473399</v>
+        <v>17.46534079469799</v>
       </c>
     </row>
     <row r="65">
@@ -2898,28 +2898,28 @@
         <v>0.3</v>
       </c>
       <c r="E65" t="n">
-        <v>8.162141933309721</v>
+        <v>8.162141933309719</v>
       </c>
       <c r="F65" t="n">
-        <v>5.927019035346338</v>
+        <v>5.92701903534634</v>
       </c>
       <c r="G65" t="n">
         <v>0</v>
       </c>
       <c r="H65" t="n">
-        <v>3.743371434397131</v>
+        <v>3.743371836479491</v>
       </c>
       <c r="I65" t="n">
-        <v>33.55964715510039</v>
+        <v>33.55964173433919</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
       </c>
       <c r="K65" t="n">
-        <v>4.395752719728842</v>
+        <v>4.395752719719552</v>
       </c>
       <c r="L65" t="n">
-        <v>17.46534079538619</v>
+        <v>17.46534079540978</v>
       </c>
     </row>
     <row r="66">
@@ -2936,28 +2936,28 @@
         <v>0.4</v>
       </c>
       <c r="E66" t="n">
-        <v>8.06740143910546</v>
+        <v>8.067401439105463</v>
       </c>
       <c r="F66" t="n">
-        <v>5.996877480197115</v>
+        <v>5.996877480197112</v>
       </c>
       <c r="G66" t="n">
         <v>0</v>
       </c>
       <c r="H66" t="n">
-        <v>3.743371856281114</v>
+        <v>3.743371736835742</v>
       </c>
       <c r="I66" t="n">
-        <v>33.55964144458471</v>
+        <v>33.55964316336497</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
       </c>
       <c r="K66" t="n">
-        <v>4.395752719768211</v>
+        <v>4.395752719895895</v>
       </c>
       <c r="L66" t="n">
-        <v>17.46534079528188</v>
+        <v>17.46534079480371</v>
       </c>
     </row>
     <row r="67">
@@ -2974,28 +2974,28 @@
         <v>0.9</v>
       </c>
       <c r="E67" t="n">
-        <v>7.744056430685746</v>
+        <v>7.744056430685744</v>
       </c>
       <c r="F67" t="n">
-        <v>6.248247945552081</v>
+        <v>6.248247945552082</v>
       </c>
       <c r="G67" t="n">
         <v>0</v>
       </c>
       <c r="H67" t="n">
-        <v>3.743371856410349</v>
+        <v>3.743371473491525</v>
       </c>
       <c r="I67" t="n">
-        <v>33.5596414427964</v>
+        <v>33.55964673309816</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
       </c>
       <c r="K67" t="n">
-        <v>4.395752719920004</v>
+        <v>4.395752719607122</v>
       </c>
       <c r="L67" t="n">
-        <v>17.46534079471174</v>
+        <v>17.46534079591096</v>
       </c>
     </row>
     <row r="68">
@@ -3012,16 +3012,16 @@
         <v>0</v>
       </c>
       <c r="E68" t="n">
-        <v>8.61255600312302</v>
+        <v>8.612556003123018</v>
       </c>
       <c r="F68" t="n">
-        <v>5.616027178402859</v>
+        <v>5.616027178402819</v>
       </c>
       <c r="G68" t="n">
         <v>0.1</v>
       </c>
       <c r="H68" t="n">
-        <v>3.61464487639092</v>
+        <v>3.614644876390921</v>
       </c>
       <c r="I68" t="n">
         <v>34.92415151190161</v>
@@ -3038,7 +3038,7 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>33.72091318648222</v>
+        <v>33.7209131864819</v>
       </c>
       <c r="B69" t="n">
         <v>0</v>
@@ -3050,16 +3050,16 @@
         <v>0</v>
       </c>
       <c r="E69" t="n">
-        <v>8.612556003123018</v>
+        <v>8.61255600312302</v>
       </c>
       <c r="F69" t="n">
-        <v>5.61602717840287</v>
+        <v>5.616027178402838</v>
       </c>
       <c r="G69" t="n">
         <v>0.2</v>
       </c>
       <c r="H69" t="n">
-        <v>3.521833028281219</v>
+        <v>3.521833028281218</v>
       </c>
       <c r="I69" t="n">
         <v>35.98536345410113</v>
@@ -3068,10 +3068,10 @@
         <v>0.1861872028258322</v>
       </c>
       <c r="K69" t="n">
-        <v>4.049546550063069</v>
+        <v>4.04954655006307</v>
       </c>
       <c r="L69" t="n">
-        <v>19.01329900288214</v>
+        <v>19.01329900288213</v>
       </c>
     </row>
     <row r="70">
@@ -3088,16 +3088,16 @@
         <v>0</v>
       </c>
       <c r="E70" t="n">
-        <v>8.612556003123023</v>
+        <v>8.61255600312302</v>
       </c>
       <c r="F70" t="n">
-        <v>5.616027178402855</v>
+        <v>5.616027178402846</v>
       </c>
       <c r="G70" t="n">
         <v>0.3</v>
       </c>
       <c r="H70" t="n">
-        <v>3.450971586571708</v>
+        <v>3.450971586571707</v>
       </c>
       <c r="I70" t="n">
         <v>36.84438848520298</v>
@@ -3106,15 +3106,15 @@
         <v>0.2724584114361717</v>
       </c>
       <c r="K70" t="n">
-        <v>3.96087944603085</v>
+        <v>3.960879446030854</v>
       </c>
       <c r="L70" t="n">
-        <v>19.45586233971915</v>
+        <v>19.45586233971913</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>58.33905675691551</v>
+        <v>58.33905676017069</v>
       </c>
       <c r="B71" t="n">
         <v>0</v>
@@ -3126,33 +3126,33 @@
         <v>0</v>
       </c>
       <c r="E71" t="n">
-        <v>8.612556003123021</v>
+        <v>8.612556003123016</v>
       </c>
       <c r="F71" t="n">
-        <v>5.616027178402868</v>
+        <v>5.616027178402865</v>
       </c>
       <c r="G71" t="n">
         <v>0.4</v>
       </c>
       <c r="H71" t="n">
-        <v>3.394708122773546</v>
+        <v>3.3947081227438</v>
       </c>
       <c r="I71" t="n">
-        <v>37.55929838657981</v>
+        <v>37.55929838661633</v>
       </c>
       <c r="J71" t="n">
         <v>0.3709916581317118</v>
       </c>
       <c r="K71" t="n">
-        <v>3.885472523752267</v>
+        <v>3.885472523752266</v>
       </c>
       <c r="L71" t="n">
-        <v>19.84914493013566</v>
+        <v>19.84914493013567</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>101.6044903464519</v>
+        <v>101.6044903464645</v>
       </c>
       <c r="B72" t="n">
         <v>0</v>
@@ -3167,22 +3167,22 @@
         <v>8.61255600312302</v>
       </c>
       <c r="F72" t="n">
-        <v>5.616027178402857</v>
+        <v>5.616027178402861</v>
       </c>
       <c r="G72" t="n">
         <v>0.9</v>
       </c>
       <c r="H72" t="n">
-        <v>3.223645099627039</v>
+        <v>3.223645099626946</v>
       </c>
       <c r="I72" t="n">
-        <v>39.93586483587215</v>
+        <v>39.93586483587221</v>
       </c>
       <c r="J72" t="n">
         <v>0.9187962143520164</v>
       </c>
       <c r="K72" t="n">
-        <v>3.666551565360047</v>
+        <v>3.666551565360048</v>
       </c>
       <c r="L72" t="n">
         <v>21.08903337881345</v>
@@ -3190,7 +3190,7 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>21.37829750524171</v>
+        <v>21.37829750522033</v>
       </c>
       <c r="B73" t="n">
         <v>0</v>
@@ -3202,33 +3202,33 @@
         <v>0</v>
       </c>
       <c r="E73" t="n">
-        <v>8.612556003123018</v>
+        <v>8.61255600312302</v>
       </c>
       <c r="F73" t="n">
-        <v>5.61602717840287</v>
+        <v>5.616027178402855</v>
       </c>
       <c r="G73" t="n">
         <v>0.1247653346366633</v>
       </c>
       <c r="H73" t="n">
-        <v>3.589027608060948</v>
+        <v>3.589027608061252</v>
       </c>
       <c r="I73" t="n">
-        <v>35.2102006432139</v>
+        <v>35.21020064321461</v>
       </c>
       <c r="J73" t="n">
         <v>0.1</v>
       </c>
       <c r="K73" t="n">
-        <v>4.173296784901265</v>
+        <v>4.173296784901269</v>
       </c>
       <c r="L73" t="n">
-        <v>18.42886757135937</v>
+        <v>18.42886757135935</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>35.00167089836352</v>
+        <v>35.00167089836386</v>
       </c>
       <c r="B74" t="n">
         <v>0</v>
@@ -3243,25 +3243,25 @@
         <v>8.612556003123021</v>
       </c>
       <c r="F74" t="n">
-        <v>5.616027178402834</v>
+        <v>5.61602717840285</v>
       </c>
       <c r="G74" t="n">
         <v>0.2063981465460308</v>
       </c>
       <c r="H74" t="n">
-        <v>3.516742338019175</v>
+        <v>3.516742338019172</v>
       </c>
       <c r="I74" t="n">
-        <v>36.04561280808695</v>
+        <v>36.045612808087</v>
       </c>
       <c r="J74" t="n">
         <v>0.2</v>
       </c>
       <c r="K74" t="n">
-        <v>4.033441996411134</v>
+        <v>4.033441996411131</v>
       </c>
       <c r="L74" t="n">
-        <v>19.09214830533379</v>
+        <v>19.0921483053338</v>
       </c>
     </row>
     <row r="75">
@@ -3281,30 +3281,30 @@
         <v>8.61255600312302</v>
       </c>
       <c r="F75" t="n">
-        <v>5.616027178402858</v>
+        <v>5.616027178402865</v>
       </c>
       <c r="G75" t="n">
         <v>0.3137697936590399</v>
       </c>
       <c r="H75" t="n">
-        <v>3.442478302831986</v>
+        <v>3.442478302831989</v>
       </c>
       <c r="I75" t="n">
-        <v>36.95038383171704</v>
+        <v>36.950383831717</v>
       </c>
       <c r="J75" t="n">
         <v>0.3</v>
       </c>
       <c r="K75" t="n">
-        <v>3.937554987460157</v>
+        <v>3.937554987460162</v>
       </c>
       <c r="L75" t="n">
-        <v>19.57579927509693</v>
+        <v>19.5757992750969</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>59.45245776562128</v>
+        <v>59.45245776565447</v>
       </c>
       <c r="B76" t="n">
         <v>0</v>
@@ -3316,33 +3316,33 @@
         <v>0</v>
       </c>
       <c r="E76" t="n">
-        <v>8.612556003123021</v>
+        <v>8.61255600312302</v>
       </c>
       <c r="F76" t="n">
-        <v>5.616027178402834</v>
+        <v>5.616027178402838</v>
       </c>
       <c r="G76" t="n">
         <v>0.4026174994879254</v>
       </c>
       <c r="H76" t="n">
-        <v>3.393387678295042</v>
+        <v>3.393387678294769</v>
       </c>
       <c r="I76" t="n">
-        <v>37.57644467614871</v>
+        <v>37.57644467614968</v>
       </c>
       <c r="J76" t="n">
         <v>0.4</v>
       </c>
       <c r="K76" t="n">
-        <v>3.866911644169634</v>
+        <v>3.86691164416963</v>
       </c>
       <c r="L76" t="n">
-        <v>19.94845421713874</v>
+        <v>19.94845421713876</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>102.638124663748</v>
+        <v>102.6381246652596</v>
       </c>
       <c r="B77" t="n">
         <v>0</v>
@@ -3357,16 +3357,16 @@
         <v>8.61255600312302</v>
       </c>
       <c r="F77" t="n">
-        <v>5.616027178402859</v>
+        <v>5.616027178402845</v>
       </c>
       <c r="G77" t="n">
         <v>0.9261043454272662</v>
       </c>
       <c r="H77" t="n">
-        <v>3.21758285243637</v>
+        <v>3.217582852426232</v>
       </c>
       <c r="I77" t="n">
-        <v>40.02630051774122</v>
+        <v>40.02630051775188</v>
       </c>
       <c r="J77" t="n">
         <v>0.9</v>
@@ -3392,28 +3392,28 @@
         <v>0.1</v>
       </c>
       <c r="E78" t="n">
-        <v>7.658962145149544</v>
+        <v>7.658962145149542</v>
       </c>
       <c r="F78" t="n">
-        <v>6.317949772334973</v>
+        <v>6.317949772334975</v>
       </c>
       <c r="G78" t="n">
         <v>0</v>
       </c>
       <c r="H78" t="n">
-        <v>4.509158846995403</v>
+        <v>4.509158846995454</v>
       </c>
       <c r="I78" t="n">
-        <v>27.31758801122518</v>
+        <v>27.31758801122306</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
       </c>
       <c r="K78" t="n">
-        <v>5.272990572693508</v>
+        <v>5.272990572691759</v>
       </c>
       <c r="L78" t="n">
-        <v>14.48923362419594</v>
+        <v>14.48923362420006</v>
       </c>
     </row>
     <row r="79">
@@ -3430,28 +3430,28 @@
         <v>0.2</v>
       </c>
       <c r="E79" t="n">
-        <v>7.525051081621916</v>
+        <v>7.525051081621912</v>
       </c>
       <c r="F79" t="n">
-        <v>6.430850327703494</v>
+        <v>6.430850327703497</v>
       </c>
       <c r="G79" t="n">
         <v>0</v>
       </c>
       <c r="H79" t="n">
-        <v>4.509158846995449</v>
+        <v>4.509158846318763</v>
       </c>
       <c r="I79" t="n">
-        <v>27.31758801122301</v>
+        <v>27.3175880173613</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
       </c>
       <c r="K79" t="n">
-        <v>5.272990572696991</v>
+        <v>5.272990572696992</v>
       </c>
       <c r="L79" t="n">
-        <v>14.48923362418054</v>
+        <v>14.48923362418111</v>
       </c>
     </row>
     <row r="80">
@@ -3468,28 +3468,28 @@
         <v>0.3</v>
       </c>
       <c r="E80" t="n">
-        <v>7.417853743579847</v>
+        <v>7.417853743579846</v>
       </c>
       <c r="F80" t="n">
-        <v>6.524185059903331</v>
+        <v>6.524185059903333</v>
       </c>
       <c r="G80" t="n">
         <v>0</v>
       </c>
       <c r="H80" t="n">
-        <v>4.509158846995455</v>
+        <v>4.509158846992159</v>
       </c>
       <c r="I80" t="n">
-        <v>27.3175880112232</v>
+        <v>27.31758801128926</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
       </c>
       <c r="K80" t="n">
-        <v>5.272990572696822</v>
+        <v>5.272990572696991</v>
       </c>
       <c r="L80" t="n">
-        <v>14.48923362418303</v>
+        <v>14.48923362418046</v>
       </c>
     </row>
     <row r="81">
@@ -3506,28 +3506,28 @@
         <v>0.4</v>
       </c>
       <c r="E81" t="n">
-        <v>7.328660955698762</v>
+        <v>7.328660955698759</v>
       </c>
       <c r="F81" t="n">
-        <v>6.603938387878665</v>
+        <v>6.603938387878668</v>
       </c>
       <c r="G81" t="n">
         <v>0</v>
       </c>
       <c r="H81" t="n">
-        <v>4.509158846908393</v>
+        <v>4.509158846994992</v>
       </c>
       <c r="I81" t="n">
-        <v>27.31758801200958</v>
+        <v>27.31758801123436</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
       </c>
       <c r="K81" t="n">
-        <v>5.27299057269699</v>
+        <v>5.272990572696993</v>
       </c>
       <c r="L81" t="n">
-        <v>14.48923362418117</v>
+        <v>14.48923362418114</v>
       </c>
     </row>
     <row r="82">
@@ -3544,7 +3544,7 @@
         <v>0.9</v>
       </c>
       <c r="E82" t="n">
-        <v>7.02759939761558</v>
+        <v>7.027599397615582</v>
       </c>
       <c r="F82" t="n">
         <v>6.888192676121482</v>
@@ -3553,24 +3553,24 @@
         <v>0</v>
       </c>
       <c r="H82" t="n">
-        <v>4.509158846995449</v>
+        <v>4.50915884699542</v>
       </c>
       <c r="I82" t="n">
-        <v>27.3175880112231</v>
+        <v>27.31758801122416</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
       </c>
       <c r="K82" t="n">
-        <v>5.272990572696989</v>
+        <v>5.272990572696103</v>
       </c>
       <c r="L82" t="n">
-        <v>14.48923362418039</v>
+        <v>14.48923362418668</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>24.35280591724352</v>
+        <v>24.35280591724307</v>
       </c>
       <c r="B83" t="n">
         <v>0</v>
@@ -3582,19 +3582,19 @@
         <v>0</v>
       </c>
       <c r="E83" t="n">
-        <v>7.837064168615012</v>
+        <v>7.837064168615006</v>
       </c>
       <c r="F83" t="n">
-        <v>6.173805682149561</v>
+        <v>6.173805682149524</v>
       </c>
       <c r="G83" t="n">
         <v>0.1</v>
       </c>
       <c r="H83" t="n">
-        <v>4.335524995031109</v>
+        <v>4.335524995031112</v>
       </c>
       <c r="I83" t="n">
-        <v>28.50932177756017</v>
+        <v>28.50932177756015</v>
       </c>
       <c r="J83" t="n">
         <v>0.1082177012392873</v>
@@ -3620,10 +3620,10 @@
         <v>0</v>
       </c>
       <c r="E84" t="n">
-        <v>7.837064168615007</v>
+        <v>7.837064168615009</v>
       </c>
       <c r="F84" t="n">
-        <v>6.173805682149554</v>
+        <v>6.173805682149539</v>
       </c>
       <c r="G84" t="n">
         <v>0.2</v>
@@ -3638,10 +3638,10 @@
         <v>0.1861872028258322</v>
       </c>
       <c r="K84" t="n">
-        <v>4.793578934046007</v>
+        <v>4.793578934046012</v>
       </c>
       <c r="L84" t="n">
-        <v>15.97516621938441</v>
+        <v>15.97516621938439</v>
       </c>
     </row>
     <row r="85">
@@ -3658,28 +3658,28 @@
         <v>0</v>
       </c>
       <c r="E85" t="n">
-        <v>7.837064168615009</v>
+        <v>7.837064168615006</v>
       </c>
       <c r="F85" t="n">
-        <v>6.173805682149569</v>
+        <v>6.17380568214955</v>
       </c>
       <c r="G85" t="n">
         <v>0.3</v>
       </c>
       <c r="H85" t="n">
-        <v>4.11246745646153</v>
+        <v>4.112467456461531</v>
       </c>
       <c r="I85" t="n">
-        <v>30.21129176485882</v>
+        <v>30.21129176485881</v>
       </c>
       <c r="J85" t="n">
         <v>0.2724584114361717</v>
       </c>
       <c r="K85" t="n">
-        <v>4.647643714064566</v>
+        <v>4.647643714064562</v>
       </c>
       <c r="L85" t="n">
-        <v>16.49087103004834</v>
+        <v>16.49087103004835</v>
       </c>
     </row>
     <row r="86">
@@ -3696,16 +3696,16 @@
         <v>0</v>
       </c>
       <c r="E86" t="n">
-        <v>7.837064168615007</v>
+        <v>7.837064168615004</v>
       </c>
       <c r="F86" t="n">
-        <v>6.173805682149557</v>
+        <v>6.173805682149561</v>
       </c>
       <c r="G86" t="n">
         <v>0.4</v>
       </c>
       <c r="H86" t="n">
-        <v>4.032194573316414</v>
+        <v>4.032194573316413</v>
       </c>
       <c r="I86" t="n">
         <v>30.87773509975563</v>
@@ -3714,7 +3714,7 @@
         <v>0.3709916581317118</v>
       </c>
       <c r="K86" t="n">
-        <v>4.513984366932661</v>
+        <v>4.513984366932663</v>
       </c>
       <c r="L86" t="n">
         <v>16.9937723594608</v>
@@ -3722,7 +3722,7 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>166.051787943253</v>
+        <v>166.0517879422206</v>
       </c>
       <c r="B87" t="n">
         <v>0</v>
@@ -3737,25 +3737,25 @@
         <v>7.837064168615006</v>
       </c>
       <c r="F87" t="n">
-        <v>6.173805682149553</v>
+        <v>6.173805682149551</v>
       </c>
       <c r="G87" t="n">
         <v>0.9</v>
       </c>
       <c r="H87" t="n">
-        <v>3.76654313947536</v>
+        <v>3.766543139479575</v>
       </c>
       <c r="I87" t="n">
-        <v>33.32612956193377</v>
+        <v>33.32612956190602</v>
       </c>
       <c r="J87" t="n">
         <v>0.9187962143520164</v>
       </c>
       <c r="K87" t="n">
-        <v>4.105149470269706</v>
+        <v>4.105149470269883</v>
       </c>
       <c r="L87" t="n">
-        <v>18.74609482972911</v>
+        <v>18.74609482972849</v>
       </c>
     </row>
     <row r="88">
@@ -3775,22 +3775,22 @@
         <v>7.837064168615006</v>
       </c>
       <c r="F88" t="n">
-        <v>6.173805682149554</v>
+        <v>6.173805682149535</v>
       </c>
       <c r="G88" t="n">
         <v>0.1247653346366633</v>
       </c>
       <c r="H88" t="n">
-        <v>4.301130354332845</v>
+        <v>4.30113035433284</v>
       </c>
       <c r="I88" t="n">
-        <v>28.75848174617386</v>
+        <v>28.7584817461739</v>
       </c>
       <c r="J88" t="n">
         <v>0.1</v>
       </c>
       <c r="K88" t="n">
-        <v>4.977885818595451</v>
+        <v>4.97788581859545</v>
       </c>
       <c r="L88" t="n">
         <v>15.36877144665517</v>
@@ -3798,7 +3798,7 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>46.1624987222564</v>
+        <v>46.16249872225677</v>
       </c>
       <c r="B89" t="n">
         <v>0</v>
@@ -3810,10 +3810,10 @@
         <v>0</v>
       </c>
       <c r="E89" t="n">
-        <v>7.837064168615007</v>
+        <v>7.837064168615009</v>
       </c>
       <c r="F89" t="n">
-        <v>6.173805682149556</v>
+        <v>6.17380568214955</v>
       </c>
       <c r="G89" t="n">
         <v>0.2063981465460308</v>
@@ -3828,15 +3828,15 @@
         <v>0.2</v>
       </c>
       <c r="K89" t="n">
-        <v>4.767998876531849</v>
+        <v>4.767998876531847</v>
       </c>
       <c r="L89" t="n">
-        <v>16.06318375226907</v>
+        <v>16.06318375226908</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>67.33349544284323</v>
+        <v>67.33349544284391</v>
       </c>
       <c r="B90" t="n">
         <v>0</v>
@@ -3851,30 +3851,30 @@
         <v>7.837064168615006</v>
       </c>
       <c r="F90" t="n">
-        <v>6.173805682149555</v>
+        <v>6.17380568214953</v>
       </c>
       <c r="G90" t="n">
         <v>0.3137697936590399</v>
       </c>
       <c r="H90" t="n">
-        <v>4.100520633784763</v>
+        <v>4.100520633784759</v>
       </c>
       <c r="I90" t="n">
-        <v>30.30853986447129</v>
+        <v>30.30853986447131</v>
       </c>
       <c r="J90" t="n">
         <v>0.3</v>
       </c>
       <c r="K90" t="n">
-        <v>4.607184891544382</v>
+        <v>4.607184891544377</v>
       </c>
       <c r="L90" t="n">
-        <v>16.63988212863547</v>
+        <v>16.63988212863548</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>85.06366876632356</v>
+        <v>85.0636687663243</v>
       </c>
       <c r="B91" t="n">
         <v>0</v>
@@ -3886,16 +3886,16 @@
         <v>0</v>
       </c>
       <c r="E91" t="n">
-        <v>7.837064168615009</v>
+        <v>7.837064168615007</v>
       </c>
       <c r="F91" t="n">
-        <v>6.173805682149575</v>
+        <v>6.173805682149577</v>
       </c>
       <c r="G91" t="n">
         <v>0.4026174994879254</v>
       </c>
       <c r="H91" t="n">
-        <v>4.0302758839185</v>
+        <v>4.030275883918499</v>
       </c>
       <c r="I91" t="n">
         <v>30.89404689015254</v>
@@ -3904,15 +3904,15 @@
         <v>0.4</v>
       </c>
       <c r="K91" t="n">
-        <v>4.479934196712301</v>
+        <v>4.479934196712302</v>
       </c>
       <c r="L91" t="n">
-        <v>17.12690822717056</v>
+        <v>17.12690822717055</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>167.8955230012027</v>
+        <v>167.8955230012453</v>
       </c>
       <c r="B92" t="n">
         <v>0</v>
@@ -3924,16 +3924,16 @@
         <v>0</v>
       </c>
       <c r="E92" t="n">
-        <v>7.837064168615006</v>
+        <v>7.837064168615009</v>
       </c>
       <c r="F92" t="n">
-        <v>6.17380568214956</v>
+        <v>6.173805682149546</v>
       </c>
       <c r="G92" t="n">
         <v>0.9261043454272662</v>
       </c>
       <c r="H92" t="n">
-        <v>3.756446993650571</v>
+        <v>3.756446993650572</v>
       </c>
       <c r="I92" t="n">
         <v>33.42744356830013</v>
@@ -3942,15 +3942,15 @@
         <v>0.9</v>
       </c>
       <c r="K92" t="n">
-        <v>4.113852220028178</v>
+        <v>4.113852220027621</v>
       </c>
       <c r="L92" t="n">
-        <v>18.70496455751945</v>
+        <v>18.70496455751894</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>-1.332170214856333</v>
+        <v>-1.332170215260652</v>
       </c>
       <c r="B93" t="n">
         <v>0</v>
@@ -3962,33 +3962,33 @@
         <v>0.1</v>
       </c>
       <c r="E93" t="n">
-        <v>6.881596036859924</v>
+        <v>6.881596036859921</v>
       </c>
       <c r="F93" t="n">
-        <v>7.035067073026367</v>
+        <v>7.035067073026371</v>
       </c>
       <c r="G93" t="n">
         <v>0</v>
       </c>
       <c r="H93" t="n">
-        <v>5.234362327473655</v>
+        <v>5.234362327483119</v>
       </c>
       <c r="I93" t="n">
-        <v>23.28719013922434</v>
+        <v>23.28719013923213</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
       </c>
       <c r="K93" t="n">
-        <v>6.114834605628894</v>
+        <v>6.114834605629476</v>
       </c>
       <c r="L93" t="n">
-        <v>12.4596904990298</v>
+        <v>12.45969049902896</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>-4.049495629276092</v>
+        <v>-4.049495629541639</v>
       </c>
       <c r="B94" t="n">
         <v>0</v>
@@ -4000,33 +4000,33 @@
         <v>0.2</v>
       </c>
       <c r="E94" t="n">
-        <v>6.766664235926041</v>
+        <v>6.766664235926038</v>
       </c>
       <c r="F94" t="n">
-        <v>7.155177451354788</v>
+        <v>7.155177451354792</v>
       </c>
       <c r="G94" t="n">
         <v>0</v>
       </c>
       <c r="H94" t="n">
-        <v>5.234362327461625</v>
+        <v>5.234362327483369</v>
       </c>
       <c r="I94" t="n">
-        <v>23.28719013941486</v>
+        <v>23.28719013922632</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
       </c>
       <c r="K94" t="n">
-        <v>6.114834605629452</v>
+        <v>6.114834605629451</v>
       </c>
       <c r="L94" t="n">
-        <v>12.45969049902895</v>
+        <v>12.45969049902891</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>-6.567710567906022</v>
+        <v>-6.567710567833331</v>
       </c>
       <c r="B95" t="n">
         <v>0</v>
@@ -4038,33 +4038,33 @@
         <v>0.3</v>
       </c>
       <c r="E95" t="n">
-        <v>6.676228233285356</v>
+        <v>6.676228233286731</v>
       </c>
       <c r="F95" t="n">
-        <v>7.25261875260166</v>
+        <v>7.252618752601803</v>
       </c>
       <c r="G95" t="n">
         <v>0</v>
       </c>
       <c r="H95" t="n">
-        <v>5.234362327483132</v>
+        <v>5.234362327482882</v>
       </c>
       <c r="I95" t="n">
-        <v>23.28719013923191</v>
+        <v>23.28719013923107</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
       </c>
       <c r="K95" t="n">
-        <v>6.114834605629493</v>
+        <v>6.114834605629484</v>
       </c>
       <c r="L95" t="n">
-        <v>12.45969049902883</v>
+        <v>12.45969049902886</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>-8.916920732880685</v>
+        <v>-8.916920733186998</v>
       </c>
       <c r="B96" t="n">
         <v>0</v>
@@ -4076,33 +4076,33 @@
         <v>0.4</v>
       </c>
       <c r="E96" t="n">
-        <v>6.602232654388004</v>
+        <v>6.602232654372989</v>
       </c>
       <c r="F96" t="n">
-        <v>7.334348027625421</v>
+        <v>7.334348027642058</v>
       </c>
       <c r="G96" t="n">
         <v>0</v>
       </c>
       <c r="H96" t="n">
-        <v>5.234362327483363</v>
+        <v>5.234362327480314</v>
       </c>
       <c r="I96" t="n">
-        <v>23.28719013922635</v>
+        <v>23.28719013923874</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
       </c>
       <c r="K96" t="n">
-        <v>6.114834605629477</v>
+        <v>6.114834605629428</v>
       </c>
       <c r="L96" t="n">
-        <v>12.45969049902877</v>
+        <v>12.45969049902893</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>-18.81803641841031</v>
+        <v>-18.81803641830559</v>
       </c>
       <c r="B97" t="n">
         <v>0</v>
@@ -4114,33 +4114,33 @@
         <v>0.9</v>
       </c>
       <c r="E97" t="n">
-        <v>6.361184206158711</v>
+        <v>6.361184206158725</v>
       </c>
       <c r="F97" t="n">
-        <v>7.613890141625032</v>
+        <v>7.61389014162499</v>
       </c>
       <c r="G97" t="n">
         <v>0</v>
       </c>
       <c r="H97" t="n">
-        <v>5.234362327483369</v>
+        <v>5.234362327481742</v>
       </c>
       <c r="I97" t="n">
-        <v>23.28719013922631</v>
+        <v>23.28719013923457</v>
       </c>
       <c r="J97" t="n">
         <v>0</v>
       </c>
       <c r="K97" t="n">
-        <v>6.114834605629372</v>
+        <v>6.114834605629454</v>
       </c>
       <c r="L97" t="n">
-        <v>12.45969049902921</v>
+        <v>12.45969049902894</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>26.3347781324592</v>
+        <v>26.3347781324589</v>
       </c>
       <c r="B98" t="n">
         <v>0</v>
@@ -4152,19 +4152,19 @@
         <v>0</v>
       </c>
       <c r="E98" t="n">
-        <v>7.03652582351871</v>
+        <v>7.036525823518705</v>
       </c>
       <c r="F98" t="n">
-        <v>6.879412161042484</v>
+        <v>6.87941216104238</v>
       </c>
       <c r="G98" t="n">
         <v>0.1</v>
       </c>
       <c r="H98" t="n">
-        <v>5.052738297533367</v>
+        <v>5.052738297533373</v>
       </c>
       <c r="I98" t="n">
-        <v>24.17662715341196</v>
+        <v>24.17662715341194</v>
       </c>
       <c r="J98" t="n">
         <v>0.1082177012392873</v>
@@ -4178,7 +4178,7 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>47.70273922685348</v>
+        <v>47.70273922685402</v>
       </c>
       <c r="B99" t="n">
         <v>0</v>
@@ -4190,33 +4190,33 @@
         <v>0</v>
       </c>
       <c r="E99" t="n">
-        <v>7.036525823518708</v>
+        <v>7.036525823518714</v>
       </c>
       <c r="F99" t="n">
-        <v>6.879412161042415</v>
+        <v>6.879412161042475</v>
       </c>
       <c r="G99" t="n">
         <v>0.2</v>
       </c>
       <c r="H99" t="n">
-        <v>4.910237968469839</v>
+        <v>4.910237968469831</v>
       </c>
       <c r="I99" t="n">
-        <v>24.92531420114916</v>
+        <v>24.92531420114917</v>
       </c>
       <c r="J99" t="n">
         <v>0.1861872028258322</v>
       </c>
       <c r="K99" t="n">
-        <v>5.569182817693889</v>
+        <v>5.569182817693894</v>
       </c>
       <c r="L99" t="n">
-        <v>13.70314677153785</v>
+        <v>13.70314677153784</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>69.5288724871215</v>
+        <v>69.52887248711305</v>
       </c>
       <c r="B100" t="n">
         <v>0</v>
@@ -4228,33 +4228,33 @@
         <v>0</v>
       </c>
       <c r="E100" t="n">
-        <v>7.036525823518708</v>
+        <v>7.036525823518712</v>
       </c>
       <c r="F100" t="n">
-        <v>6.879412161042429</v>
+        <v>6.879412161042444</v>
       </c>
       <c r="G100" t="n">
         <v>0.3</v>
       </c>
       <c r="H100" t="n">
-        <v>4.793680444460562</v>
+        <v>4.79368044446063</v>
       </c>
       <c r="I100" t="n">
-        <v>25.57445800156789</v>
+        <v>25.57445800156761</v>
       </c>
       <c r="J100" t="n">
         <v>0.2724584114361717</v>
       </c>
       <c r="K100" t="n">
-        <v>5.404204350756454</v>
+        <v>5.40420435075646</v>
       </c>
       <c r="L100" t="n">
-        <v>14.13002829260943</v>
+        <v>14.13002829260942</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>91.57591160279156</v>
+        <v>91.57591160279111</v>
       </c>
       <c r="B101" t="n">
         <v>0</v>
@@ -4266,10 +4266,10 @@
         <v>0</v>
       </c>
       <c r="E101" t="n">
-        <v>7.036525823518708</v>
+        <v>7.036525823518714</v>
       </c>
       <c r="F101" t="n">
-        <v>6.879412161042457</v>
+        <v>6.879412161042461</v>
       </c>
       <c r="G101" t="n">
         <v>0.4</v>
@@ -4284,15 +4284,15 @@
         <v>0.3709916581317118</v>
       </c>
       <c r="K101" t="n">
-        <v>5.250672918035875</v>
+        <v>5.250672918035882</v>
       </c>
       <c r="L101" t="n">
-        <v>14.55217543507358</v>
+        <v>14.55217543507356</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>195.769790155638</v>
+        <v>195.7697901556399</v>
       </c>
       <c r="B102" t="n">
         <v>0</v>
@@ -4304,33 +4304,33 @@
         <v>0</v>
       </c>
       <c r="E102" t="n">
-        <v>7.036525823518715</v>
+        <v>7.036525823518707</v>
       </c>
       <c r="F102" t="n">
-        <v>6.87941216104245</v>
+        <v>6.879412161042403</v>
       </c>
       <c r="G102" t="n">
         <v>0.9</v>
       </c>
       <c r="H102" t="n">
-        <v>4.389800427566256</v>
+        <v>4.38980042756626</v>
       </c>
       <c r="I102" t="n">
-        <v>28.12523679037499</v>
+        <v>28.12523679037497</v>
       </c>
       <c r="J102" t="n">
         <v>0.9187962143520164</v>
       </c>
       <c r="K102" t="n">
-        <v>4.713439010305852</v>
+        <v>4.713439010305819</v>
       </c>
       <c r="L102" t="n">
-        <v>16.25424305335352</v>
+        <v>16.25424305335354</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>28.98896336111186</v>
+        <v>28.98896336111157</v>
       </c>
       <c r="B103" t="n">
         <v>0</v>
@@ -4342,10 +4342,10 @@
         <v>0</v>
       </c>
       <c r="E103" t="n">
-        <v>7.036525823518705</v>
+        <v>7.036525823518709</v>
       </c>
       <c r="F103" t="n">
-        <v>6.879412161042408</v>
+        <v>6.879412161042465</v>
       </c>
       <c r="G103" t="n">
         <v>0.1247653346366633</v>
@@ -4354,21 +4354,21 @@
         <v>5.01422572594895</v>
       </c>
       <c r="I103" t="n">
-        <v>24.37434002473973</v>
+        <v>24.37434002473972</v>
       </c>
       <c r="J103" t="n">
         <v>0.1</v>
       </c>
       <c r="K103" t="n">
-        <v>5.778561248032205</v>
+        <v>5.778561248032207</v>
       </c>
       <c r="L103" t="n">
-        <v>13.19748050013088</v>
+        <v>13.19748050013087</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>49.86104721298723</v>
+        <v>49.86104721299763</v>
       </c>
       <c r="B104" t="n">
         <v>0</v>
@@ -4383,22 +4383,22 @@
         <v>7.036525823518712</v>
       </c>
       <c r="F104" t="n">
-        <v>6.879412161042455</v>
+        <v>6.879412161042437</v>
       </c>
       <c r="G104" t="n">
         <v>0.2063981465460308</v>
       </c>
       <c r="H104" t="n">
-        <v>4.902195711594073</v>
+        <v>4.902195711593977</v>
       </c>
       <c r="I104" t="n">
-        <v>24.96900398019909</v>
+        <v>24.96900398019946</v>
       </c>
       <c r="J104" t="n">
         <v>0.2</v>
       </c>
       <c r="K104" t="n">
-        <v>5.540289473033624</v>
+        <v>5.540289473033623</v>
       </c>
       <c r="L104" t="n">
         <v>13.77601630590739</v>
@@ -4406,7 +4406,7 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>73.82948992900793</v>
+        <v>73.82948992900836</v>
       </c>
       <c r="B105" t="n">
         <v>0</v>
@@ -4421,30 +4421,30 @@
         <v>7.036525823518715</v>
       </c>
       <c r="F105" t="n">
-        <v>6.879412161042474</v>
+        <v>6.879412161042478</v>
       </c>
       <c r="G105" t="n">
         <v>0.3137697936590399</v>
       </c>
       <c r="H105" t="n">
-        <v>4.779478728641965</v>
+        <v>4.77947872864197</v>
       </c>
       <c r="I105" t="n">
-        <v>25.65596181732004</v>
+        <v>25.65596181732001</v>
       </c>
       <c r="J105" t="n">
         <v>0.3</v>
       </c>
       <c r="K105" t="n">
-        <v>5.358158620144749</v>
+        <v>5.358158620144747</v>
       </c>
       <c r="L105" t="n">
-        <v>14.25401270430055</v>
+        <v>14.25401270430056</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>94.33705261420074</v>
+        <v>94.33705261420045</v>
       </c>
       <c r="B106" t="n">
         <v>0</v>
@@ -4456,33 +4456,33 @@
         <v>0</v>
       </c>
       <c r="E106" t="n">
-        <v>7.036525823518714</v>
+        <v>7.036525823518712</v>
       </c>
       <c r="F106" t="n">
-        <v>6.879412161042461</v>
+        <v>6.879412161042652</v>
       </c>
       <c r="G106" t="n">
         <v>0.4026174994879254</v>
       </c>
       <c r="H106" t="n">
-        <v>4.696410910174022</v>
+        <v>4.696410910174029</v>
       </c>
       <c r="I106" t="n">
-        <v>26.14373195327791</v>
+        <v>26.14373195327786</v>
       </c>
       <c r="J106" t="n">
         <v>0.4</v>
       </c>
       <c r="K106" t="n">
-        <v>5.210672537910132</v>
+        <v>5.210672537910126</v>
       </c>
       <c r="L106" t="n">
-        <v>14.66638237813964</v>
+        <v>14.66638237813966</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>197.5197333722285</v>
+        <v>197.5197333722272</v>
       </c>
       <c r="B107" t="n">
         <v>0</v>
@@ -4494,16 +4494,16 @@
         <v>0</v>
       </c>
       <c r="E107" t="n">
-        <v>7.036525823518709</v>
+        <v>7.036525823518712</v>
       </c>
       <c r="F107" t="n">
-        <v>6.87941216104239</v>
+        <v>6.879412161042471</v>
       </c>
       <c r="G107" t="n">
         <v>0.9261043454272662</v>
       </c>
       <c r="H107" t="n">
-        <v>4.378071981065519</v>
+        <v>4.378071981065517</v>
       </c>
       <c r="I107" t="n">
         <v>28.20731119596918</v>
@@ -4512,15 +4512,15 @@
         <v>0.9</v>
       </c>
       <c r="K107" t="n">
-        <v>4.726652454008943</v>
+        <v>4.726652454008947</v>
       </c>
       <c r="L107" t="n">
-        <v>16.20755001913633</v>
+        <v>16.20755001913632</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>6.834780035277051</v>
+        <v>6.83478003555356</v>
       </c>
       <c r="B108" t="n">
         <v>0</v>
@@ -4532,33 +4532,33 @@
         <v>0.1</v>
       </c>
       <c r="E108" t="n">
-        <v>6.128497937407318</v>
+        <v>6.12849793740546</v>
       </c>
       <c r="F108" t="n">
-        <v>7.904787369190159</v>
+        <v>7.904787369195323</v>
       </c>
       <c r="G108" t="n">
         <v>0</v>
       </c>
       <c r="H108" t="n">
-        <v>5.846909926368788</v>
+        <v>5.846909926368639</v>
       </c>
       <c r="I108" t="n">
-        <v>20.72742782212903</v>
+        <v>20.72742782212946</v>
       </c>
       <c r="J108" t="n">
         <v>0</v>
       </c>
       <c r="K108" t="n">
-        <v>6.810947385913783</v>
+        <v>6.810947385901413</v>
       </c>
       <c r="L108" t="n">
-        <v>11.16889058376146</v>
+        <v>11.16889058380164</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>5.274583490016099</v>
+        <v>5.27458349120156</v>
       </c>
       <c r="B109" t="n">
         <v>0</v>
@@ -4570,33 +4570,33 @@
         <v>0.2</v>
       </c>
       <c r="E109" t="n">
-        <v>6.054000358592873</v>
+        <v>6.054000358603711</v>
       </c>
       <c r="F109" t="n">
-        <v>8.002693397380355</v>
+        <v>8.002693397328384</v>
       </c>
       <c r="G109" t="n">
         <v>0</v>
       </c>
       <c r="H109" t="n">
-        <v>5.846909926368786</v>
+        <v>5.846909926368784</v>
       </c>
       <c r="I109" t="n">
-        <v>20.72742782212903</v>
+        <v>20.72742782212904</v>
       </c>
       <c r="J109" t="n">
         <v>0</v>
       </c>
       <c r="K109" t="n">
-        <v>6.810947385909925</v>
+        <v>6.810947385874167</v>
       </c>
       <c r="L109" t="n">
-        <v>11.16889058379427</v>
+        <v>11.16889058380461</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>3.910921536253885</v>
+        <v>3.910921536759576</v>
       </c>
       <c r="B110" t="n">
         <v>0</v>
@@ -4608,33 +4608,33 @@
         <v>0.3</v>
       </c>
       <c r="E110" t="n">
-        <v>5.995457690847346</v>
+        <v>5.995457690830439</v>
       </c>
       <c r="F110" t="n">
-        <v>8.081355488661039</v>
+        <v>8.081355488716024</v>
       </c>
       <c r="G110" t="n">
         <v>0</v>
       </c>
       <c r="H110" t="n">
-        <v>5.84690992636879</v>
+        <v>5.846909926366481</v>
       </c>
       <c r="I110" t="n">
-        <v>20.72742782212902</v>
+        <v>20.72742782213567</v>
       </c>
       <c r="J110" t="n">
         <v>0</v>
       </c>
       <c r="K110" t="n">
-        <v>6.810947385881176</v>
+        <v>6.81094738586947</v>
       </c>
       <c r="L110" t="n">
-        <v>11.16889058380283</v>
+        <v>11.1688905838009</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>2.692555536845356</v>
+        <v>2.692555536037152</v>
       </c>
       <c r="B111" t="n">
         <v>0</v>
@@ -4646,33 +4646,33 @@
         <v>0.4</v>
       </c>
       <c r="E111" t="n">
-        <v>5.947428973040711</v>
+        <v>5.947428973040716</v>
       </c>
       <c r="F111" t="n">
-        <v>8.147058427425245</v>
+        <v>8.147058427425241</v>
       </c>
       <c r="G111" t="n">
         <v>0</v>
       </c>
       <c r="H111" t="n">
-        <v>5.846909926359623</v>
+        <v>5.846909926368788</v>
       </c>
       <c r="I111" t="n">
-        <v>20.72742782229992</v>
+        <v>20.72742782212903</v>
       </c>
       <c r="J111" t="n">
         <v>0</v>
       </c>
       <c r="K111" t="n">
-        <v>6.810947385890646</v>
+        <v>6.81094738590721</v>
       </c>
       <c r="L111" t="n">
-        <v>11.1688905838042</v>
+        <v>11.16889058379658</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>-2.079471920009799</v>
+        <v>-2.079471919994657</v>
       </c>
       <c r="B112" t="n">
         <v>0</v>
@@ -4684,33 +4684,33 @@
         <v>0.9</v>
       </c>
       <c r="E112" t="n">
-        <v>5.788470958957247</v>
+        <v>5.788470958957248</v>
       </c>
       <c r="F112" t="n">
-        <v>8.372370077823835</v>
+        <v>8.372370077823833</v>
       </c>
       <c r="G112" t="n">
         <v>0</v>
       </c>
       <c r="H112" t="n">
-        <v>5.846909926368789</v>
+        <v>5.846909926359956</v>
       </c>
       <c r="I112" t="n">
-        <v>20.72742782212902</v>
+        <v>20.72742782230031</v>
       </c>
       <c r="J112" t="n">
         <v>0</v>
       </c>
       <c r="K112" t="n">
-        <v>6.810947385874627</v>
+        <v>6.81094738588172</v>
       </c>
       <c r="L112" t="n">
-        <v>11.16889058380216</v>
+        <v>11.16889058380803</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>27.62637003434606</v>
+        <v>27.62637003434565</v>
       </c>
       <c r="B113" t="n">
         <v>0</v>
@@ -4722,10 +4722,10 @@
         <v>0</v>
       </c>
       <c r="E113" t="n">
-        <v>6.229814680542392</v>
+        <v>6.229814680542388</v>
       </c>
       <c r="F113" t="n">
-        <v>7.775428450084743</v>
+        <v>7.775428450084746</v>
       </c>
       <c r="G113" t="n">
         <v>0.1</v>
@@ -4748,7 +4748,7 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>45.98878045746835</v>
+        <v>45.98878045746655</v>
       </c>
       <c r="B114" t="n">
         <v>0</v>
@@ -4760,33 +4760,33 @@
         <v>0</v>
       </c>
       <c r="E114" t="n">
-        <v>6.229814680542415</v>
+        <v>6.229814680542374</v>
       </c>
       <c r="F114" t="n">
-        <v>7.775428450084248</v>
+        <v>7.775428450084835</v>
       </c>
       <c r="G114" t="n">
         <v>0.2</v>
       </c>
       <c r="H114" t="n">
-        <v>5.582196107608238</v>
+        <v>5.582196107608262</v>
       </c>
       <c r="I114" t="n">
-        <v>21.75916478669942</v>
+        <v>21.75916478669934</v>
       </c>
       <c r="J114" t="n">
         <v>0.1861872028258322</v>
       </c>
       <c r="K114" t="n">
-        <v>6.311575079575896</v>
+        <v>6.311575079575875</v>
       </c>
       <c r="L114" t="n">
-        <v>12.06536120701531</v>
+        <v>12.06536120701534</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>66.10333155687294</v>
+        <v>66.10333155687472</v>
       </c>
       <c r="B115" t="n">
         <v>0</v>
@@ -4798,33 +4798,33 @@
         <v>0</v>
       </c>
       <c r="E115" t="n">
-        <v>6.229814680542388</v>
+        <v>6.229814680542418</v>
       </c>
       <c r="F115" t="n">
-        <v>7.775428450084738</v>
+        <v>7.775428450084294</v>
       </c>
       <c r="G115" t="n">
         <v>0.3</v>
       </c>
       <c r="H115" t="n">
-        <v>5.467817013843073</v>
+        <v>5.467817013843058</v>
       </c>
       <c r="I115" t="n">
-        <v>22.23836450104402</v>
+        <v>22.23836450104408</v>
       </c>
       <c r="J115" t="n">
         <v>0.2724584114361717</v>
       </c>
       <c r="K115" t="n">
-        <v>6.134000054261062</v>
+        <v>6.134000054261064</v>
       </c>
       <c r="L115" t="n">
-        <v>12.42013818746446</v>
+        <v>12.42013818746445</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>87.92605840786248</v>
+        <v>87.92605840786152</v>
       </c>
       <c r="B116" t="n">
         <v>0</v>
@@ -4836,33 +4836,33 @@
         <v>0</v>
       </c>
       <c r="E116" t="n">
-        <v>6.229814680542417</v>
+        <v>6.229814680542386</v>
       </c>
       <c r="F116" t="n">
-        <v>7.775428450084322</v>
+        <v>7.775428450084768</v>
       </c>
       <c r="G116" t="n">
         <v>0.4</v>
       </c>
       <c r="H116" t="n">
-        <v>5.366971155165505</v>
+        <v>5.366971155165527</v>
       </c>
       <c r="I116" t="n">
-        <v>22.67925293210372</v>
+        <v>22.67925293210364</v>
       </c>
       <c r="J116" t="n">
         <v>0.3709916581317118</v>
       </c>
       <c r="K116" t="n">
-        <v>5.961526264742207</v>
+        <v>5.961526264742172</v>
       </c>
       <c r="L116" t="n">
-        <v>12.78546215459656</v>
+        <v>12.7854621545966</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>197.758045242448</v>
+        <v>197.7580452424492</v>
       </c>
       <c r="B117" t="n">
         <v>0</v>
@@ -4874,10 +4874,10 @@
         <v>0</v>
       </c>
       <c r="E117" t="n">
-        <v>6.229814680542415</v>
+        <v>6.229814680542383</v>
       </c>
       <c r="F117" t="n">
-        <v>7.775428450084292</v>
+        <v>7.775428450084793</v>
       </c>
       <c r="G117" t="n">
         <v>0.9</v>
@@ -4886,16 +4886,16 @@
         <v>5.013853272390429</v>
       </c>
       <c r="I117" t="n">
-        <v>24.37626844442449</v>
+        <v>24.3762684444245</v>
       </c>
       <c r="J117" t="n">
         <v>0.9187962143520164</v>
       </c>
       <c r="K117" t="n">
-        <v>5.375148878582299</v>
+        <v>5.375148878582295</v>
       </c>
       <c r="L117" t="n">
-        <v>14.20800890067435</v>
+        <v>14.20800890067436</v>
       </c>
     </row>
     <row r="118">
@@ -4912,33 +4912,33 @@
         <v>0</v>
       </c>
       <c r="E118" t="n">
-        <v>6.229814680542383</v>
+        <v>6.229814680542413</v>
       </c>
       <c r="F118" t="n">
-        <v>7.775428450084793</v>
+        <v>7.775428450084306</v>
       </c>
       <c r="G118" t="n">
         <v>0.1247653346366633</v>
       </c>
       <c r="H118" t="n">
-        <v>5.677040887610818</v>
+        <v>5.677040887610817</v>
       </c>
       <c r="I118" t="n">
-        <v>21.37759753844515</v>
+        <v>21.37759753844516</v>
       </c>
       <c r="J118" t="n">
         <v>0.1</v>
       </c>
       <c r="K118" t="n">
-        <v>6.523361592502432</v>
+        <v>6.523361592502427</v>
       </c>
       <c r="L118" t="n">
-        <v>11.66804559417191</v>
+        <v>11.66804559417192</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>48.00714090231821</v>
+        <v>48.00714090231396</v>
       </c>
       <c r="B119" t="n">
         <v>0</v>
@@ -4950,33 +4950,33 @@
         <v>0</v>
       </c>
       <c r="E119" t="n">
-        <v>6.229814680542414</v>
+        <v>6.229814680542411</v>
       </c>
       <c r="F119" t="n">
-        <v>7.775428450084282</v>
+        <v>7.775428450084238</v>
       </c>
       <c r="G119" t="n">
         <v>0.2063981465460308</v>
       </c>
       <c r="H119" t="n">
-        <v>5.574467231081983</v>
+        <v>5.574467231081984</v>
       </c>
       <c r="I119" t="n">
-        <v>21.79087610485098</v>
+        <v>21.79087610485097</v>
       </c>
       <c r="J119" t="n">
         <v>0.2</v>
       </c>
       <c r="K119" t="n">
-        <v>6.280953943054494</v>
+        <v>6.28095394305458</v>
       </c>
       <c r="L119" t="n">
-        <v>12.12507452459406</v>
+        <v>12.12507452459397</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>70.34975053173936</v>
+        <v>70.34975053170132</v>
       </c>
       <c r="B120" t="n">
         <v>0</v>
@@ -4988,33 +4988,33 @@
         <v>0</v>
       </c>
       <c r="E120" t="n">
-        <v>6.229814680542414</v>
+        <v>6.229814680542418</v>
       </c>
       <c r="F120" t="n">
-        <v>7.775428450084324</v>
+        <v>7.775428450084251</v>
       </c>
       <c r="G120" t="n">
         <v>0.3137697936590399</v>
       </c>
       <c r="H120" t="n">
-        <v>5.453144591001693</v>
+        <v>5.453144591001646</v>
       </c>
       <c r="I120" t="n">
-        <v>22.30141150939614</v>
+        <v>22.30141150939633</v>
       </c>
       <c r="J120" t="n">
         <v>0.3</v>
       </c>
       <c r="K120" t="n">
-        <v>6.083014358416881</v>
+        <v>6.083014358417758</v>
       </c>
       <c r="L120" t="n">
-        <v>12.52592282596386</v>
+        <v>12.52592282596257</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>90.85820507627585</v>
+        <v>90.85820507636862</v>
       </c>
       <c r="B121" t="n">
         <v>0</v>
@@ -5026,33 +5026,33 @@
         <v>0</v>
       </c>
       <c r="E121" t="n">
-        <v>6.229814680542382</v>
+        <v>6.229814680542388</v>
       </c>
       <c r="F121" t="n">
-        <v>7.775428450084776</v>
+        <v>7.775428450084751</v>
       </c>
       <c r="G121" t="n">
         <v>0.4026174994879254</v>
       </c>
       <c r="H121" t="n">
-        <v>5.364503824149426</v>
+        <v>5.364503824148882</v>
       </c>
       <c r="I121" t="n">
-        <v>22.69026561983227</v>
+        <v>22.69026561983405</v>
       </c>
       <c r="J121" t="n">
         <v>0.4</v>
       </c>
       <c r="K121" t="n">
-        <v>5.916680425885447</v>
+        <v>5.916680425885118</v>
       </c>
       <c r="L121" t="n">
-        <v>12.8840308499482</v>
+        <v>12.8840308499487</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>199.6739991890043</v>
+        <v>199.6739991890056</v>
       </c>
       <c r="B122" t="n">
         <v>0</v>
@@ -5064,10 +5064,10 @@
         <v>0</v>
       </c>
       <c r="E122" t="n">
-        <v>6.22981468054238</v>
+        <v>6.229814680542413</v>
       </c>
       <c r="F122" t="n">
-        <v>7.7754284500848</v>
+        <v>7.77542845008428</v>
       </c>
       <c r="G122" t="n">
         <v>0.9261043454272662</v>
@@ -5076,16 +5076,16 @@
         <v>5.000219964684943</v>
       </c>
       <c r="I122" t="n">
-        <v>24.44707451116663</v>
+        <v>24.44707451116664</v>
       </c>
       <c r="J122" t="n">
         <v>0.9</v>
       </c>
       <c r="K122" t="n">
-        <v>5.389450425310828</v>
+        <v>5.389450425310831</v>
       </c>
       <c r="L122" t="n">
-        <v>14.16951723043</v>
+        <v>14.16951723042999</v>
       </c>
     </row>
     <row r="123">
@@ -5102,7 +5102,7 @@
         <v>0</v>
       </c>
       <c r="E123" t="n">
-        <v>7.837064168615003</v>
+        <v>7.837064168615002</v>
       </c>
       <c r="F123" t="n">
         <v>6.173805682149559</v>
@@ -5120,7 +5120,7 @@
         <v>0.1</v>
       </c>
       <c r="K123" t="n">
-        <v>3.770437980766415</v>
+        <v>3.770437980766414</v>
       </c>
       <c r="L123" t="n">
         <v>20.4814558693205</v>
@@ -5140,19 +5140,19 @@
         <v>0</v>
       </c>
       <c r="E124" t="n">
-        <v>7.837064168615002</v>
+        <v>7.837064168614999</v>
       </c>
       <c r="F124" t="n">
-        <v>6.173805682149557</v>
+        <v>6.173805682149541</v>
       </c>
       <c r="G124" t="n">
         <v>0.1701643100102089</v>
       </c>
       <c r="H124" t="n">
-        <v>4.244175767458287</v>
+        <v>4.244175767458285</v>
       </c>
       <c r="I124" t="n">
-        <v>29.18131136449999</v>
+        <v>29.1813113645</v>
       </c>
       <c r="J124" t="n">
         <v>0.2</v>
@@ -5166,7 +5166,7 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>51.19915313046028</v>
+        <v>51.19915313046097</v>
       </c>
       <c r="B125" t="n">
         <v>90</v>
@@ -5178,10 +5178,10 @@
         <v>0</v>
       </c>
       <c r="E125" t="n">
-        <v>7.837064168614999</v>
+        <v>7.837064168615</v>
       </c>
       <c r="F125" t="n">
-        <v>6.173805682149546</v>
+        <v>6.173805682149554</v>
       </c>
       <c r="G125" t="n">
         <v>0.3214442565952542</v>
@@ -5190,21 +5190,21 @@
         <v>4.093997882615534</v>
       </c>
       <c r="I125" t="n">
-        <v>30.3619160937488</v>
+        <v>30.36191609374881</v>
       </c>
       <c r="J125" t="n">
         <v>0.3</v>
       </c>
       <c r="K125" t="n">
-        <v>3.630536246129327</v>
+        <v>3.630536246129323</v>
       </c>
       <c r="L125" t="n">
-        <v>21.30839062991481</v>
+        <v>21.30839062991482</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>58.88742559902328</v>
+        <v>58.88742559902227</v>
       </c>
       <c r="B126" t="n">
         <v>90</v>
@@ -5219,30 +5219,30 @@
         <v>7.837064168615</v>
       </c>
       <c r="F126" t="n">
-        <v>6.17380568214956</v>
+        <v>6.173805682149554</v>
       </c>
       <c r="G126" t="n">
         <v>0.3720151345183279</v>
       </c>
       <c r="H126" t="n">
-        <v>4.053242978902852</v>
+        <v>4.053242978902857</v>
       </c>
       <c r="I126" t="n">
-        <v>30.69998519193069</v>
+        <v>30.69998519193065</v>
       </c>
       <c r="J126" t="n">
         <v>0.4</v>
       </c>
       <c r="K126" t="n">
-        <v>3.586463213376641</v>
+        <v>3.586463213376665</v>
       </c>
       <c r="L126" t="n">
-        <v>21.58328154599323</v>
+        <v>21.58328154599474</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>122.9848839959848</v>
+        <v>122.9848839960663</v>
       </c>
       <c r="B127" t="n">
         <v>90</v>
@@ -5254,33 +5254,33 @@
         <v>0</v>
       </c>
       <c r="E127" t="n">
-        <v>7.837064168615003</v>
+        <v>7.837064168615002</v>
       </c>
       <c r="F127" t="n">
-        <v>6.173805682149572</v>
+        <v>6.173805682149539</v>
       </c>
       <c r="G127" t="n">
         <v>0.9137793267857967</v>
       </c>
       <c r="H127" t="n">
-        <v>3.761181232691156</v>
+        <v>3.761181232691152</v>
       </c>
       <c r="I127" t="n">
-        <v>33.37985343681321</v>
+        <v>33.37985343681326</v>
       </c>
       <c r="J127" t="n">
         <v>0.9</v>
       </c>
       <c r="K127" t="n">
-        <v>3.453741272603847</v>
+        <v>3.45374127260206</v>
       </c>
       <c r="L127" t="n">
-        <v>22.45695698888139</v>
+        <v>22.45695698889998</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>1.835788085431368</v>
+        <v>1.835788085108026</v>
       </c>
       <c r="B128" t="n">
         <v>90</v>
@@ -5292,33 +5292,33 @@
         <v>0</v>
       </c>
       <c r="E128" t="n">
-        <v>9.699347069291392</v>
+        <v>9.699347069291379</v>
       </c>
       <c r="F128" t="n">
-        <v>4.985069224042763</v>
+        <v>4.985069224042773</v>
       </c>
       <c r="G128" t="n">
         <v>0.1189512132472919</v>
       </c>
       <c r="H128" t="n">
-        <v>2.681662652113733</v>
+        <v>2.681662652128345</v>
       </c>
       <c r="I128" t="n">
-        <v>50.50392244803923</v>
+        <v>50.50392244784169</v>
       </c>
       <c r="J128" t="n">
         <v>0.1</v>
       </c>
       <c r="K128" t="n">
-        <v>1.908379287040441</v>
+        <v>1.90837928704069</v>
       </c>
       <c r="L128" t="n">
-        <v>43.73432903618903</v>
+        <v>43.73432903617852</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>2.634739230819063</v>
+        <v>2.634739230834278</v>
       </c>
       <c r="B129" t="n">
         <v>90</v>
@@ -5330,33 +5330,33 @@
         <v>0</v>
       </c>
       <c r="E129" t="n">
-        <v>9.699347069291383</v>
+        <v>9.699347069291399</v>
       </c>
       <c r="F129" t="n">
-        <v>4.985069224042769</v>
+        <v>4.985069224042785</v>
       </c>
       <c r="G129" t="n">
         <v>0.1701643100102089</v>
       </c>
       <c r="H129" t="n">
-        <v>2.675665367384411</v>
+        <v>2.675665367384082</v>
       </c>
       <c r="I129" t="n">
-        <v>50.65999279092324</v>
+        <v>50.65999279091609</v>
       </c>
       <c r="J129" t="n">
         <v>0.2</v>
       </c>
       <c r="K129" t="n">
-        <v>1.904998512896706</v>
+        <v>1.904998512780959</v>
       </c>
       <c r="L129" t="n">
-        <v>43.83169431140891</v>
+        <v>43.83169431849718</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>4.564451747701021</v>
+        <v>4.564451747724794</v>
       </c>
       <c r="B130" t="n">
         <v>90</v>
@@ -5368,33 +5368,33 @@
         <v>0</v>
       </c>
       <c r="E130" t="n">
-        <v>9.699347069291406</v>
+        <v>9.699347069291395</v>
       </c>
       <c r="F130" t="n">
-        <v>4.98506922404275</v>
+        <v>4.985069224042761</v>
       </c>
       <c r="G130" t="n">
         <v>0.3214442565952542</v>
       </c>
       <c r="H130" t="n">
-        <v>2.65998867903058</v>
+        <v>2.659988679030274</v>
       </c>
       <c r="I130" t="n">
-        <v>51.07378872710613</v>
+        <v>51.07378872710795</v>
       </c>
       <c r="J130" t="n">
         <v>0.3</v>
       </c>
       <c r="K130" t="n">
-        <v>1.901669738753149</v>
+        <v>1.90166973875314</v>
       </c>
       <c r="L130" t="n">
-        <v>43.92805650531952</v>
+        <v>43.92805650531964</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>5.247608665199103</v>
+        <v>5.247608665200418</v>
       </c>
       <c r="B131" t="n">
         <v>90</v>
@@ -5406,33 +5406,33 @@
         <v>0</v>
       </c>
       <c r="E131" t="n">
-        <v>9.699347069291386</v>
+        <v>9.69934706929139</v>
       </c>
       <c r="F131" t="n">
-        <v>4.98506922404277</v>
+        <v>4.985069224042777</v>
       </c>
       <c r="G131" t="n">
         <v>0.3720151345183279</v>
       </c>
       <c r="H131" t="n">
-        <v>2.6552967046603</v>
+        <v>2.655296704660302</v>
       </c>
       <c r="I131" t="n">
-        <v>51.19931357277213</v>
+        <v>51.19931357277207</v>
       </c>
       <c r="J131" t="n">
         <v>0.4</v>
       </c>
       <c r="K131" t="n">
-        <v>1.898391433030046</v>
+        <v>1.898391433026318</v>
       </c>
       <c r="L131" t="n">
-        <v>44.02344164232167</v>
+        <v>44.02344164232335</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>10.86255706230083</v>
+        <v>10.86255706230495</v>
       </c>
       <c r="B132" t="n">
         <v>90</v>
@@ -5444,28 +5444,28 @@
         <v>0</v>
       </c>
       <c r="E132" t="n">
-        <v>9.699347069291388</v>
+        <v>9.699347069291385</v>
       </c>
       <c r="F132" t="n">
-        <v>4.985069224042767</v>
+        <v>4.985069224042773</v>
       </c>
       <c r="G132" t="n">
         <v>0.9137793267857967</v>
       </c>
       <c r="H132" t="n">
-        <v>2.615721871101734</v>
+        <v>2.615721871101633</v>
       </c>
       <c r="I132" t="n">
-        <v>52.29043361348931</v>
+        <v>52.29043361349095</v>
       </c>
       <c r="J132" t="n">
         <v>0.9</v>
       </c>
       <c r="K132" t="n">
-        <v>1.882707929980548</v>
+        <v>1.882707929980482</v>
       </c>
       <c r="L132" t="n">
-        <v>44.48654708292874</v>
+        <v>44.48654708293421</v>
       </c>
     </row>
   </sheetData>

--- a/simulatedData/dataset_hypothetical.xlsx
+++ b/simulatedData/dataset_hypothetical.xlsx
@@ -492,7 +492,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>5.443484845281919e-12</v>
+        <v>-0.1400084086880591</v>
       </c>
       <c r="B2" t="n">
         <v>0</v>
@@ -501,36 +501,36 @@
         <v>-25</v>
       </c>
       <c r="D2" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="E2" t="n">
-        <v>9.699347069291393</v>
+        <v>9.674792499509973</v>
       </c>
       <c r="F2" t="n">
-        <v>4.985069224042767</v>
+        <v>4.997753447165158</v>
       </c>
       <c r="G2" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="H2" t="n">
-        <v>2.697430405916348</v>
+        <v>2.69598722559045</v>
       </c>
       <c r="I2" t="n">
-        <v>50.0993040483645</v>
+        <v>50.13599931864145</v>
       </c>
       <c r="J2" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="K2" t="n">
-        <v>3.092067302409011</v>
+        <v>3.090003758505476</v>
       </c>
       <c r="L2" t="n">
-        <v>25.25640953197178</v>
+        <v>25.27446204547638</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>4.818890932283339e-12</v>
+        <v>-0.07993334990770844</v>
       </c>
       <c r="B3" t="n">
         <v>0</v>
@@ -539,36 +539,36 @@
         <v>-24</v>
       </c>
       <c r="D3" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="E3" t="n">
-        <v>9.630354885510028</v>
+        <v>9.605842519195699</v>
       </c>
       <c r="F3" t="n">
-        <v>5.020873794760672</v>
+        <v>5.033719176879168</v>
       </c>
       <c r="G3" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="H3" t="n">
-        <v>2.758249353703567</v>
+        <v>2.756302552984517</v>
       </c>
       <c r="I3" t="n">
-        <v>48.61131064316509</v>
+        <v>48.65725798371691</v>
       </c>
       <c r="J3" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="K3" t="n">
-        <v>3.176064903438797</v>
+        <v>3.173505443797927</v>
       </c>
       <c r="L3" t="n">
-        <v>24.54361124311865</v>
+        <v>24.56471442491245</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>4.815811529851255e-12</v>
+        <v>0.0002668327349940325</v>
       </c>
       <c r="B4" t="n">
         <v>0</v>
@@ -577,36 +577,36 @@
         <v>-23</v>
       </c>
       <c r="D4" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="E4" t="n">
-        <v>9.560827209729428</v>
+        <v>9.536371198339612</v>
       </c>
       <c r="F4" t="n">
-        <v>5.057481072452389</v>
+        <v>5.070484895993405</v>
       </c>
       <c r="G4" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="H4" t="n">
-        <v>2.820855337202761</v>
+        <v>2.818256069668041</v>
       </c>
       <c r="I4" t="n">
-        <v>47.18827641641769</v>
+        <v>47.24534975707584</v>
       </c>
       <c r="J4" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="K4" t="n">
-        <v>3.260709315896745</v>
+        <v>3.257414432484517</v>
       </c>
       <c r="L4" t="n">
-        <v>23.86623840568347</v>
+        <v>23.89188226652331</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>4.810787306799591e-12</v>
+        <v>0.1023389456468406</v>
       </c>
       <c r="B5" t="n">
         <v>0</v>
@@ -615,36 +615,36 @@
         <v>-22</v>
       </c>
       <c r="D5" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="E5" t="n">
-        <v>9.490772943835177</v>
+        <v>9.466387238359946</v>
       </c>
       <c r="F5" t="n">
-        <v>5.094910212584586</v>
+        <v>5.108069696513545</v>
       </c>
       <c r="G5" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="H5" t="n">
-        <v>2.88511300332616</v>
+        <v>2.881708111543737</v>
       </c>
       <c r="I5" t="n">
-        <v>45.82807847675473</v>
+        <v>45.89780638132266</v>
       </c>
       <c r="J5" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="K5" t="n">
-        <v>3.345941141093194</v>
+        <v>3.341603274678447</v>
       </c>
       <c r="L5" t="n">
-        <v>23.22209118380449</v>
+        <v>23.25400736451213</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>4.803835669331699e-12</v>
+        <v>0.2258183565325773</v>
       </c>
       <c r="B6" t="n">
         <v>0</v>
@@ -653,36 +653,36 @@
         <v>-21</v>
       </c>
       <c r="D6" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="E6" t="n">
-        <v>9.420201171386379</v>
+        <v>9.395899317221589</v>
       </c>
       <c r="F6" t="n">
-        <v>5.133180979166139</v>
+        <v>5.146493377575099</v>
       </c>
       <c r="G6" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="H6" t="n">
-        <v>2.950892880225108</v>
+        <v>2.94653999736118</v>
       </c>
       <c r="I6" t="n">
-        <v>44.52846622806055</v>
+        <v>44.61178640356723</v>
       </c>
       <c r="J6" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="K6" t="n">
-        <v>3.431702862494683</v>
+        <v>3.425974122853319</v>
       </c>
       <c r="L6" t="n">
-        <v>22.60912837113162</v>
+        <v>22.64903271308672</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>4.794974800622795e-12</v>
+        <v>0.3677988965997114</v>
       </c>
       <c r="B7" t="n">
         <v>0</v>
@@ -691,36 +691,36 @@
         <v>-20</v>
       </c>
       <c r="D7" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="E7" t="n">
-        <v>9.349121163616873</v>
+        <v>9.32491629446074</v>
       </c>
       <c r="F7" t="n">
-        <v>5.172313763739848</v>
+        <v>5.185776374019299</v>
       </c>
       <c r="G7" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="H7" t="n">
-        <v>3.01807095925132</v>
+        <v>3.012653582013691</v>
       </c>
       <c r="I7" t="n">
-        <v>43.28709281230567</v>
+        <v>43.38421688440186</v>
       </c>
       <c r="J7" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="K7" t="n">
-        <v>3.517939746769324</v>
+        <v>3.510472320837264</v>
       </c>
       <c r="L7" t="n">
-        <v>22.02544941102833</v>
+        <v>22.07476319945855</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>4.784223650566282e-12</v>
+        <v>0.5232761186280339</v>
       </c>
       <c r="B8" t="n">
         <v>0</v>
@@ -729,36 +729,36 @@
         <v>-19</v>
       </c>
       <c r="D8" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="E8" t="n">
-        <v>9.277542385800682</v>
+        <v>9.253447086424647</v>
       </c>
       <c r="F8" t="n">
-        <v>5.212329604768589</v>
+        <v>5.225939842151328</v>
       </c>
       <c r="G8" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="H8" t="n">
-        <v>3.086528906879938</v>
+        <v>3.079967627265657</v>
       </c>
       <c r="I8" t="n">
-        <v>42.10156261211326</v>
+        <v>42.21195237626316</v>
       </c>
       <c r="J8" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="K8" t="n">
-        <v>3.604599169038484</v>
+        <v>3.595088798351144</v>
       </c>
       <c r="L8" t="n">
-        <v>21.46928770458955</v>
+        <v>21.52891071195329</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>4.771601926726869e-12</v>
+        <v>0.6859359252383923</v>
       </c>
       <c r="B9" t="n">
         <v>0</v>
@@ -767,36 +767,36 @@
         <v>-18</v>
       </c>
       <c r="D9" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="E9" t="n">
-        <v>9.205474504005354</v>
+        <v>9.181500816296527</v>
       </c>
       <c r="F9" t="n">
-        <v>5.253250207385437</v>
+        <v>5.267005612676728</v>
       </c>
       <c r="G9" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="H9" t="n">
-        <v>3.156153997553547</v>
+        <v>3.148412136897412</v>
       </c>
       <c r="I9" t="n">
-        <v>40.96946516035371</v>
+        <v>41.0919198746883</v>
       </c>
       <c r="J9" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="K9" t="n">
-        <v>3.691630532625133</v>
+        <v>3.679851759273937</v>
       </c>
       <c r="L9" t="n">
-        <v>20.93900051358815</v>
+        <v>21.00919258715944</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>4.757130086568783e-12</v>
+        <v>0.8491211229914972</v>
       </c>
       <c r="B10" t="n">
         <v>0</v>
@@ -805,36 +805,36 @@
         <v>-17</v>
       </c>
       <c r="D10" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="E10" t="n">
-        <v>9.132927392258562</v>
+        <v>9.109086606598355</v>
       </c>
       <c r="F10" t="n">
-        <v>5.295097963471852</v>
+        <v>5.308996321866094</v>
       </c>
       <c r="G10" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="H10" t="n">
-        <v>3.226839002257657</v>
+        <v>3.217922142059355</v>
       </c>
       <c r="I10" t="n">
-        <v>39.88840321610132</v>
+        <v>40.02122685438088</v>
       </c>
       <c r="J10" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="K10" t="n">
-        <v>3.778985068429549</v>
+        <v>3.764811894503343</v>
       </c>
       <c r="L10" t="n">
-        <v>20.43306023696256</v>
+        <v>20.51344040460785</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>1.607854903206587e-11</v>
+        <v>1.006736628690543</v>
       </c>
       <c r="B11" t="n">
         <v>0</v>
@@ -843,36 +843,36 @@
         <v>-16</v>
       </c>
       <c r="D11" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="E11" t="n">
-        <v>9.059911140154993</v>
+        <v>9.036213792496149</v>
       </c>
       <c r="F11" t="n">
-        <v>5.337895972019213</v>
+        <v>5.351935332944387</v>
       </c>
       <c r="G11" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="H11" t="n">
-        <v>3.298481770332996</v>
+        <v>3.288432270580628</v>
       </c>
       <c r="I11" t="n">
-        <v>38.85602027941138</v>
+        <v>38.99722256142227</v>
       </c>
       <c r="J11" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="K11" t="n">
-        <v>3.866615740128793</v>
+        <v>3.850026086701415</v>
       </c>
       <c r="L11" t="n">
-        <v>19.9500456629309</v>
+        <v>20.0396865813855</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>4.722721599512451e-12</v>
+        <v>1.153917769721877</v>
       </c>
       <c r="B12" t="n">
         <v>0</v>
@@ -881,36 +881,36 @@
         <v>-15</v>
       </c>
       <c r="D12" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="E12" t="n">
-        <v>8.986436060932469</v>
+        <v>8.962891855427635</v>
       </c>
       <c r="F12" t="n">
-        <v>5.38166805972018</v>
+        <v>5.395846800784406</v>
       </c>
       <c r="G12" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="H12" t="n">
-        <v>3.370986326460237</v>
+        <v>3.359872905451627</v>
       </c>
       <c r="I12" t="n">
-        <v>37.86999222242693</v>
+        <v>38.01751547766499</v>
       </c>
       <c r="J12" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="K12" t="n">
-        <v>3.954477139618122</v>
+        <v>3.935543407989614</v>
       </c>
       <c r="L12" t="n">
-        <v>19.48863399476637</v>
+        <v>19.58621383244614</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>4.702829566374978e-12</v>
+        <v>1.287390452956813</v>
       </c>
       <c r="B13" t="n">
         <v>0</v>
@@ -919,36 +919,36 @@
         <v>-14</v>
       </c>
       <c r="D13" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="E13" t="n">
-        <v>8.912512700048374</v>
+        <v>8.889130439304232</v>
       </c>
       <c r="F13" t="n">
-        <v>5.426438801725501</v>
+        <v>5.440755686480681</v>
       </c>
       <c r="G13" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="H13" t="n">
-        <v>3.444260067874878</v>
+        <v>3.432168376243277</v>
       </c>
       <c r="I13" t="n">
-        <v>36.92809202183857</v>
+        <v>37.07995586034635</v>
       </c>
       <c r="J13" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="K13" t="n">
-        <v>4.042525290504308</v>
+        <v>4.021395292635352</v>
       </c>
       <c r="L13" t="n">
-        <v>19.0475938565376</v>
+        <v>19.15156771612528</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>1.592839723049625e-11</v>
+        <v>1.405540033965936</v>
       </c>
       <c r="B14" t="n">
         <v>0</v>
@@ -957,36 +957,36 @@
         <v>-13</v>
       </c>
       <c r="D14" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="E14" t="n">
-        <v>8.838151844289541</v>
+        <v>8.814939386839999</v>
       </c>
       <c r="F14" t="n">
-        <v>5.472233542490808</v>
+        <v>5.486687774044657</v>
       </c>
       <c r="G14" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="H14" t="n">
-        <v>3.518216099303301</v>
+        <v>3.50523692534119</v>
       </c>
       <c r="I14" t="n">
-        <v>36.02814793334121</v>
+        <v>36.18259800488144</v>
       </c>
       <c r="J14" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="K14" t="n">
-        <v>4.130717622989087</v>
+        <v>4.107590476917923</v>
       </c>
       <c r="L14" t="n">
-        <v>18.62577808474621</v>
+        <v>18.73453971959612</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>4.657786957480437e-12</v>
+        <v>1.508237111160271</v>
       </c>
       <c r="B15" t="n">
         <v>0</v>
@@ -995,36 +995,36 @@
         <v>-12</v>
       </c>
       <c r="D15" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="E15" t="n">
-        <v>8.763364531451213</v>
+        <v>8.740328757981706</v>
       </c>
       <c r="F15" t="n">
-        <v>5.519078416623477</v>
+        <v>5.533669686298635</v>
       </c>
       <c r="G15" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="H15" t="n">
-        <v>3.592771760862532</v>
+        <v>3.578992169222666</v>
       </c>
       <c r="I15" t="n">
-        <v>35.16807492260258</v>
+        <v>35.32365349955974</v>
       </c>
       <c r="J15" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="K15" t="n">
-        <v>4.219012847104465</v>
+        <v>4.194114186724368</v>
       </c>
       <c r="L15" t="n">
-        <v>18.22211753419642</v>
+        <v>18.33413167112221</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>1.580413030208249e-11</v>
+        <v>1.59652898748716</v>
       </c>
       <c r="B16" t="n">
         <v>0</v>
@@ -1033,36 +1033,36 @@
         <v>-11</v>
       </c>
       <c r="D16" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="E16" t="n">
-        <v>8.688162060623023</v>
+        <v>8.66530885897699</v>
       </c>
       <c r="F16" t="n">
-        <v>5.567000369624425</v>
+        <v>5.581728898383049</v>
       </c>
       <c r="G16" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="H16" t="n">
-        <v>3.667848486320693</v>
+        <v>3.653345213656091</v>
       </c>
       <c r="I16" t="n">
-        <v>34.34587631889599</v>
+        <v>34.50144785178121</v>
       </c>
       <c r="J16" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="K16" t="n">
-        <v>4.307370868235205</v>
+        <v>4.280930476599516</v>
       </c>
       <c r="L16" t="n">
-        <v>17.83561520735162</v>
+        <v>17.94951187757321</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>1.573493969530995e-11</v>
+        <v>1.6722424539513</v>
       </c>
       <c r="B17" t="n">
         <v>0</v>
@@ -1071,36 +1071,36 @@
         <v>-10</v>
       </c>
       <c r="D17" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="E17" t="n">
-        <v>8.61255600312302</v>
+        <v>8.589890273757018</v>
       </c>
       <c r="F17" t="n">
-        <v>5.616027178402867</v>
+        <v>5.630893748259997</v>
       </c>
       <c r="G17" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="H17" t="n">
-        <v>3.743371850910907</v>
+        <v>3.728207260350392</v>
       </c>
       <c r="I17" t="n">
-        <v>33.55964152193394</v>
+        <v>33.71438343618257</v>
       </c>
       <c r="J17" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="K17" t="n">
-        <v>4.395752719586175</v>
+        <v>4.367986742337839</v>
       </c>
       <c r="L17" t="n">
-        <v>17.46534079596972</v>
+        <v>17.57997038709597</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>1.566113173175429e-11</v>
+        <v>1.737594898001503</v>
       </c>
       <c r="B18" t="n">
         <v>0</v>
@@ -1109,36 +1109,36 @@
         <v>-9</v>
       </c>
       <c r="D18" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="E18" t="n">
-        <v>8.536558214123042</v>
+        <v>8.514083899148634</v>
       </c>
       <c r="F18" t="n">
-        <v>5.666187471420737</v>
+        <v>5.681193443578445</v>
       </c>
       <c r="G18" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="H18" t="n">
-        <v>3.819270939230787</v>
+        <v>3.80349201564021</v>
       </c>
       <c r="I18" t="n">
-        <v>32.80755282507882</v>
+        <v>32.96091266558673</v>
       </c>
       <c r="J18" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="K18" t="n">
-        <v>4.484120482968211</v>
+        <v>4.455219104734957</v>
       </c>
       <c r="L18" t="n">
-        <v>17.11042571830219</v>
+        <v>17.22487945922485</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>1.558277290874763e-11</v>
+        <v>1.794871270506402</v>
       </c>
       <c r="B19" t="n">
         <v>0</v>
@@ -1147,36 +1147,36 @@
         <v>-8</v>
       </c>
       <c r="D19" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="E19" t="n">
-        <v>8.460180845012571</v>
+        <v>8.437900984034778</v>
       </c>
       <c r="F19" t="n">
-        <v>5.717510748302229</v>
+        <v>5.732658064277779</v>
       </c>
       <c r="G19" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="H19" t="n">
-        <v>3.895478513272141</v>
+        <v>3.879117381589366</v>
       </c>
       <c r="I19" t="n">
-        <v>32.08787904216323</v>
+        <v>32.23952624928749</v>
       </c>
       <c r="J19" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="K19" t="n">
-        <v>4.572437234826272</v>
+        <v>4.542557918602482</v>
       </c>
       <c r="L19" t="n">
-        <v>16.77005847775497</v>
+        <v>16.88366170920247</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>1.549993046729767e-11</v>
+        <v>1.84616269479964</v>
       </c>
       <c r="B20" t="n">
         <v>0</v>
@@ -1185,36 +1185,36 @@
         <v>-7</v>
       </c>
       <c r="D20" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="E20" t="n">
-        <v>8.383436356550773</v>
+        <v>8.361353172500774</v>
       </c>
       <c r="F20" t="n">
-        <v>5.770027398716848</v>
+        <v>5.785318560280558</v>
       </c>
       <c r="G20" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="H20" t="n">
-        <v>3.971930492951591</v>
+        <v>3.95500696959691</v>
       </c>
       <c r="I20" t="n">
-        <v>31.39897843765132</v>
+        <v>31.54874408444939</v>
       </c>
       <c r="J20" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="K20" t="n">
-        <v>4.660666984094037</v>
+        <v>4.629932231666206</v>
       </c>
       <c r="L20" t="n">
-        <v>16.44348043465661</v>
+        <v>16.55576831014247</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>1.541267238685443e-11</v>
+        <v>1.893199975413166</v>
       </c>
       <c r="B21" t="n">
         <v>0</v>
@@ -1223,36 +1223,36 @@
         <v>-6.000000000000001</v>
       </c>
       <c r="D21" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="E21" t="n">
-        <v>8.30633753286056</v>
+        <v>8.284452562953911</v>
       </c>
       <c r="F21" t="n">
-        <v>5.823768720316807</v>
+        <v>5.83920673618984</v>
       </c>
       <c r="G21" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="H21" t="n">
-        <v>4.048565932038013</v>
+        <v>4.031090701050842</v>
       </c>
       <c r="I21" t="n">
-        <v>30.73929402712836</v>
+        <v>30.88711745844196</v>
       </c>
       <c r="J21" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="K21" t="n">
-        <v>4.74877462388235</v>
+        <v>4.717273684737492</v>
       </c>
       <c r="L21" t="n">
-        <v>16.12998188670748</v>
+        <v>16.24066418069265</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>1.532106738369594e-11</v>
+        <v>1.937267977174056</v>
       </c>
       <c r="B22" t="n">
         <v>0</v>
@@ -1261,36 +1261,36 @@
         <v>-5</v>
       </c>
       <c r="D22" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="E22" t="n">
-        <v>8.228897496322054</v>
+        <v>8.20721171125458</v>
       </c>
       <c r="F22" t="n">
-        <v>5.8787669354746</v>
+        <v>5.894355266414501</v>
       </c>
       <c r="G22" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="H22" t="n">
-        <v>4.125326786189955</v>
+        <v>4.107305003669961</v>
       </c>
       <c r="I22" t="n">
-        <v>30.10735151929713</v>
+        <v>30.25323331839101</v>
       </c>
       <c r="J22" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="K22" t="n">
-        <v>4.836725883699718</v>
+        <v>4.804518923479229</v>
       </c>
       <c r="L22" t="n">
-        <v>15.82889847330988</v>
+        <v>15.93782111922261</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>1.522518491301397e-11</v>
+        <v>1.979185498415188</v>
       </c>
       <c r="B23" t="n">
         <v>0</v>
@@ -1299,36 +1299,36 @@
         <v>-4</v>
       </c>
       <c r="D23" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="E23" t="n">
-        <v>8.151129723426582</v>
+        <v>8.129643755729747</v>
       </c>
       <c r="F23" t="n">
-        <v>5.935055206531922</v>
+        <v>5.950797630993789</v>
       </c>
       <c r="G23" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="H23" t="n">
-        <v>4.202157636599373</v>
+        <v>4.183592574553463</v>
       </c>
       <c r="I23" t="n">
-        <v>29.50175733780496</v>
+        <v>29.64572068155682</v>
       </c>
       <c r="J23" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="K23" t="n">
-        <v>4.924487287391338</v>
+        <v>4.891611112479819</v>
       </c>
       <c r="L23" t="n">
-        <v>15.53960786209036</v>
+        <v>15.64671488066352</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>1.51250951747906e-11</v>
+        <v>2.019335690947513</v>
       </c>
       <c r="B24" t="n">
         <v>0</v>
@@ -1337,36 +1337,36 @@
         <v>-3</v>
       </c>
       <c r="D24" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="E24" t="n">
-        <v>8.073048061657223</v>
+        <v>8.051762428172882</v>
       </c>
       <c r="F24" t="n">
-        <v>5.992667649224857</v>
+        <v>6.008568115231848</v>
       </c>
       <c r="G24" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="H24" t="n">
-        <v>4.279005674422212</v>
+        <v>4.259901854020566</v>
       </c>
       <c r="I24" t="n">
-        <v>28.92119355072527</v>
+        <v>29.0632572850501</v>
       </c>
       <c r="J24" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="K24" t="n">
-        <v>5.012026114971531</v>
+        <v>4.978500324068662</v>
       </c>
       <c r="L24" t="n">
-        <v>15.26152669890068</v>
+        <v>15.36682761471946</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>1.502086912356782e-11</v>
+        <v>2.057724179295215</v>
       </c>
       <c r="B25" t="n">
         <v>0</v>
@@ -1375,36 +1375,36 @@
         <v>-2</v>
       </c>
       <c r="D25" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="E25" t="n">
-        <v>7.994666747465935</v>
+        <v>7.97358212460301</v>
       </c>
       <c r="F25" t="n">
-        <v>6.051639343908493</v>
+        <v>6.06770176649816</v>
       </c>
       <c r="G25" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="H25" t="n">
-        <v>4.355820387296889</v>
+        <v>4.336186323127133</v>
       </c>
       <c r="I25" t="n">
-        <v>28.3644161481989</v>
+        <v>28.50457545454717</v>
       </c>
       <c r="J25" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="K25" t="n">
-        <v>5.099310367635607</v>
+        <v>5.065143562076692</v>
       </c>
       <c r="L25" t="n">
-        <v>14.99410780125049</v>
+        <v>15.09764928278799</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>1.491257848222277e-11</v>
+        <v>2.094055212009436</v>
       </c>
       <c r="B26" t="n">
         <v>0</v>
@@ -1413,36 +1413,36 @@
         <v>-1</v>
       </c>
       <c r="D26" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="E26" t="n">
-        <v>7.916000425422448</v>
+        <v>7.895117966001207</v>
       </c>
       <c r="F26" t="n">
-        <v>6.112006344143065</v>
+        <v>6.128234349670168</v>
       </c>
       <c r="G26" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="H26" t="n">
-        <v>4.432553505047626</v>
+        <v>4.412403756607143</v>
       </c>
       <c r="I26" t="n">
-        <v>27.83025049707959</v>
+        <v>27.96846643456399</v>
       </c>
       <c r="J26" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="K26" t="n">
-        <v>5.186308736294465</v>
+        <v>5.151504104259787</v>
       </c>
       <c r="L26" t="n">
-        <v>14.73683757300254</v>
+        <v>14.83868185006057</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>1.480029575987363e-11</v>
+        <v>2.127822807142061</v>
       </c>
       <c r="B27" t="n">
         <v>0</v>
@@ -1451,36 +1451,36 @@
         <v>0</v>
       </c>
       <c r="D27" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="E27" t="n">
-        <v>7.837064168615004</v>
+        <v>7.816385858994765</v>
       </c>
       <c r="F27" t="n">
-        <v>6.173805682149499</v>
+        <v>6.190202294374796</v>
       </c>
       <c r="G27" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="H27" t="n">
-        <v>4.509158846994181</v>
+        <v>4.488515317790219</v>
       </c>
       <c r="I27" t="n">
-        <v>27.31758801123689</v>
+        <v>27.45378396753983</v>
       </c>
       <c r="J27" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="K27" t="n">
-        <v>5.27299057269192</v>
+        <v>5.237550674788751</v>
       </c>
       <c r="L27" t="n">
-        <v>14.48923362419971</v>
+        <v>14.5894425737286</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>1.468409427405283e-11</v>
+        <v>2.15837978881834</v>
       </c>
       <c r="B28" t="n">
         <v>0</v>
@@ -1489,36 +1489,36 @@
         <v>1</v>
       </c>
       <c r="D28" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="E28" t="n">
-        <v>7.757873500388883</v>
+        <v>7.737402554833733</v>
       </c>
       <c r="F28" t="n">
-        <v>6.237075370569893</v>
+        <v>6.253642634349717</v>
       </c>
       <c r="G28" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="H28" t="n">
-        <v>4.585592156148826</v>
+        <v>4.564484971661416</v>
       </c>
       <c r="I28" t="n">
-        <v>26.82538302991853</v>
+        <v>26.95944484543691</v>
       </c>
       <c r="J28" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="K28" t="n">
-        <v>5.359325863191454</v>
+        <v>5.323256484388052</v>
       </c>
       <c r="L28" t="n">
-        <v>14.25084257792133</v>
+        <v>14.34946694377509</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>1.45640481772966e-11</v>
+        <v>2.185022141717919</v>
       </c>
       <c r="B29" t="n">
         <v>0</v>
@@ -1527,36 +1527,36 @@
         <v>2</v>
       </c>
       <c r="D29" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="E29" t="n">
-        <v>7.678444417513592</v>
+        <v>7.658185704615946</v>
       </c>
       <c r="F29" t="n">
-        <v>6.301854399891735</v>
+        <v>6.318592939683906</v>
       </c>
       <c r="G29" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="H29" t="n">
-        <v>4.661811017948281</v>
+        <v>4.640278655767839</v>
       </c>
       <c r="I29" t="n">
-        <v>26.35264905238753</v>
+        <v>26.48442977706619</v>
       </c>
       <c r="J29" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="K29" t="n">
-        <v>5.445285204849969</v>
+        <v>5.40859825639533</v>
       </c>
       <c r="L29" t="n">
-        <v>14.02123804899875</v>
+        <v>14.1183109395284</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>1.444023248831234e-11</v>
+        <v>2.207046720203155</v>
       </c>
       <c r="B30" t="n">
         <v>0</v>
@@ -1565,36 +1565,36 @@
         <v>3</v>
       </c>
       <c r="D30" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="E30" t="n">
-        <v>7.598793414876552</v>
+        <v>7.578753892772683</v>
       </c>
       <c r="F30" t="n">
-        <v>6.368182730810237</v>
+        <v>6.385091254538004</v>
       </c>
       <c r="G30" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="H30" t="n">
-        <v>4.737774732130628</v>
+        <v>4.715863764123172</v>
       </c>
       <c r="I30" t="n">
-        <v>25.8984556086091</v>
+        <v>26.02778192326773</v>
       </c>
       <c r="J30" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="K30" t="n">
-        <v>5.530839783609429</v>
+        <v>5.493555303976523</v>
       </c>
       <c r="L30" t="n">
-        <v>13.8000187802265</v>
+        <v>13.8955525605016</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>1.431272312789768e-11</v>
+        <v>2.223804757355561</v>
       </c>
       <c r="B31" t="n">
         <v>0</v>
@@ -1603,36 +1603,36 @@
         <v>4</v>
       </c>
       <c r="D31" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="E31" t="n">
-        <v>7.518937511806604</v>
+        <v>7.499126748185373</v>
       </c>
       <c r="F31" t="n">
-        <v>6.436101280702531</v>
+        <v>6.453175968033061</v>
       </c>
       <c r="G31" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="H31" t="n">
-        <v>4.813444211286638</v>
+        <v>4.791208630341445</v>
       </c>
       <c r="I31" t="n">
-        <v>25.46192506406228</v>
+        <v>25.5886050500633</v>
       </c>
       <c r="J31" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="K31" t="n">
-        <v>5.615961354369178</v>
+        <v>5.578108738345489</v>
       </c>
       <c r="L31" t="n">
-        <v>13.58680692298771</v>
+        <v>13.68079260042582</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>8.937688241234482e-12</v>
+        <v>2.234742010362341</v>
       </c>
       <c r="B32" t="n">
         <v>0</v>
@@ -1641,36 +1641,36 @@
         <v>5</v>
       </c>
       <c r="D32" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="E32" t="n">
-        <v>7.438894280137573</v>
+        <v>7.41932484746609</v>
       </c>
       <c r="F32" t="n">
-        <v>6.505651903280183</v>
+        <v>6.522885825649344</v>
       </c>
       <c r="G32" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="H32" t="n">
-        <v>4.888781886761088</v>
+        <v>4.866282133542315</v>
       </c>
       <c r="I32" t="n">
-        <v>25.04222956274972</v>
+        <v>25.16606088226898</v>
       </c>
       <c r="J32" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="K32" t="n">
-        <v>5.70062222275502</v>
+        <v>5.662240656348483</v>
       </c>
       <c r="L32" t="n">
-        <v>13.3812464503874</v>
+        <v>13.47365508192575</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>0.241614915920489</v>
+        <v>2.392875369689216</v>
       </c>
       <c r="B33" t="n">
         <v>0</v>
@@ -1679,36 +1679,36 @@
         <v>6.000000000000001</v>
       </c>
       <c r="D33" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="E33" t="n">
-        <v>7.358681874128894</v>
+        <v>7.339369825207706</v>
       </c>
       <c r="F33" t="n">
-        <v>6.576877360362941</v>
+        <v>6.594259782012457</v>
       </c>
       <c r="G33" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="H33" t="n">
-        <v>4.960086384437963</v>
+        <v>4.93880680298404</v>
       </c>
       <c r="I33" t="n">
-        <v>24.6580081992406</v>
+        <v>24.77138694013815</v>
       </c>
       <c r="J33" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="K33" t="n">
-        <v>5.784795228443813</v>
+        <v>5.745933713716822</v>
       </c>
       <c r="L33" t="n">
-        <v>13.18300169179237</v>
+        <v>13.27378670086365</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>0.5454864322902875</v>
+        <v>2.687164128694393</v>
       </c>
       <c r="B34" t="n">
         <v>0</v>
@@ -1717,36 +1717,36 @@
         <v>7</v>
       </c>
       <c r="D34" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="E34" t="n">
-        <v>7.278319062367198</v>
+        <v>7.2592843377951</v>
       </c>
       <c r="F34" t="n">
-        <v>6.649821284579734</v>
+        <v>6.667336951406632</v>
       </c>
       <c r="G34" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="H34" t="n">
-        <v>5.029976954118224</v>
+        <v>5.008854869516179</v>
       </c>
       <c r="I34" t="n">
-        <v>24.29307441699305</v>
+        <v>24.40217883388344</v>
       </c>
       <c r="J34" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="K34" t="n">
-        <v>5.868453729884766</v>
+        <v>5.829170446886083</v>
       </c>
       <c r="L34" t="n">
-        <v>12.99175597874675</v>
+        <v>13.08085658650702</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>0.8714397699293456</v>
+        <v>2.997320388141058</v>
       </c>
       <c r="B35" t="n">
         <v>0</v>
@@ -1755,36 +1755,36 @@
         <v>8</v>
       </c>
       <c r="D35" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="E35" t="n">
-        <v>7.197825261779796</v>
+        <v>7.179092030938309</v>
       </c>
       <c r="F35" t="n">
-        <v>6.724528131648237</v>
+        <v>6.742156550943109</v>
       </c>
       <c r="G35" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="H35" t="n">
-        <v>5.099017878520635</v>
+        <v>5.078131491053539</v>
       </c>
       <c r="I35" t="n">
-        <v>23.94338537308721</v>
+        <v>24.04807066647393</v>
       </c>
       <c r="J35" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="K35" t="n">
-        <v>5.951571590284007</v>
+        <v>5.911933057498101</v>
       </c>
       <c r="L35" t="n">
-        <v>12.80721039317575</v>
+        <v>12.89455512273046</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>1.220056913541201</v>
+        <v>3.324083309144113</v>
       </c>
       <c r="B36" t="n">
         <v>0</v>
@@ -1793,36 +1793,36 @@
         <v>9</v>
       </c>
       <c r="D36" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="E36" t="n">
-        <v>7.11722057389845</v>
+        <v>7.098817481261667</v>
       </c>
       <c r="F36" t="n">
-        <v>6.801043120714596</v>
+        <v>6.818757860821518</v>
       </c>
       <c r="G36" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="H36" t="n">
-        <v>5.167161373426362</v>
+        <v>5.146586120193035</v>
       </c>
       <c r="I36" t="n">
-        <v>23.60829563424215</v>
+        <v>23.70844713588246</v>
       </c>
       <c r="J36" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="K36" t="n">
-        <v>6.034123164740935</v>
+        <v>5.994203066182448</v>
       </c>
       <c r="L36" t="n">
-        <v>12.6290826093082</v>
+        <v>12.71459300300526</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>1.623790945521175</v>
+        <v>3.668218249980643</v>
       </c>
       <c r="B37" t="n">
         <v>0</v>
@@ -1831,36 +1831,36 @@
         <v>10</v>
       </c>
       <c r="D37" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="E37" t="n">
-        <v>7.036525823518708</v>
+        <v>7.018486110311152</v>
       </c>
       <c r="F37" t="n">
-        <v>6.879412161042447</v>
+        <v>6.897180206819828</v>
       </c>
       <c r="G37" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="H37" t="n">
-        <v>5.234362327483366</v>
+        <v>5.214169403139731</v>
       </c>
       <c r="I37" t="n">
-        <v>23.28719013922633</v>
+        <v>23.38272636825997</v>
       </c>
       <c r="J37" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="K37" t="n">
-        <v>6.114834605629484</v>
+        <v>6.075961143277834</v>
       </c>
       <c r="L37" t="n">
-        <v>12.45969049902903</v>
+        <v>12.5406999984345</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>2.186736238823471</v>
+        <v>4.145730634139735</v>
       </c>
       <c r="B38" t="n">
         <v>0</v>
@@ -1869,36 +1869,36 @@
         <v>11</v>
       </c>
       <c r="D38" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="E38" t="n">
-        <v>6.955762599907269</v>
+        <v>6.938124064767765</v>
       </c>
       <c r="F38" t="n">
-        <v>6.959681763129237</v>
+        <v>6.97746297474689</v>
       </c>
       <c r="G38" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="H38" t="n">
-        <v>5.300578531505893</v>
+        <v>5.280833618421992</v>
       </c>
       <c r="I38" t="n">
-        <v>22.97948170839738</v>
+        <v>23.07035599040199</v>
       </c>
       <c r="J38" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="K38" t="n">
-        <v>6.189584455744591</v>
+        <v>6.152824150006175</v>
       </c>
       <c r="L38" t="n">
-        <v>12.30684554192704</v>
+        <v>12.38153599254812</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>2.782187956015926</v>
+        <v>4.698153586476463</v>
       </c>
       <c r="B39" t="n">
         <v>0</v>
@@ -1907,36 +1907,36 @@
         <v>12</v>
       </c>
       <c r="D39" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="E39" t="n">
-        <v>6.874953300716663</v>
+        <v>6.857758126837762</v>
       </c>
       <c r="F39" t="n">
-        <v>7.041898932091689</v>
+        <v>7.059645606581261</v>
       </c>
       <c r="G39" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="H39" t="n">
-        <v>5.365770894360369</v>
+        <v>5.346533132870802</v>
       </c>
       <c r="I39" t="n">
-        <v>22.68460880226144</v>
+        <v>22.7708095680219</v>
       </c>
       <c r="J39" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="K39" t="n">
-        <v>6.263269000125094</v>
+        <v>6.226944384869401</v>
       </c>
       <c r="L39" t="n">
-        <v>12.15983351180907</v>
+        <v>12.23186168111578</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>3.410233420704634</v>
+        <v>5.279263233702796</v>
       </c>
       <c r="B40" t="n">
         <v>0</v>
@@ -1945,36 +1945,36 @@
         <v>13</v>
       </c>
       <c r="D40" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="E40" t="n">
-        <v>6.794121178772662</v>
+        <v>6.777415390528634</v>
       </c>
       <c r="F40" t="n">
-        <v>7.126111040903421</v>
+        <v>7.143767812494678</v>
       </c>
       <c r="G40" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="H40" t="n">
-        <v>5.429903636832283</v>
+        <v>5.411224851440444</v>
       </c>
       <c r="I40" t="n">
-        <v>22.40203352797043</v>
+        <v>22.48358345615583</v>
       </c>
       <c r="J40" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="K40" t="n">
-        <v>6.335855434439985</v>
+        <v>6.300052322337417</v>
       </c>
       <c r="L40" t="n">
-        <v>12.01843247146348</v>
+        <v>12.08776168950952</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>4.070748177683578</v>
+        <v>5.889606057900594</v>
       </c>
       <c r="B41" t="n">
         <v>0</v>
@@ -1983,36 +1983,36 @@
         <v>14</v>
       </c>
       <c r="D41" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="E41" t="n">
-        <v>6.713290391905606</v>
+        <v>6.697123225197729</v>
       </c>
       <c r="F41" t="n">
-        <v>7.212365680779768</v>
+        <v>7.229869554823696</v>
       </c>
       <c r="G41" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="H41" t="n">
-        <v>5.492944454476767</v>
+        <v>5.47486868363404</v>
       </c>
       <c r="I41" t="n">
-        <v>22.13123990479459</v>
+        <v>22.20819393928616</v>
       </c>
       <c r="J41" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="K41" t="n">
-        <v>6.407313127951696</v>
+        <v>6.372112521759943</v>
       </c>
       <c r="L41" t="n">
-        <v>11.88242981403002</v>
+        <v>11.94903602144485</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>4.763381315114865</v>
+        <v>6.529517101665113</v>
       </c>
       <c r="B42" t="n">
         <v>0</v>
@@ -2021,36 +2021,36 @@
         <v>15</v>
       </c>
       <c r="D42" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="E42" t="n">
-        <v>6.63248605600134</v>
+        <v>6.616908986085878</v>
       </c>
       <c r="F42" t="n">
-        <v>7.300710485690381</v>
+        <v>7.317991272361913</v>
       </c>
       <c r="G42" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="H42" t="n">
-        <v>5.554864643466563</v>
+        <v>5.537427818397188</v>
       </c>
       <c r="I42" t="n">
-        <v>21.87173236185275</v>
+        <v>21.94417531100033</v>
       </c>
       <c r="J42" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="K42" t="n">
-        <v>6.477613773438917</v>
+        <v>6.443090664923109</v>
       </c>
       <c r="L42" t="n">
-        <v>11.75162156798551</v>
+        <v>11.81549413036037</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>5.487543079605482</v>
+        <v>7.199074141406458</v>
       </c>
       <c r="B43" t="n">
         <v>0</v>
@@ -2059,36 +2059,36 @@
         <v>16</v>
       </c>
       <c r="D43" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="E43" t="n">
-        <v>6.551734301450765</v>
+        <v>6.536799809366508</v>
       </c>
       <c r="F43" t="n">
-        <v>7.391192927639349</v>
+        <v>7.408174058318481</v>
       </c>
       <c r="G43" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="H43" t="n">
-        <v>5.615639182744262</v>
+        <v>5.598869159398824</v>
       </c>
       <c r="I43" t="n">
-        <v>21.6230344764644</v>
+        <v>21.6910776306752</v>
       </c>
       <c r="J43" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="K43" t="n">
-        <v>6.546731516644604</v>
+        <v>6.512953984004779</v>
       </c>
       <c r="L43" t="n">
-        <v>11.62581178154423</v>
+        <v>11.68695371089036</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>6.242395040237359</v>
+        <v>7.898071715659277</v>
       </c>
       <c r="B44" t="n">
         <v>0</v>
@@ -2097,36 +2097,36 @@
         <v>17</v>
       </c>
       <c r="D44" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="E44" t="n">
-        <v>6.471062333178566</v>
+        <v>6.456822416053022</v>
       </c>
       <c r="F44" t="n">
-        <v>7.483860078971662</v>
+        <v>7.500459854786851</v>
       </c>
       <c r="G44" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="H44" t="n">
-        <v>5.675246769240775</v>
+        <v>5.659163507282059</v>
       </c>
       <c r="I44" t="n">
-        <v>21.38468792566678</v>
+        <v>21.44846550765479</v>
       </c>
       <c r="J44" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="K44" t="n">
-        <v>6.614643061934336</v>
+        <v>6.581671552802501</v>
       </c>
       <c r="L44" t="n">
-        <v>11.50481198234488</v>
+        <v>11.56323979984679</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>7.026842960284902</v>
+        <v>8.625994833399044</v>
       </c>
       <c r="B45" t="n">
         <v>0</v>
@@ -2135,36 +2135,36 @@
         <v>18</v>
       </c>
       <c r="D45" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="E45" t="n">
-        <v>6.390498494430956</v>
+        <v>6.377002963132554</v>
       </c>
       <c r="F45" t="n">
-        <v>7.578758337568939</v>
+        <v>7.594891623071748</v>
       </c>
       <c r="G45" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="H45" t="n">
-        <v>5.733669804229779</v>
+        <v>5.718285736872161</v>
       </c>
       <c r="I45" t="n">
-        <v>21.15625163373845</v>
+        <v>21.21591700263178</v>
       </c>
       <c r="J45" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="K45" t="n">
-        <v>6.681327750997908</v>
+        <v>6.649214604047406</v>
       </c>
       <c r="L45" t="n">
-        <v>11.38844070855768</v>
+        <v>11.44418393062909</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>7.839532457461945</v>
+        <v>9.381999153531646</v>
       </c>
       <c r="B46" t="n">
         <v>0</v>
@@ -2173,36 +2173,36 @@
         <v>19</v>
       </c>
       <c r="D46" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="E46" t="n">
-        <v>6.31007233449836</v>
+        <v>6.297366879649487</v>
       </c>
       <c r="F46" t="n">
-        <v>7.675933110356645</v>
+        <v>7.691513544229373</v>
       </c>
       <c r="G46" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="H46" t="n">
-        <v>5.790894331048739</v>
+        <v>5.77621487772729</v>
       </c>
       <c r="I46" t="n">
-        <v>20.93730109162667</v>
+        <v>20.9930229055145</v>
       </c>
       <c r="J46" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="K46" t="n">
-        <v>6.746767613246317</v>
+        <v>6.715556798228725</v>
       </c>
       <c r="L46" t="n">
-        <v>11.27652310559494</v>
+        <v>11.32962343500124</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>8.678847466207028</v>
+        <v>10.16490033562218</v>
       </c>
       <c r="B47" t="n">
         <v>0</v>
@@ -2211,36 +2211,36 @@
         <v>20</v>
       </c>
       <c r="D47" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="E47" t="n">
-        <v>6.229814680542417</v>
+        <v>6.217938888403745</v>
       </c>
       <c r="F47" t="n">
-        <v>7.775428450084272</v>
+        <v>7.790371035946718</v>
       </c>
       <c r="G47" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="H47" t="n">
-        <v>5.84690992636139</v>
+        <v>5.832934107637366</v>
       </c>
       <c r="I47" t="n">
-        <v>20.72742782215037</v>
+        <v>20.77938630677823</v>
       </c>
       <c r="J47" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="K47" t="n">
-        <v>6.810947385861487</v>
+        <v>6.780674446288424</v>
       </c>
       <c r="L47" t="n">
-        <v>11.16889058381805</v>
+        <v>11.21940087182564</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>-3.538937443681989</v>
+        <v>-3.322976994159535</v>
       </c>
       <c r="B48" t="n">
         <v>0</v>
@@ -2252,33 +2252,33 @@
         <v>0.1</v>
       </c>
       <c r="E48" t="n">
-        <v>9.489621785789451</v>
+        <v>9.489621785789399</v>
       </c>
       <c r="F48" t="n">
-        <v>5.095529895621962</v>
+        <v>5.095529895621987</v>
       </c>
       <c r="G48" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="H48" t="n">
-        <v>2.697430126586939</v>
+        <v>2.69598722559045</v>
       </c>
       <c r="I48" t="n">
-        <v>50.09929523907</v>
+        <v>50.13599931864145</v>
       </c>
       <c r="J48" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="K48" t="n">
-        <v>3.092067197337133</v>
+        <v>3.090003758505476</v>
       </c>
       <c r="L48" t="n">
-        <v>25.25641030724787</v>
+        <v>25.27446204547638</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>-7.022259678786298</v>
+        <v>-6.806299230543922</v>
       </c>
       <c r="B49" t="n">
         <v>0</v>
@@ -2290,33 +2290,33 @@
         <v>0.2</v>
       </c>
       <c r="E49" t="n">
-        <v>9.334823541325351</v>
+        <v>9.334823541274869</v>
       </c>
       <c r="F49" t="n">
-        <v>5.18025754519766</v>
+        <v>5.18025754522241</v>
       </c>
       <c r="G49" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="H49" t="n">
-        <v>2.697430397701317</v>
+        <v>2.69598722559045</v>
       </c>
       <c r="I49" t="n">
-        <v>50.09930382112732</v>
+        <v>50.13599931864145</v>
       </c>
       <c r="J49" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="K49" t="n">
-        <v>3.09206729904317</v>
+        <v>3.090003758505476</v>
       </c>
       <c r="L49" t="n">
-        <v>25.25640955378933</v>
+        <v>25.27446204547638</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>-10.44958826563855</v>
+        <v>-10.23362785518705</v>
       </c>
       <c r="B50" t="n">
         <v>0</v>
@@ -2328,33 +2328,33 @@
         <v>0.3</v>
       </c>
       <c r="E50" t="n">
-        <v>9.212529374081235</v>
+        <v>9.212529372813766</v>
       </c>
       <c r="F50" t="n">
-        <v>5.249216019122017</v>
+        <v>5.249216019758705</v>
       </c>
       <c r="G50" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="H50" t="n">
-        <v>2.697430403631818</v>
+        <v>2.69598722559045</v>
       </c>
       <c r="I50" t="n">
-        <v>50.09930398475608</v>
+        <v>50.13599931864145</v>
       </c>
       <c r="J50" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="K50" t="n">
-        <v>3.092067333040089</v>
+        <v>3.090003758505476</v>
       </c>
       <c r="L50" t="n">
-        <v>25.25640925531289</v>
+        <v>25.27446204547638</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>-13.82660796280627</v>
+        <v>-13.61064775934526</v>
       </c>
       <c r="B51" t="n">
         <v>0</v>
@@ -2366,33 +2366,33 @@
         <v>0.4</v>
       </c>
       <c r="E51" t="n">
-        <v>9.111589061977837</v>
+        <v>9.111589055180144</v>
       </c>
       <c r="F51" t="n">
-        <v>5.307534045233512</v>
+        <v>5.307534048717319</v>
       </c>
       <c r="G51" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="H51" t="n">
-        <v>2.697430393490434</v>
+        <v>2.69598722559045</v>
       </c>
       <c r="I51" t="n">
-        <v>50.09930370514866</v>
+        <v>50.13599931864145</v>
       </c>
       <c r="J51" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="K51" t="n">
-        <v>3.092067092660014</v>
+        <v>3.090003758505476</v>
       </c>
       <c r="L51" t="n">
-        <v>25.25641112531996</v>
+        <v>25.27446204547638</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>-30.144494065624</v>
+        <v>-29.928533616095</v>
       </c>
       <c r="B52" t="n">
         <v>0</v>
@@ -2404,33 +2404,33 @@
         <v>0.9</v>
       </c>
       <c r="E52" t="n">
-        <v>8.771892049491504</v>
+        <v>8.771892049491598</v>
       </c>
       <c r="F52" t="n">
-        <v>5.513696461027649</v>
+        <v>5.51369646102752</v>
       </c>
       <c r="G52" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="H52" t="n">
-        <v>2.697430306331713</v>
+        <v>2.69598722559045</v>
       </c>
       <c r="I52" t="n">
-        <v>50.0993010591862</v>
+        <v>50.13599931864145</v>
       </c>
       <c r="J52" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="K52" t="n">
-        <v>3.092067080735457</v>
+        <v>3.090003758505476</v>
       </c>
       <c r="L52" t="n">
-        <v>25.25641119353691</v>
+        <v>25.27446204547638</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>2.102152324628775</v>
+        <v>1.746185093649242</v>
       </c>
       <c r="B53" t="n">
         <v>0</v>
@@ -2439,36 +2439,36 @@
         <v>-25</v>
       </c>
       <c r="D53" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="E53" t="n">
-        <v>9.699347069291424</v>
+        <v>9.674792499509973</v>
       </c>
       <c r="F53" t="n">
-        <v>4.985069224042792</v>
+        <v>4.997753447165158</v>
       </c>
       <c r="G53" t="n">
         <v>0.1</v>
       </c>
       <c r="H53" t="n">
-        <v>2.683989998574929</v>
+        <v>2.683989982038264</v>
       </c>
       <c r="I53" t="n">
-        <v>50.44368285083699</v>
+        <v>50.44368310508963</v>
       </c>
       <c r="J53" t="n">
         <v>0.1082177012392873</v>
       </c>
       <c r="K53" t="n">
-        <v>3.070883992165514</v>
+        <v>3.070883992165347</v>
       </c>
       <c r="L53" t="n">
-        <v>25.4430111918928</v>
+        <v>25.44301119190287</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>3.839251524612708</v>
+        <v>3.483282667059602</v>
       </c>
       <c r="B54" t="n">
         <v>0</v>
@@ -2477,36 +2477,36 @@
         <v>-25</v>
       </c>
       <c r="D54" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="E54" t="n">
-        <v>9.69934706929139</v>
+        <v>9.674792499509973</v>
       </c>
       <c r="F54" t="n">
-        <v>4.985069224042768</v>
+        <v>4.997753447165158</v>
       </c>
       <c r="G54" t="n">
         <v>0.2</v>
       </c>
       <c r="H54" t="n">
-        <v>2.672349906452221</v>
+        <v>2.672349906449244</v>
       </c>
       <c r="I54" t="n">
-        <v>50.74679737773828</v>
+        <v>50.74679737778793</v>
       </c>
       <c r="J54" t="n">
         <v>0.1861872028258322</v>
       </c>
       <c r="K54" t="n">
-        <v>3.056952118327383</v>
+        <v>3.056952118315445</v>
       </c>
       <c r="L54" t="n">
-        <v>25.56730559354667</v>
+        <v>25.56730559357616</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>5.484213403597066</v>
+        <v>5.128244566935586</v>
       </c>
       <c r="B55" t="n">
         <v>0</v>
@@ -2515,36 +2515,36 @@
         <v>-25</v>
       </c>
       <c r="D55" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="E55" t="n">
-        <v>9.699347069291395</v>
+        <v>9.674792499509973</v>
       </c>
       <c r="F55" t="n">
-        <v>4.985069224042769</v>
+        <v>4.997753447165158</v>
       </c>
       <c r="G55" t="n">
         <v>0.3</v>
       </c>
       <c r="H55" t="n">
-        <v>2.662052797422408</v>
+        <v>2.662052797338107</v>
       </c>
       <c r="I55" t="n">
-        <v>51.01881471155315</v>
+        <v>51.01881471301468</v>
       </c>
       <c r="J55" t="n">
         <v>0.2724584114361717</v>
       </c>
       <c r="K55" t="n">
-        <v>3.042562690630355</v>
+        <v>3.042562690214266</v>
       </c>
       <c r="L55" t="n">
-        <v>25.69701456619964</v>
+        <v>25.69701456638909</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>7.078163436514869</v>
+        <v>6.722194807666186</v>
       </c>
       <c r="B56" t="n">
         <v>0</v>
@@ -2553,36 +2553,36 @@
         <v>-25</v>
       </c>
       <c r="D56" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="E56" t="n">
-        <v>9.699347069291395</v>
+        <v>9.674792499509973</v>
       </c>
       <c r="F56" t="n">
-        <v>4.985069224042767</v>
+        <v>4.997753447165158</v>
       </c>
       <c r="G56" t="n">
         <v>0.4</v>
       </c>
       <c r="H56" t="n">
-        <v>2.652798813906231</v>
+        <v>2.65279881346392</v>
       </c>
       <c r="I56" t="n">
-        <v>51.26646119326673</v>
+        <v>51.26646120375292</v>
       </c>
       <c r="J56" t="n">
         <v>0.3709916581317118</v>
       </c>
       <c r="K56" t="n">
-        <v>3.027211975723695</v>
+        <v>3.027211969891652</v>
       </c>
       <c r="L56" t="n">
-        <v>25.83690649497283</v>
+        <v>25.83690649212364</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>14.09452555419547</v>
+        <v>13.73855669571153</v>
       </c>
       <c r="B57" t="n">
         <v>0</v>
@@ -2591,36 +2591,36 @@
         <v>-25</v>
       </c>
       <c r="D57" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="E57" t="n">
-        <v>9.699347069291392</v>
+        <v>9.674792499509973</v>
       </c>
       <c r="F57" t="n">
-        <v>4.985069224042769</v>
+        <v>4.997753447165158</v>
       </c>
       <c r="G57" t="n">
         <v>0.9</v>
       </c>
       <c r="H57" t="n">
-        <v>2.616554302275604</v>
+        <v>2.616554302275259</v>
       </c>
       <c r="I57" t="n">
-        <v>52.2668636245016</v>
+        <v>52.26686362451041</v>
       </c>
       <c r="J57" t="n">
         <v>0.9187962143520164</v>
       </c>
       <c r="K57" t="n">
-        <v>2.955899517665743</v>
+        <v>2.955899517647545</v>
       </c>
       <c r="L57" t="n">
-        <v>26.50814840086409</v>
+        <v>26.50814840308093</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>2.388112351156182</v>
+        <v>2.032143492852784</v>
       </c>
       <c r="B58" t="n">
         <v>0</v>
@@ -2629,36 +2629,36 @@
         <v>-25</v>
       </c>
       <c r="D58" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="E58" t="n">
-        <v>9.699347069291422</v>
+        <v>9.674792499509973</v>
       </c>
       <c r="F58" t="n">
-        <v>4.985069224042783</v>
+        <v>4.997753447165158</v>
       </c>
       <c r="G58" t="n">
         <v>0.1247653346366633</v>
       </c>
       <c r="H58" t="n">
-        <v>2.680960870590401</v>
+        <v>2.68096087059541</v>
       </c>
       <c r="I58" t="n">
-        <v>50.52212255331549</v>
+        <v>50.52212255324304</v>
       </c>
       <c r="J58" t="n">
         <v>0.1</v>
       </c>
       <c r="K58" t="n">
-        <v>3.072411329380817</v>
+        <v>3.072411329380332</v>
       </c>
       <c r="L58" t="n">
-        <v>25.42946125384874</v>
+        <v>25.42946125387167</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>3.993545822059574</v>
+        <v>3.637576965114806</v>
       </c>
       <c r="B59" t="n">
         <v>0</v>
@@ -2667,36 +2667,36 @@
         <v>-25</v>
       </c>
       <c r="D59" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="E59" t="n">
-        <v>9.699347069291415</v>
+        <v>9.674792499509973</v>
       </c>
       <c r="F59" t="n">
-        <v>4.985069224042745</v>
+        <v>4.997753447165158</v>
       </c>
       <c r="G59" t="n">
         <v>0.2063981465460308</v>
       </c>
       <c r="H59" t="n">
-        <v>2.671654675914093</v>
+        <v>2.671654675909866</v>
       </c>
       <c r="I59" t="n">
-        <v>50.76504750905971</v>
+        <v>50.76504750912715</v>
       </c>
       <c r="J59" t="n">
         <v>0.2</v>
       </c>
       <c r="K59" t="n">
-        <v>3.054581008435064</v>
+        <v>3.054581008409635</v>
       </c>
       <c r="L59" t="n">
-        <v>25.58858546705819</v>
+        <v>25.5885854672469</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>5.782095715022011</v>
+        <v>5.426126898026276</v>
       </c>
       <c r="B60" t="n">
         <v>0</v>
@@ -2705,36 +2705,36 @@
         <v>-25</v>
       </c>
       <c r="D60" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="E60" t="n">
-        <v>9.699347069291395</v>
+        <v>9.674792499509973</v>
       </c>
       <c r="F60" t="n">
-        <v>4.985069224042764</v>
+        <v>4.997753447165158</v>
       </c>
       <c r="G60" t="n">
         <v>0.3137697936590399</v>
       </c>
       <c r="H60" t="n">
-        <v>2.660722059192303</v>
+        <v>2.660722059078572</v>
       </c>
       <c r="I60" t="n">
-        <v>51.05423924417285</v>
+        <v>51.05423924619476</v>
       </c>
       <c r="J60" t="n">
         <v>0.3</v>
       </c>
       <c r="K60" t="n">
-        <v>3.038164646143399</v>
+        <v>3.038164645184302</v>
       </c>
       <c r="L60" t="n">
-        <v>25.73693290014568</v>
+        <v>25.7369329003337</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>7.248230992216659</v>
+        <v>6.892262524601229</v>
       </c>
       <c r="B61" t="n">
         <v>0</v>
@@ -2743,36 +2743,36 @@
         <v>-25</v>
       </c>
       <c r="D61" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="E61" t="n">
-        <v>9.699347069291395</v>
+        <v>9.674792499509973</v>
       </c>
       <c r="F61" t="n">
-        <v>4.98506922404277</v>
+        <v>4.997753447165158</v>
       </c>
       <c r="G61" t="n">
         <v>0.4026174994879254</v>
       </c>
       <c r="H61" t="n">
-        <v>2.652568566175738</v>
+        <v>2.652568565720003</v>
       </c>
       <c r="I61" t="n">
-        <v>51.27266195917266</v>
+        <v>51.2726619701151</v>
       </c>
       <c r="J61" t="n">
         <v>0.4</v>
       </c>
       <c r="K61" t="n">
-        <v>3.022883063824821</v>
+        <v>3.022883052767959</v>
       </c>
       <c r="L61" t="n">
-        <v>25.87664304552222</v>
+        <v>25.87664303642461</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>14.2276759606621</v>
+        <v>13.87170710234789</v>
       </c>
       <c r="B62" t="n">
         <v>0</v>
@@ -2781,36 +2781,36 @@
         <v>-25</v>
       </c>
       <c r="D62" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="E62" t="n">
-        <v>9.699347069291415</v>
+        <v>9.674792499509973</v>
       </c>
       <c r="F62" t="n">
-        <v>4.98506922404278</v>
+        <v>4.997753447165158</v>
       </c>
       <c r="G62" t="n">
         <v>0.9261043454272662</v>
       </c>
       <c r="H62" t="n">
-        <v>2.614983040688909</v>
+        <v>2.614983040688262</v>
       </c>
       <c r="I62" t="n">
-        <v>52.31137641976959</v>
+        <v>52.31137641978442</v>
       </c>
       <c r="J62" t="n">
         <v>0.9</v>
       </c>
       <c r="K62" t="n">
-        <v>2.958056868950858</v>
+        <v>2.958056868937892</v>
       </c>
       <c r="L62" t="n">
-        <v>26.48730884250892</v>
+        <v>26.48730884399222</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>-3.556607353125074</v>
+        <v>-1.521713742648745</v>
       </c>
       <c r="B63" t="n">
         <v>0</v>
@@ -2822,33 +2822,33 @@
         <v>0.1</v>
       </c>
       <c r="E63" t="n">
-        <v>8.419262476514668</v>
+        <v>8.419262476514664</v>
       </c>
       <c r="F63" t="n">
-        <v>5.745391646600253</v>
+        <v>5.745391646600256</v>
       </c>
       <c r="G63" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="H63" t="n">
-        <v>3.743371734523987</v>
+        <v>3.728207260350392</v>
       </c>
       <c r="I63" t="n">
-        <v>33.55964318988732</v>
+        <v>33.71438343618257</v>
       </c>
       <c r="J63" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="K63" t="n">
-        <v>4.395752719922317</v>
+        <v>4.367986742337839</v>
       </c>
       <c r="L63" t="n">
-        <v>17.46534079469805</v>
+        <v>17.57997038709597</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>-6.99445339015288</v>
+        <v>-4.959559779774936</v>
       </c>
       <c r="B64" t="n">
         <v>0</v>
@@ -2860,33 +2860,33 @@
         <v>0.2</v>
       </c>
       <c r="E64" t="n">
-        <v>8.276089552328594</v>
+        <v>8.276089552324507</v>
       </c>
       <c r="F64" t="n">
-        <v>5.845127815053154</v>
+        <v>5.845127815055658</v>
       </c>
       <c r="G64" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="H64" t="n">
-        <v>3.743371856454088</v>
+        <v>3.728207260350392</v>
       </c>
       <c r="I64" t="n">
-        <v>33.55964144214902</v>
+        <v>33.71438343618257</v>
       </c>
       <c r="J64" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="K64" t="n">
-        <v>4.395752719922316</v>
+        <v>4.367986742337839</v>
       </c>
       <c r="L64" t="n">
-        <v>17.46534079469799</v>
+        <v>17.57997038709597</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>-10.34982833341321</v>
+        <v>-8.314934725501383</v>
       </c>
       <c r="B65" t="n">
         <v>0</v>
@@ -2898,33 +2898,33 @@
         <v>0.3</v>
       </c>
       <c r="E65" t="n">
-        <v>8.162141933309719</v>
+        <v>8.16214193323002</v>
       </c>
       <c r="F65" t="n">
-        <v>5.92701903534634</v>
+        <v>5.9270190353964</v>
       </c>
       <c r="G65" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="H65" t="n">
-        <v>3.743371836479491</v>
+        <v>3.728207260350392</v>
       </c>
       <c r="I65" t="n">
-        <v>33.55964173433919</v>
+        <v>33.71438343618257</v>
       </c>
       <c r="J65" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="K65" t="n">
-        <v>4.395752719719552</v>
+        <v>4.367986742337839</v>
       </c>
       <c r="L65" t="n">
-        <v>17.46534079540978</v>
+        <v>17.57997038709597</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>-13.64288997161601</v>
+        <v>-11.60799637479514</v>
       </c>
       <c r="B66" t="n">
         <v>0</v>
@@ -2936,33 +2936,33 @@
         <v>0.4</v>
       </c>
       <c r="E66" t="n">
-        <v>8.067401439105463</v>
+        <v>8.067401438740575</v>
       </c>
       <c r="F66" t="n">
-        <v>5.996877480197112</v>
+        <v>5.996877480431216</v>
       </c>
       <c r="G66" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="H66" t="n">
-        <v>3.743371736835742</v>
+        <v>3.728207260350392</v>
       </c>
       <c r="I66" t="n">
-        <v>33.55964316336497</v>
+        <v>33.71438343618257</v>
       </c>
       <c r="J66" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="K66" t="n">
-        <v>4.395752719895895</v>
+        <v>4.367986742337839</v>
       </c>
       <c r="L66" t="n">
-        <v>17.46534079480371</v>
+        <v>17.57997038709597</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>-29.48560119040208</v>
+        <v>-27.45070759328967</v>
       </c>
       <c r="B67" t="n">
         <v>0</v>
@@ -2974,33 +2974,33 @@
         <v>0.9</v>
       </c>
       <c r="E67" t="n">
-        <v>7.744056430685744</v>
+        <v>7.744056430472471</v>
       </c>
       <c r="F67" t="n">
-        <v>6.248247945552082</v>
+        <v>6.248247945699662</v>
       </c>
       <c r="G67" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="H67" t="n">
-        <v>3.743371473491525</v>
+        <v>3.728207260350392</v>
       </c>
       <c r="I67" t="n">
-        <v>33.55964673309816</v>
+        <v>33.71438343618257</v>
       </c>
       <c r="J67" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="K67" t="n">
-        <v>4.395752719607122</v>
+        <v>4.367986742337839</v>
       </c>
       <c r="L67" t="n">
-        <v>17.46534079591096</v>
+        <v>17.57997038709597</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>19.24723242696969</v>
+        <v>18.88458202039785</v>
       </c>
       <c r="B68" t="n">
         <v>0</v>
@@ -3009,36 +3009,36 @@
         <v>-10</v>
       </c>
       <c r="D68" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="E68" t="n">
-        <v>8.612556003123018</v>
+        <v>8.589890273757018</v>
       </c>
       <c r="F68" t="n">
-        <v>5.616027178402819</v>
+        <v>5.630893748259997</v>
       </c>
       <c r="G68" t="n">
         <v>0.1</v>
       </c>
       <c r="H68" t="n">
-        <v>3.614644876390921</v>
+        <v>3.614644873198309</v>
       </c>
       <c r="I68" t="n">
-        <v>34.92415151190161</v>
+        <v>34.92415153705563</v>
       </c>
       <c r="J68" t="n">
         <v>0.1082177012392873</v>
       </c>
       <c r="K68" t="n">
-        <v>4.159405809410647</v>
+        <v>4.159405797187044</v>
       </c>
       <c r="L68" t="n">
-        <v>18.4926395348988</v>
+        <v>18.49263957153843</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>33.7209131864819</v>
+        <v>33.35826202994125</v>
       </c>
       <c r="B69" t="n">
         <v>0</v>
@@ -3047,22 +3047,22 @@
         <v>-10</v>
       </c>
       <c r="D69" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="E69" t="n">
-        <v>8.61255600312302</v>
+        <v>8.589890273757018</v>
       </c>
       <c r="F69" t="n">
-        <v>5.616027178402838</v>
+        <v>5.630893748259997</v>
       </c>
       <c r="G69" t="n">
         <v>0.2</v>
       </c>
       <c r="H69" t="n">
-        <v>3.521833028281218</v>
+        <v>3.521833028281217</v>
       </c>
       <c r="I69" t="n">
-        <v>35.98536345410113</v>
+        <v>35.98536345410115</v>
       </c>
       <c r="J69" t="n">
         <v>0.1861872028258322</v>
@@ -3076,7 +3076,7 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>46.63695673391781</v>
+        <v>46.27430557737743</v>
       </c>
       <c r="B70" t="n">
         <v>0</v>
@@ -3085,22 +3085,22 @@
         <v>-10</v>
       </c>
       <c r="D70" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="E70" t="n">
-        <v>8.61255600312302</v>
+        <v>8.589890273757018</v>
       </c>
       <c r="F70" t="n">
-        <v>5.616027178402846</v>
+        <v>5.630893748259997</v>
       </c>
       <c r="G70" t="n">
         <v>0.3</v>
       </c>
       <c r="H70" t="n">
-        <v>3.450971586571707</v>
+        <v>3.450971586571703</v>
       </c>
       <c r="I70" t="n">
-        <v>36.84438848520298</v>
+        <v>36.84438848520302</v>
       </c>
       <c r="J70" t="n">
         <v>0.2724584114361717</v>
@@ -3114,7 +3114,7 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>58.33905676017069</v>
+        <v>57.97640574392715</v>
       </c>
       <c r="B71" t="n">
         <v>0</v>
@@ -3123,36 +3123,36 @@
         <v>-10</v>
       </c>
       <c r="D71" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="E71" t="n">
-        <v>8.612556003123016</v>
+        <v>8.589890273757018</v>
       </c>
       <c r="F71" t="n">
-        <v>5.616027178402865</v>
+        <v>5.630893748259997</v>
       </c>
       <c r="G71" t="n">
         <v>0.4</v>
       </c>
       <c r="H71" t="n">
-        <v>3.3947081227438</v>
+        <v>3.394708122773821</v>
       </c>
       <c r="I71" t="n">
-        <v>37.55929838661633</v>
+        <v>37.55929838657884</v>
       </c>
       <c r="J71" t="n">
         <v>0.3709916581317118</v>
       </c>
       <c r="K71" t="n">
-        <v>3.885472523752266</v>
+        <v>3.885472520739296</v>
       </c>
       <c r="L71" t="n">
-        <v>19.84914493013567</v>
+        <v>19.84914493910321</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>101.6044903464645</v>
+        <v>101.2418391894508</v>
       </c>
       <c r="B72" t="n">
         <v>0</v>
@@ -3161,36 +3161,36 @@
         <v>-10</v>
       </c>
       <c r="D72" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="E72" t="n">
-        <v>8.61255600312302</v>
+        <v>8.589890273757018</v>
       </c>
       <c r="F72" t="n">
-        <v>5.616027178402861</v>
+        <v>5.630893748259997</v>
       </c>
       <c r="G72" t="n">
         <v>0.9</v>
       </c>
       <c r="H72" t="n">
-        <v>3.223645099626946</v>
+        <v>3.223645099627036</v>
       </c>
       <c r="I72" t="n">
-        <v>39.93586483587221</v>
+        <v>39.93586483587218</v>
       </c>
       <c r="J72" t="n">
         <v>0.9187962143520164</v>
       </c>
       <c r="K72" t="n">
-        <v>3.666551565360048</v>
+        <v>3.666551565355674</v>
       </c>
       <c r="L72" t="n">
-        <v>21.08903337881345</v>
+        <v>21.08903337898147</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>21.37829750522033</v>
+        <v>21.01564746265416</v>
       </c>
       <c r="B73" t="n">
         <v>0</v>
@@ -3199,36 +3199,36 @@
         <v>-10</v>
       </c>
       <c r="D73" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="E73" t="n">
-        <v>8.61255600312302</v>
+        <v>8.589890273757018</v>
       </c>
       <c r="F73" t="n">
-        <v>5.616027178402855</v>
+        <v>5.630893748259997</v>
       </c>
       <c r="G73" t="n">
         <v>0.1247653346366633</v>
       </c>
       <c r="H73" t="n">
-        <v>3.589027608061252</v>
+        <v>3.589027600263354</v>
       </c>
       <c r="I73" t="n">
-        <v>35.21020064321461</v>
+        <v>35.21020070561843</v>
       </c>
       <c r="J73" t="n">
         <v>0.1</v>
       </c>
       <c r="K73" t="n">
-        <v>4.173296784901269</v>
+        <v>4.173296775704062</v>
       </c>
       <c r="L73" t="n">
-        <v>18.42886757135935</v>
+        <v>18.4288675987423</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>35.00167089836386</v>
+        <v>34.63901974182288</v>
       </c>
       <c r="B74" t="n">
         <v>0</v>
@@ -3237,36 +3237,36 @@
         <v>-10</v>
       </c>
       <c r="D74" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="E74" t="n">
-        <v>8.612556003123021</v>
+        <v>8.589890273757018</v>
       </c>
       <c r="F74" t="n">
-        <v>5.61602717840285</v>
+        <v>5.630893748259997</v>
       </c>
       <c r="G74" t="n">
         <v>0.2063981465460308</v>
       </c>
       <c r="H74" t="n">
-        <v>3.516742338019172</v>
+        <v>3.516742338019173</v>
       </c>
       <c r="I74" t="n">
-        <v>36.045612808087</v>
+        <v>36.04561280808696</v>
       </c>
       <c r="J74" t="n">
         <v>0.2</v>
       </c>
       <c r="K74" t="n">
-        <v>4.033441996411131</v>
+        <v>4.033441996411133</v>
       </c>
       <c r="L74" t="n">
-        <v>19.0921483053338</v>
+        <v>19.09214830533379</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>48.87603260037391</v>
+        <v>48.51338223085865</v>
       </c>
       <c r="B75" t="n">
         <v>0</v>
@@ -3275,36 +3275,36 @@
         <v>-10</v>
       </c>
       <c r="D75" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="E75" t="n">
-        <v>8.61255600312302</v>
+        <v>8.589890273757018</v>
       </c>
       <c r="F75" t="n">
-        <v>5.616027178402865</v>
+        <v>5.630893748259997</v>
       </c>
       <c r="G75" t="n">
         <v>0.3137697936590399</v>
       </c>
       <c r="H75" t="n">
-        <v>3.442478302831989</v>
+        <v>3.442478302831979</v>
       </c>
       <c r="I75" t="n">
-        <v>36.950383831717</v>
+        <v>36.95038383171711</v>
       </c>
       <c r="J75" t="n">
         <v>0.3</v>
       </c>
       <c r="K75" t="n">
-        <v>3.937554987460162</v>
+        <v>3.937554970077634</v>
       </c>
       <c r="L75" t="n">
-        <v>19.5757992750969</v>
+        <v>19.5757993291502</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>59.45245776565447</v>
+        <v>59.08980666425929</v>
       </c>
       <c r="B76" t="n">
         <v>0</v>
@@ -3313,36 +3313,36 @@
         <v>-10</v>
       </c>
       <c r="D76" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="E76" t="n">
-        <v>8.61255600312302</v>
+        <v>8.589890273757018</v>
       </c>
       <c r="F76" t="n">
-        <v>5.616027178402838</v>
+        <v>5.630893748259997</v>
       </c>
       <c r="G76" t="n">
         <v>0.4026174994879254</v>
       </c>
       <c r="H76" t="n">
-        <v>3.393387678294769</v>
+        <v>3.393387678295039</v>
       </c>
       <c r="I76" t="n">
-        <v>37.57644467614968</v>
+        <v>37.57644467614872</v>
       </c>
       <c r="J76" t="n">
         <v>0.4</v>
       </c>
       <c r="K76" t="n">
-        <v>3.86691164416963</v>
+        <v>3.866911643032256</v>
       </c>
       <c r="L76" t="n">
-        <v>19.94845421713876</v>
+        <v>19.94845422041704</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>102.6381246652596</v>
+        <v>102.27547371019</v>
       </c>
       <c r="B77" t="n">
         <v>0</v>
@@ -3351,36 +3351,36 @@
         <v>-10</v>
       </c>
       <c r="D77" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="E77" t="n">
-        <v>8.61255600312302</v>
+        <v>8.589890273757018</v>
       </c>
       <c r="F77" t="n">
-        <v>5.616027178402845</v>
+        <v>5.630893748259997</v>
       </c>
       <c r="G77" t="n">
         <v>0.9261043454272662</v>
       </c>
       <c r="H77" t="n">
-        <v>3.217582852426232</v>
+        <v>3.217582851471375</v>
       </c>
       <c r="I77" t="n">
-        <v>40.02630051775188</v>
+        <v>40.02630052819546</v>
       </c>
       <c r="J77" t="n">
         <v>0.9</v>
       </c>
       <c r="K77" t="n">
-        <v>3.671338418474063</v>
+        <v>3.67133841847279</v>
       </c>
       <c r="L77" t="n">
-        <v>21.06022642645797</v>
+        <v>21.06022642651917</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>-3.382424291726935</v>
+        <v>-0.9093593896202357</v>
       </c>
       <c r="B78" t="n">
         <v>0</v>
@@ -3392,33 +3392,33 @@
         <v>0.1</v>
       </c>
       <c r="E78" t="n">
-        <v>7.658962145149542</v>
+        <v>7.658962145149546</v>
       </c>
       <c r="F78" t="n">
-        <v>6.317949772334975</v>
+        <v>6.317949772334971</v>
       </c>
       <c r="G78" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="H78" t="n">
-        <v>4.509158846995454</v>
+        <v>4.488515317790219</v>
       </c>
       <c r="I78" t="n">
-        <v>27.31758801122306</v>
+        <v>27.45378396753983</v>
       </c>
       <c r="J78" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="K78" t="n">
-        <v>5.272990572691759</v>
+        <v>5.237550674788751</v>
       </c>
       <c r="L78" t="n">
-        <v>14.48923362420006</v>
+        <v>14.5894425737286</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>-6.639323072125402</v>
+        <v>-4.16625817003859</v>
       </c>
       <c r="B79" t="n">
         <v>0</v>
@@ -3430,33 +3430,33 @@
         <v>0.2</v>
       </c>
       <c r="E79" t="n">
-        <v>7.525051081621912</v>
+        <v>7.525051081621179</v>
       </c>
       <c r="F79" t="n">
-        <v>6.430850327703497</v>
+        <v>6.430850327704034</v>
       </c>
       <c r="G79" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="H79" t="n">
-        <v>4.509158846318763</v>
+        <v>4.488515317790219</v>
       </c>
       <c r="I79" t="n">
-        <v>27.3175880173613</v>
+        <v>27.45378396753983</v>
       </c>
       <c r="J79" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="K79" t="n">
-        <v>5.272990572696992</v>
+        <v>5.237550674788751</v>
       </c>
       <c r="L79" t="n">
-        <v>14.48923362418111</v>
+        <v>14.5894425737286</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>-9.797266891972548</v>
+        <v>-7.32420199031244</v>
       </c>
       <c r="B80" t="n">
         <v>0</v>
@@ -3468,33 +3468,33 @@
         <v>0.3</v>
       </c>
       <c r="E80" t="n">
-        <v>7.417853743579846</v>
+        <v>7.417853743565902</v>
       </c>
       <c r="F80" t="n">
-        <v>6.524185059903333</v>
+        <v>6.524185059913829</v>
       </c>
       <c r="G80" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="H80" t="n">
-        <v>4.509158846992159</v>
+        <v>4.488515317790219</v>
       </c>
       <c r="I80" t="n">
-        <v>27.31758801128926</v>
+        <v>27.45378396753983</v>
       </c>
       <c r="J80" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="K80" t="n">
-        <v>5.272990572696991</v>
+        <v>5.237550674788751</v>
       </c>
       <c r="L80" t="n">
-        <v>14.48923362418046</v>
+        <v>14.5894425737286</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>-12.86940171717191</v>
+        <v>-10.39633681730069</v>
       </c>
       <c r="B81" t="n">
         <v>0</v>
@@ -3506,33 +3506,33 @@
         <v>0.4</v>
       </c>
       <c r="E81" t="n">
-        <v>7.328660955698759</v>
+        <v>7.328660955638217</v>
       </c>
       <c r="F81" t="n">
-        <v>6.603938387878668</v>
+        <v>6.603938387925278</v>
       </c>
       <c r="G81" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="H81" t="n">
-        <v>4.509158846994992</v>
+        <v>4.488515317790219</v>
       </c>
       <c r="I81" t="n">
-        <v>27.31758801123436</v>
+        <v>27.45378396753983</v>
       </c>
       <c r="J81" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="K81" t="n">
-        <v>5.272990572696993</v>
+        <v>5.237550674788751</v>
       </c>
       <c r="L81" t="n">
-        <v>14.48923362418114</v>
+        <v>14.5894425737286</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>-27.15356401559231</v>
+        <v>-24.68049911409584</v>
       </c>
       <c r="B82" t="n">
         <v>0</v>
@@ -3544,33 +3544,33 @@
         <v>0.9</v>
       </c>
       <c r="E82" t="n">
-        <v>7.027599397615582</v>
+        <v>7.027599397605362</v>
       </c>
       <c r="F82" t="n">
-        <v>6.888192676121482</v>
+        <v>6.888192676129986</v>
       </c>
       <c r="G82" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="H82" t="n">
-        <v>4.50915884699542</v>
+        <v>4.488515317790219</v>
       </c>
       <c r="I82" t="n">
-        <v>27.31758801122416</v>
+        <v>27.45378396753983</v>
       </c>
       <c r="J82" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="K82" t="n">
-        <v>5.272990572696103</v>
+        <v>5.237550674788751</v>
       </c>
       <c r="L82" t="n">
-        <v>14.48923362418668</v>
+        <v>14.5894425737286</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>24.35280591724307</v>
+        <v>24.00756382226408</v>
       </c>
       <c r="B83" t="n">
         <v>0</v>
@@ -3579,36 +3579,36 @@
         <v>0</v>
       </c>
       <c r="D83" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="E83" t="n">
-        <v>7.837064168615006</v>
+        <v>7.816385858994765</v>
       </c>
       <c r="F83" t="n">
-        <v>6.173805682149524</v>
+        <v>6.190202294374796</v>
       </c>
       <c r="G83" t="n">
         <v>0.1</v>
       </c>
       <c r="H83" t="n">
-        <v>4.335524995031112</v>
+        <v>4.33552499503111</v>
       </c>
       <c r="I83" t="n">
-        <v>28.50932177756015</v>
+        <v>28.50932177756016</v>
       </c>
       <c r="J83" t="n">
         <v>0.1082177012392873</v>
       </c>
       <c r="K83" t="n">
-        <v>4.958162324228196</v>
+        <v>4.958162324228195</v>
       </c>
       <c r="L83" t="n">
-        <v>15.4314273504268</v>
+        <v>15.43142735042681</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>44.20544047627426</v>
+        <v>43.86019838133102</v>
       </c>
       <c r="B84" t="n">
         <v>0</v>
@@ -3617,36 +3617,36 @@
         <v>0</v>
       </c>
       <c r="D84" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="E84" t="n">
-        <v>7.837064168615009</v>
+        <v>7.816385858994765</v>
       </c>
       <c r="F84" t="n">
-        <v>6.173805682149539</v>
+        <v>6.190202294374796</v>
       </c>
       <c r="G84" t="n">
         <v>0.2</v>
       </c>
       <c r="H84" t="n">
-        <v>4.210319808315458</v>
+        <v>4.210319808315242</v>
       </c>
       <c r="I84" t="n">
-        <v>29.43892951192797</v>
+        <v>29.4389295119292</v>
       </c>
       <c r="J84" t="n">
         <v>0.1861872028258322</v>
       </c>
       <c r="K84" t="n">
-        <v>4.793578934046012</v>
+        <v>4.793578934045752</v>
       </c>
       <c r="L84" t="n">
-        <v>15.97516621938439</v>
+        <v>15.97516621938501</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>63.56325425022536</v>
+        <v>63.21801215578438</v>
       </c>
       <c r="B85" t="n">
         <v>0</v>
@@ -3655,36 +3655,36 @@
         <v>0</v>
       </c>
       <c r="D85" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="E85" t="n">
-        <v>7.837064168615006</v>
+        <v>7.816385858994765</v>
       </c>
       <c r="F85" t="n">
-        <v>6.17380568214955</v>
+        <v>6.190202294374796</v>
       </c>
       <c r="G85" t="n">
         <v>0.3</v>
       </c>
       <c r="H85" t="n">
-        <v>4.112467456461531</v>
+        <v>4.112467456459517</v>
       </c>
       <c r="I85" t="n">
-        <v>30.21129176485881</v>
+        <v>30.21129176487078</v>
       </c>
       <c r="J85" t="n">
         <v>0.2724584114361717</v>
       </c>
       <c r="K85" t="n">
-        <v>4.647643714064562</v>
+        <v>4.647643714059256</v>
       </c>
       <c r="L85" t="n">
-        <v>16.49087103004835</v>
+        <v>16.49087103006213</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>82.74406498369817</v>
+        <v>82.39882289205369</v>
       </c>
       <c r="B86" t="n">
         <v>0</v>
@@ -3693,36 +3693,36 @@
         <v>0</v>
       </c>
       <c r="D86" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="E86" t="n">
-        <v>7.837064168615004</v>
+        <v>7.816385858994765</v>
       </c>
       <c r="F86" t="n">
-        <v>6.173805682149561</v>
+        <v>6.190202294374796</v>
       </c>
       <c r="G86" t="n">
         <v>0.4</v>
       </c>
       <c r="H86" t="n">
-        <v>4.032194573316413</v>
+        <v>4.032194573311462</v>
       </c>
       <c r="I86" t="n">
-        <v>30.87773509975563</v>
+        <v>30.87773509978622</v>
       </c>
       <c r="J86" t="n">
         <v>0.3709916581317118</v>
       </c>
       <c r="K86" t="n">
-        <v>4.513984366932663</v>
+        <v>4.513984366888052</v>
       </c>
       <c r="L86" t="n">
-        <v>16.9937723594608</v>
+        <v>16.99377235958557</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>166.0517879422206</v>
+        <v>165.7065458472593</v>
       </c>
       <c r="B87" t="n">
         <v>0</v>
@@ -3731,36 +3731,36 @@
         <v>0</v>
       </c>
       <c r="D87" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="E87" t="n">
-        <v>7.837064168615006</v>
+        <v>7.816385858994765</v>
       </c>
       <c r="F87" t="n">
-        <v>6.173805682149551</v>
+        <v>6.190202294374796</v>
       </c>
       <c r="G87" t="n">
         <v>0.9</v>
       </c>
       <c r="H87" t="n">
-        <v>3.766543139479575</v>
+        <v>3.766543139479376</v>
       </c>
       <c r="I87" t="n">
-        <v>33.32612956190602</v>
+        <v>33.32612956190746</v>
       </c>
       <c r="J87" t="n">
         <v>0.9187962143520164</v>
       </c>
       <c r="K87" t="n">
-        <v>4.105149470269883</v>
+        <v>4.105149470270265</v>
       </c>
       <c r="L87" t="n">
-        <v>18.74609482972849</v>
+        <v>18.74609482972806</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>26.95810080577186</v>
+        <v>26.61285871079307</v>
       </c>
       <c r="B88" t="n">
         <v>0</v>
@@ -3769,36 +3769,36 @@
         <v>0</v>
       </c>
       <c r="D88" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="E88" t="n">
-        <v>7.837064168615006</v>
+        <v>7.816385858994765</v>
       </c>
       <c r="F88" t="n">
-        <v>6.173805682149535</v>
+        <v>6.190202294374796</v>
       </c>
       <c r="G88" t="n">
         <v>0.1247653346366633</v>
       </c>
       <c r="H88" t="n">
-        <v>4.30113035433284</v>
+        <v>4.301130354332836</v>
       </c>
       <c r="I88" t="n">
-        <v>28.7584817461739</v>
+        <v>28.75848174617392</v>
       </c>
       <c r="J88" t="n">
         <v>0.1</v>
       </c>
       <c r="K88" t="n">
-        <v>4.97788581859545</v>
+        <v>4.977885818595456</v>
       </c>
       <c r="L88" t="n">
-        <v>15.36877144665517</v>
+        <v>15.36877144665515</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>46.16249872225677</v>
+        <v>45.81725662732819</v>
       </c>
       <c r="B89" t="n">
         <v>0</v>
@@ -3807,36 +3807,36 @@
         <v>0</v>
       </c>
       <c r="D89" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="E89" t="n">
-        <v>7.837064168615009</v>
+        <v>7.816385858994765</v>
       </c>
       <c r="F89" t="n">
-        <v>6.17380568214955</v>
+        <v>6.190202294374796</v>
       </c>
       <c r="G89" t="n">
         <v>0.2063981465460308</v>
       </c>
       <c r="H89" t="n">
-        <v>4.203379562291722</v>
+        <v>4.203379562291457</v>
       </c>
       <c r="I89" t="n">
-        <v>29.49233359533105</v>
+        <v>29.49233359533257</v>
       </c>
       <c r="J89" t="n">
         <v>0.2</v>
       </c>
       <c r="K89" t="n">
-        <v>4.767998876531847</v>
+        <v>4.767998876531376</v>
       </c>
       <c r="L89" t="n">
-        <v>16.06318375226908</v>
+        <v>16.06318375227023</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>67.33349544284391</v>
+        <v>66.98825334876372</v>
       </c>
       <c r="B90" t="n">
         <v>0</v>
@@ -3845,36 +3845,36 @@
         <v>0</v>
       </c>
       <c r="D90" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="E90" t="n">
-        <v>7.837064168615006</v>
+        <v>7.816385858994765</v>
       </c>
       <c r="F90" t="n">
-        <v>6.17380568214953</v>
+        <v>6.190202294374796</v>
       </c>
       <c r="G90" t="n">
         <v>0.3137697936590399</v>
       </c>
       <c r="H90" t="n">
-        <v>4.100520633784759</v>
+        <v>4.100520633782343</v>
       </c>
       <c r="I90" t="n">
-        <v>30.30853986447131</v>
+        <v>30.30853986448574</v>
       </c>
       <c r="J90" t="n">
         <v>0.3</v>
       </c>
       <c r="K90" t="n">
-        <v>4.607184891544377</v>
+        <v>4.607184891533563</v>
       </c>
       <c r="L90" t="n">
-        <v>16.63988212863548</v>
+        <v>16.6398821286642</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>85.0636687663243</v>
+        <v>84.71842667617977</v>
       </c>
       <c r="B91" t="n">
         <v>0</v>
@@ -3883,36 +3883,36 @@
         <v>0</v>
       </c>
       <c r="D91" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="E91" t="n">
-        <v>7.837064168615007</v>
+        <v>7.816385858994765</v>
       </c>
       <c r="F91" t="n">
-        <v>6.173805682149577</v>
+        <v>6.190202294374796</v>
       </c>
       <c r="G91" t="n">
         <v>0.4026174994879254</v>
       </c>
       <c r="H91" t="n">
-        <v>4.030275883918499</v>
+        <v>4.030275883913485</v>
       </c>
       <c r="I91" t="n">
-        <v>30.89404689015254</v>
+        <v>30.89404689018355</v>
       </c>
       <c r="J91" t="n">
         <v>0.4</v>
       </c>
       <c r="K91" t="n">
-        <v>4.479934196712302</v>
+        <v>4.479934196644229</v>
       </c>
       <c r="L91" t="n">
-        <v>17.12690822717055</v>
+        <v>17.12690822736458</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>167.8955230012453</v>
+        <v>167.5502809062134</v>
       </c>
       <c r="B92" t="n">
         <v>0</v>
@@ -3921,36 +3921,36 @@
         <v>0</v>
       </c>
       <c r="D92" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="E92" t="n">
-        <v>7.837064168615009</v>
+        <v>7.816385858994765</v>
       </c>
       <c r="F92" t="n">
-        <v>6.173805682149546</v>
+        <v>6.190202294374796</v>
       </c>
       <c r="G92" t="n">
         <v>0.9261043454272662</v>
       </c>
       <c r="H92" t="n">
-        <v>3.756446993650572</v>
+        <v>3.756446993650445</v>
       </c>
       <c r="I92" t="n">
-        <v>33.42744356830013</v>
+        <v>33.42744356830105</v>
       </c>
       <c r="J92" t="n">
         <v>0.9</v>
       </c>
       <c r="K92" t="n">
-        <v>4.113852220027621</v>
+        <v>4.113852220028694</v>
       </c>
       <c r="L92" t="n">
-        <v>18.70496455751894</v>
+        <v>18.70496455751917</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>-1.332170215260652</v>
+        <v>1.020018131749682</v>
       </c>
       <c r="B93" t="n">
         <v>0</v>
@@ -3962,33 +3962,33 @@
         <v>0.1</v>
       </c>
       <c r="E93" t="n">
-        <v>6.881596036859921</v>
+        <v>6.881596026811036</v>
       </c>
       <c r="F93" t="n">
-        <v>7.035067073026371</v>
+        <v>7.035067081718426</v>
       </c>
       <c r="G93" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="H93" t="n">
-        <v>5.234362327483119</v>
+        <v>5.214169403139731</v>
       </c>
       <c r="I93" t="n">
-        <v>23.28719013923213</v>
+        <v>23.38272636825997</v>
       </c>
       <c r="J93" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="K93" t="n">
-        <v>6.114834605629476</v>
+        <v>6.075961143277834</v>
       </c>
       <c r="L93" t="n">
-        <v>12.45969049902896</v>
+        <v>12.5406999984345</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>-4.049495629541639</v>
+        <v>-1.697307066325474</v>
       </c>
       <c r="B94" t="n">
         <v>0</v>
@@ -4000,33 +4000,33 @@
         <v>0.2</v>
       </c>
       <c r="E94" t="n">
-        <v>6.766664235926038</v>
+        <v>6.766664235926021</v>
       </c>
       <c r="F94" t="n">
-        <v>7.155177451354792</v>
+        <v>7.155177451354807</v>
       </c>
       <c r="G94" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="H94" t="n">
-        <v>5.234362327483369</v>
+        <v>5.214169403139731</v>
       </c>
       <c r="I94" t="n">
-        <v>23.28719013922632</v>
+        <v>23.38272636825997</v>
       </c>
       <c r="J94" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="K94" t="n">
-        <v>6.114834605629451</v>
+        <v>6.075961143277834</v>
       </c>
       <c r="L94" t="n">
-        <v>12.45969049902891</v>
+        <v>12.5406999984345</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>-6.567710567833331</v>
+        <v>-4.215522003350283</v>
       </c>
       <c r="B95" t="n">
         <v>0</v>
@@ -4038,33 +4038,33 @@
         <v>0.3</v>
       </c>
       <c r="E95" t="n">
-        <v>6.676228233286731</v>
+        <v>6.676228233330201</v>
       </c>
       <c r="F95" t="n">
-        <v>7.252618752601803</v>
+        <v>7.252618752571579</v>
       </c>
       <c r="G95" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="H95" t="n">
-        <v>5.234362327482882</v>
+        <v>5.214169403139731</v>
       </c>
       <c r="I95" t="n">
-        <v>23.28719013923107</v>
+        <v>23.38272636825997</v>
       </c>
       <c r="J95" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="K95" t="n">
-        <v>6.114834605629484</v>
+        <v>6.075961143277834</v>
       </c>
       <c r="L95" t="n">
-        <v>12.45969049902886</v>
+        <v>12.5406999984345</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>-8.916920733186998</v>
+        <v>-6.564732169663835</v>
       </c>
       <c r="B96" t="n">
         <v>0</v>
@@ -4076,33 +4076,33 @@
         <v>0.4</v>
       </c>
       <c r="E96" t="n">
-        <v>6.602232654372989</v>
+        <v>6.602232654387998</v>
       </c>
       <c r="F96" t="n">
-        <v>7.334348027642058</v>
+        <v>7.334348027625503</v>
       </c>
       <c r="G96" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="H96" t="n">
-        <v>5.234362327480314</v>
+        <v>5.214169403139731</v>
       </c>
       <c r="I96" t="n">
-        <v>23.28719013923874</v>
+        <v>23.38272636825997</v>
       </c>
       <c r="J96" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="K96" t="n">
-        <v>6.114834605629428</v>
+        <v>6.075961143277834</v>
       </c>
       <c r="L96" t="n">
-        <v>12.45969049902893</v>
+        <v>12.5406999984345</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>-18.81803641830559</v>
+        <v>-16.4658479990678</v>
       </c>
       <c r="B97" t="n">
         <v>0</v>
@@ -4114,33 +4114,33 @@
         <v>0.9</v>
       </c>
       <c r="E97" t="n">
-        <v>6.361184206158725</v>
+        <v>6.361184203248474</v>
       </c>
       <c r="F97" t="n">
-        <v>7.61389014162499</v>
+        <v>7.613890144470962</v>
       </c>
       <c r="G97" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="H97" t="n">
-        <v>5.234362327481742</v>
+        <v>5.214169403139731</v>
       </c>
       <c r="I97" t="n">
-        <v>23.28719013923457</v>
+        <v>23.38272636825997</v>
       </c>
       <c r="J97" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="K97" t="n">
-        <v>6.114834605629454</v>
+        <v>6.075961143277834</v>
       </c>
       <c r="L97" t="n">
-        <v>12.45969049902894</v>
+        <v>12.5406999984345</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>26.3347781324589</v>
+        <v>26.02701687370779</v>
       </c>
       <c r="B98" t="n">
         <v>0</v>
@@ -4149,36 +4149,36 @@
         <v>10</v>
       </c>
       <c r="D98" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="E98" t="n">
-        <v>7.036525823518705</v>
+        <v>7.018486110311152</v>
       </c>
       <c r="F98" t="n">
-        <v>6.87941216104238</v>
+        <v>6.897180206819828</v>
       </c>
       <c r="G98" t="n">
         <v>0.1</v>
       </c>
       <c r="H98" t="n">
-        <v>5.052738297533373</v>
+        <v>5.052738297533362</v>
       </c>
       <c r="I98" t="n">
-        <v>24.17662715341194</v>
+        <v>24.17662715341197</v>
       </c>
       <c r="J98" t="n">
         <v>0.1082177012392873</v>
       </c>
       <c r="K98" t="n">
-        <v>5.756026313118035</v>
+        <v>5.756026313117852</v>
       </c>
       <c r="L98" t="n">
-        <v>13.25008811295539</v>
+        <v>13.2500881129557</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>47.70273922685402</v>
+        <v>47.3949779700708</v>
       </c>
       <c r="B99" t="n">
         <v>0</v>
@@ -4187,36 +4187,36 @@
         <v>10</v>
       </c>
       <c r="D99" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="E99" t="n">
-        <v>7.036525823518714</v>
+        <v>7.018486110311152</v>
       </c>
       <c r="F99" t="n">
-        <v>6.879412161042475</v>
+        <v>6.897180206819828</v>
       </c>
       <c r="G99" t="n">
         <v>0.2</v>
       </c>
       <c r="H99" t="n">
-        <v>4.910237968469831</v>
+        <v>4.910237968459861</v>
       </c>
       <c r="I99" t="n">
-        <v>24.92531420114917</v>
+        <v>24.92531420119132</v>
       </c>
       <c r="J99" t="n">
         <v>0.1861872028258322</v>
       </c>
       <c r="K99" t="n">
-        <v>5.569182817693894</v>
+        <v>5.569182817673008</v>
       </c>
       <c r="L99" t="n">
-        <v>13.70314677153784</v>
+        <v>13.70314677157595</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>69.52887248711305</v>
+        <v>69.22111128970806</v>
       </c>
       <c r="B100" t="n">
         <v>0</v>
@@ -4225,36 +4225,36 @@
         <v>10</v>
       </c>
       <c r="D100" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="E100" t="n">
-        <v>7.036525823518712</v>
+        <v>7.018486110311152</v>
       </c>
       <c r="F100" t="n">
-        <v>6.879412161042444</v>
+        <v>6.897180206819828</v>
       </c>
       <c r="G100" t="n">
         <v>0.3</v>
       </c>
       <c r="H100" t="n">
-        <v>4.79368044446063</v>
+        <v>4.793680444063268</v>
       </c>
       <c r="I100" t="n">
-        <v>25.57445800156761</v>
+        <v>25.57445800335086</v>
       </c>
       <c r="J100" t="n">
         <v>0.2724584114361717</v>
       </c>
       <c r="K100" t="n">
-        <v>5.40420435075646</v>
+        <v>5.40420435056613</v>
       </c>
       <c r="L100" t="n">
-        <v>14.13002829260942</v>
+        <v>14.13002829297247</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>91.57591160279111</v>
+        <v>91.26815061829494</v>
       </c>
       <c r="B101" t="n">
         <v>0</v>
@@ -4263,36 +4263,36 @@
         <v>10</v>
       </c>
       <c r="D101" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="E101" t="n">
-        <v>7.036525823518714</v>
+        <v>7.018486110311152</v>
       </c>
       <c r="F101" t="n">
-        <v>6.879412161042461</v>
+        <v>6.897180206819828</v>
       </c>
       <c r="G101" t="n">
         <v>0.4</v>
       </c>
       <c r="H101" t="n">
-        <v>4.698669450636105</v>
+        <v>4.698669449010319</v>
       </c>
       <c r="I101" t="n">
-        <v>26.13021459058483</v>
+        <v>26.13021459814601</v>
       </c>
       <c r="J101" t="n">
         <v>0.3709916581317118</v>
       </c>
       <c r="K101" t="n">
-        <v>5.250672918035882</v>
+        <v>5.250672917570395</v>
       </c>
       <c r="L101" t="n">
-        <v>14.55217543507356</v>
+        <v>14.55217543600214</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>195.7697901556399</v>
+        <v>195.4620289595605</v>
       </c>
       <c r="B102" t="n">
         <v>0</v>
@@ -4301,36 +4301,36 @@
         <v>10</v>
       </c>
       <c r="D102" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="E102" t="n">
-        <v>7.036525823518707</v>
+        <v>7.018486110311152</v>
       </c>
       <c r="F102" t="n">
-        <v>6.879412161042403</v>
+        <v>6.897180206819828</v>
       </c>
       <c r="G102" t="n">
         <v>0.9</v>
       </c>
       <c r="H102" t="n">
-        <v>4.38980042756626</v>
+        <v>4.389800427329819</v>
       </c>
       <c r="I102" t="n">
-        <v>28.12523679037497</v>
+        <v>28.12523679160584</v>
       </c>
       <c r="J102" t="n">
         <v>0.9187962143520164</v>
       </c>
       <c r="K102" t="n">
-        <v>4.713439010305819</v>
+        <v>4.713439010275775</v>
       </c>
       <c r="L102" t="n">
-        <v>16.25424305335354</v>
+        <v>16.25424305342956</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>28.98896336111157</v>
+        <v>28.68120210236684</v>
       </c>
       <c r="B103" t="n">
         <v>0</v>
@@ -4339,36 +4339,36 @@
         <v>10</v>
       </c>
       <c r="D103" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="E103" t="n">
-        <v>7.036525823518709</v>
+        <v>7.018486110311152</v>
       </c>
       <c r="F103" t="n">
-        <v>6.879412161042465</v>
+        <v>6.897180206819828</v>
       </c>
       <c r="G103" t="n">
         <v>0.1247653346366633</v>
       </c>
       <c r="H103" t="n">
-        <v>5.01422572594895</v>
+        <v>5.014225725948836</v>
       </c>
       <c r="I103" t="n">
-        <v>24.37434002473972</v>
+        <v>24.37434002474019</v>
       </c>
       <c r="J103" t="n">
         <v>0.1</v>
       </c>
       <c r="K103" t="n">
-        <v>5.778561248032207</v>
+        <v>5.778561248032124</v>
       </c>
       <c r="L103" t="n">
-        <v>13.19748050013087</v>
+        <v>13.19748050013101</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>49.86104721299763</v>
+        <v>49.553286340974</v>
       </c>
       <c r="B104" t="n">
         <v>0</v>
@@ -4377,36 +4377,36 @@
         <v>10</v>
       </c>
       <c r="D104" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="E104" t="n">
-        <v>7.036525823518712</v>
+        <v>7.018486110311152</v>
       </c>
       <c r="F104" t="n">
-        <v>6.879412161042437</v>
+        <v>6.897180206819828</v>
       </c>
       <c r="G104" t="n">
         <v>0.2063981465460308</v>
       </c>
       <c r="H104" t="n">
-        <v>4.902195711593977</v>
+        <v>4.902195708024901</v>
       </c>
       <c r="I104" t="n">
-        <v>24.96900398019946</v>
+        <v>24.96900399412197</v>
       </c>
       <c r="J104" t="n">
         <v>0.2</v>
       </c>
       <c r="K104" t="n">
-        <v>5.540289473033623</v>
+        <v>5.540289472999258</v>
       </c>
       <c r="L104" t="n">
-        <v>13.77601630590739</v>
+        <v>13.77601630597057</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>73.82948992900836</v>
+        <v>73.52172875402445</v>
       </c>
       <c r="B105" t="n">
         <v>0</v>
@@ -4415,36 +4415,36 @@
         <v>10</v>
       </c>
       <c r="D105" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="E105" t="n">
-        <v>7.036525823518715</v>
+        <v>7.018486110311152</v>
       </c>
       <c r="F105" t="n">
-        <v>6.879412161042478</v>
+        <v>6.897180206819828</v>
       </c>
       <c r="G105" t="n">
         <v>0.3137697936590399</v>
       </c>
       <c r="H105" t="n">
-        <v>4.77947872864197</v>
+        <v>4.779478728122665</v>
       </c>
       <c r="I105" t="n">
-        <v>25.65596181732001</v>
+        <v>25.65596181966311</v>
       </c>
       <c r="J105" t="n">
         <v>0.3</v>
       </c>
       <c r="K105" t="n">
-        <v>5.358158620144747</v>
+        <v>5.358158619868684</v>
       </c>
       <c r="L105" t="n">
-        <v>14.25401270430056</v>
+        <v>14.25401270483395</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>94.33705261420045</v>
+        <v>94.02929163974291</v>
       </c>
       <c r="B106" t="n">
         <v>0</v>
@@ -4453,36 +4453,36 @@
         <v>10</v>
       </c>
       <c r="D106" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="E106" t="n">
-        <v>7.036525823518712</v>
+        <v>7.018486110311152</v>
       </c>
       <c r="F106" t="n">
-        <v>6.879412161042652</v>
+        <v>6.897180206819828</v>
       </c>
       <c r="G106" t="n">
         <v>0.4026174994879254</v>
       </c>
       <c r="H106" t="n">
-        <v>4.696410910174029</v>
+        <v>4.696410908511605</v>
       </c>
       <c r="I106" t="n">
-        <v>26.14373195327786</v>
+        <v>26.14373196101593</v>
       </c>
       <c r="J106" t="n">
         <v>0.4</v>
       </c>
       <c r="K106" t="n">
-        <v>5.210672537910126</v>
+        <v>5.210672537404371</v>
       </c>
       <c r="L106" t="n">
-        <v>14.66638237813966</v>
+        <v>14.66638237916164</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>197.5197333722272</v>
+        <v>197.2119721576904</v>
       </c>
       <c r="B107" t="n">
         <v>0</v>
@@ -4491,36 +4491,36 @@
         <v>10</v>
       </c>
       <c r="D107" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="E107" t="n">
-        <v>7.036525823518712</v>
+        <v>7.018486110311152</v>
       </c>
       <c r="F107" t="n">
-        <v>6.879412161042471</v>
+        <v>6.897180206819828</v>
       </c>
       <c r="G107" t="n">
         <v>0.9261043454272662</v>
       </c>
       <c r="H107" t="n">
-        <v>4.378071981065517</v>
+        <v>4.378071980907347</v>
       </c>
       <c r="I107" t="n">
-        <v>28.20731119596918</v>
+        <v>28.20731119679619</v>
       </c>
       <c r="J107" t="n">
         <v>0.9</v>
       </c>
       <c r="K107" t="n">
-        <v>4.726652454008947</v>
+        <v>4.726652453973265</v>
       </c>
       <c r="L107" t="n">
-        <v>16.20755001913632</v>
+        <v>16.20755001922588</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>6.83478003555356</v>
+        <v>8.521826159520957</v>
       </c>
       <c r="B108" t="n">
         <v>0</v>
@@ -4532,33 +4532,33 @@
         <v>0.1</v>
       </c>
       <c r="E108" t="n">
-        <v>6.12849793740546</v>
+        <v>6.12849793735711</v>
       </c>
       <c r="F108" t="n">
-        <v>7.904787369195323</v>
+        <v>7.904787369243286</v>
       </c>
       <c r="G108" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="H108" t="n">
-        <v>5.846909926368639</v>
+        <v>5.832934107637366</v>
       </c>
       <c r="I108" t="n">
-        <v>20.72742782212946</v>
+        <v>20.77938630677823</v>
       </c>
       <c r="J108" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="K108" t="n">
-        <v>6.810947385901413</v>
+        <v>6.780674446288424</v>
       </c>
       <c r="L108" t="n">
-        <v>11.16889058380164</v>
+        <v>11.21940087182564</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>5.27458349120156</v>
+        <v>6.961629613550096</v>
       </c>
       <c r="B109" t="n">
         <v>0</v>
@@ -4570,33 +4570,33 @@
         <v>0.2</v>
       </c>
       <c r="E109" t="n">
-        <v>6.054000358603711</v>
+        <v>6.054000358518357</v>
       </c>
       <c r="F109" t="n">
-        <v>8.002693397328384</v>
+        <v>8.002693397418568</v>
       </c>
       <c r="G109" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="H109" t="n">
-        <v>5.846909926368784</v>
+        <v>5.832934107637366</v>
       </c>
       <c r="I109" t="n">
-        <v>20.72742782212904</v>
+        <v>20.77938630677823</v>
       </c>
       <c r="J109" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="K109" t="n">
-        <v>6.810947385874167</v>
+        <v>6.780674446288424</v>
       </c>
       <c r="L109" t="n">
-        <v>11.16889058380461</v>
+        <v>11.21940087182564</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>3.910921536759576</v>
+        <v>5.597967660088427</v>
       </c>
       <c r="B110" t="n">
         <v>0</v>
@@ -4608,33 +4608,33 @@
         <v>0.3</v>
       </c>
       <c r="E110" t="n">
-        <v>5.995457690830439</v>
+        <v>5.995457690828007</v>
       </c>
       <c r="F110" t="n">
-        <v>8.081355488716024</v>
+        <v>8.081355488654909</v>
       </c>
       <c r="G110" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="H110" t="n">
-        <v>5.846909926366481</v>
+        <v>5.832934107637366</v>
       </c>
       <c r="I110" t="n">
-        <v>20.72742782213567</v>
+        <v>20.77938630677823</v>
       </c>
       <c r="J110" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="K110" t="n">
-        <v>6.81094738586947</v>
+        <v>6.780674446288424</v>
       </c>
       <c r="L110" t="n">
-        <v>11.1688905838009</v>
+        <v>11.21940087182564</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>2.692555536037152</v>
+        <v>4.379601661243163</v>
       </c>
       <c r="B111" t="n">
         <v>0</v>
@@ -4646,33 +4646,33 @@
         <v>0.4</v>
       </c>
       <c r="E111" t="n">
-        <v>5.947428973040716</v>
+        <v>5.947428973039433</v>
       </c>
       <c r="F111" t="n">
-        <v>8.147058427425241</v>
+        <v>8.147058427426614</v>
       </c>
       <c r="G111" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="H111" t="n">
-        <v>5.846909926368788</v>
+        <v>5.832934107637366</v>
       </c>
       <c r="I111" t="n">
-        <v>20.72742782212903</v>
+        <v>20.77938630677823</v>
       </c>
       <c r="J111" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="K111" t="n">
-        <v>6.81094738590721</v>
+        <v>6.780674446288424</v>
       </c>
       <c r="L111" t="n">
-        <v>11.16889058379658</v>
+        <v>11.21940087182564</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>-2.079471919994657</v>
+        <v>-0.3924258008316648</v>
       </c>
       <c r="B112" t="n">
         <v>0</v>
@@ -4684,33 +4684,33 @@
         <v>0.9</v>
       </c>
       <c r="E112" t="n">
-        <v>5.788470958957248</v>
+        <v>5.788470958807561</v>
       </c>
       <c r="F112" t="n">
-        <v>8.372370077823833</v>
+        <v>8.372370077978616</v>
       </c>
       <c r="G112" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="H112" t="n">
-        <v>5.846909926359956</v>
+        <v>5.832934107637366</v>
       </c>
       <c r="I112" t="n">
-        <v>20.72742782230031</v>
+        <v>20.77938630677823</v>
       </c>
       <c r="J112" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="K112" t="n">
-        <v>6.81094738588172</v>
+        <v>6.780674446288424</v>
       </c>
       <c r="L112" t="n">
-        <v>11.16889058380803</v>
+        <v>11.21940087182564</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>27.62637003434565</v>
+        <v>27.42537677968953</v>
       </c>
       <c r="B113" t="n">
         <v>0</v>
@@ -4719,36 +4719,36 @@
         <v>20</v>
       </c>
       <c r="D113" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="E113" t="n">
-        <v>6.229814680542388</v>
+        <v>6.217938888403745</v>
       </c>
       <c r="F113" t="n">
-        <v>7.775428450084746</v>
+        <v>7.790371035946718</v>
       </c>
       <c r="G113" t="n">
         <v>0.1</v>
       </c>
       <c r="H113" t="n">
-        <v>5.709722682678406</v>
+        <v>5.709722682678386</v>
       </c>
       <c r="I113" t="n">
-        <v>21.24927763819725</v>
+        <v>21.24927763819731</v>
       </c>
       <c r="J113" t="n">
         <v>0.1082177012392873</v>
       </c>
       <c r="K113" t="n">
-        <v>6.501604554939219</v>
+        <v>6.501604554939074</v>
       </c>
       <c r="L113" t="n">
-        <v>11.70764336776432</v>
+        <v>11.70764336776452</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>45.98878045746655</v>
+        <v>45.78778720869278</v>
       </c>
       <c r="B114" t="n">
         <v>0</v>
@@ -4757,36 +4757,36 @@
         <v>20</v>
       </c>
       <c r="D114" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="E114" t="n">
-        <v>6.229814680542374</v>
+        <v>6.217938888403745</v>
       </c>
       <c r="F114" t="n">
-        <v>7.775428450084835</v>
+        <v>7.790371035946718</v>
       </c>
       <c r="G114" t="n">
         <v>0.2</v>
       </c>
       <c r="H114" t="n">
-        <v>5.582196107608262</v>
+        <v>5.582196107591927</v>
       </c>
       <c r="I114" t="n">
-        <v>21.75916478669934</v>
+        <v>21.75916478675279</v>
       </c>
       <c r="J114" t="n">
         <v>0.1861872028258322</v>
       </c>
       <c r="K114" t="n">
-        <v>6.311575079575875</v>
+        <v>6.311575079468875</v>
       </c>
       <c r="L114" t="n">
-        <v>12.06536120701534</v>
+        <v>12.06536120717306</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>66.10333155687472</v>
+        <v>65.90233873782385</v>
       </c>
       <c r="B115" t="n">
         <v>0</v>
@@ -4795,36 +4795,36 @@
         <v>20</v>
       </c>
       <c r="D115" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="E115" t="n">
-        <v>6.229814680542418</v>
+        <v>6.217938888403745</v>
       </c>
       <c r="F115" t="n">
-        <v>7.775428450084294</v>
+        <v>7.790371035946718</v>
       </c>
       <c r="G115" t="n">
         <v>0.3</v>
       </c>
       <c r="H115" t="n">
-        <v>5.467817013843058</v>
+        <v>5.467817012509648</v>
       </c>
       <c r="I115" t="n">
-        <v>22.23836450104408</v>
+        <v>22.23836450566074</v>
       </c>
       <c r="J115" t="n">
         <v>0.2724584114361717</v>
       </c>
       <c r="K115" t="n">
-        <v>6.134000054261064</v>
+        <v>6.134000048372424</v>
       </c>
       <c r="L115" t="n">
-        <v>12.42013818746445</v>
+        <v>12.42013819667018</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>87.92605840786152</v>
+        <v>87.72506642034367</v>
       </c>
       <c r="B116" t="n">
         <v>0</v>
@@ -4833,36 +4833,36 @@
         <v>20</v>
       </c>
       <c r="D116" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="E116" t="n">
-        <v>6.229814680542386</v>
+        <v>6.217938888403745</v>
       </c>
       <c r="F116" t="n">
-        <v>7.775428450084768</v>
+        <v>7.790371035946718</v>
       </c>
       <c r="G116" t="n">
         <v>0.4</v>
       </c>
       <c r="H116" t="n">
-        <v>5.366971155165527</v>
+        <v>5.366971146818214</v>
       </c>
       <c r="I116" t="n">
-        <v>22.67925293210364</v>
+        <v>22.67925296216602</v>
       </c>
       <c r="J116" t="n">
         <v>0.3709916581317118</v>
       </c>
       <c r="K116" t="n">
-        <v>5.961526264742172</v>
+        <v>5.961526262379339</v>
       </c>
       <c r="L116" t="n">
-        <v>12.7854621545966</v>
+        <v>12.78546215836327</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>197.7580452424492</v>
+        <v>197.5570533390402</v>
       </c>
       <c r="B117" t="n">
         <v>0</v>
@@ -4871,36 +4871,36 @@
         <v>20</v>
       </c>
       <c r="D117" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="E117" t="n">
-        <v>6.229814680542383</v>
+        <v>6.217938888403745</v>
       </c>
       <c r="F117" t="n">
-        <v>7.775428450084793</v>
+        <v>7.790371035946718</v>
       </c>
       <c r="G117" t="n">
         <v>0.9</v>
       </c>
       <c r="H117" t="n">
-        <v>5.013853272390429</v>
+        <v>5.013853268482669</v>
       </c>
       <c r="I117" t="n">
-        <v>24.3762684444245</v>
+        <v>24.37626846057814</v>
       </c>
       <c r="J117" t="n">
         <v>0.9187962143520164</v>
       </c>
       <c r="K117" t="n">
-        <v>5.375148878582295</v>
+        <v>5.375148874322531</v>
       </c>
       <c r="L117" t="n">
-        <v>14.20800890067436</v>
+        <v>14.20800890827437</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>29.59676576433829</v>
+        <v>29.39577250968836</v>
       </c>
       <c r="B118" t="n">
         <v>0</v>
@@ -4909,36 +4909,36 @@
         <v>20</v>
       </c>
       <c r="D118" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="E118" t="n">
-        <v>6.229814680542413</v>
+        <v>6.217938888403745</v>
       </c>
       <c r="F118" t="n">
-        <v>7.775428450084306</v>
+        <v>7.790371035946718</v>
       </c>
       <c r="G118" t="n">
         <v>0.1247653346366633</v>
       </c>
       <c r="H118" t="n">
-        <v>5.677040887610817</v>
+        <v>5.677040887610683</v>
       </c>
       <c r="I118" t="n">
-        <v>21.37759753844516</v>
+        <v>21.37759753844557</v>
       </c>
       <c r="J118" t="n">
         <v>0.1</v>
       </c>
       <c r="K118" t="n">
-        <v>6.523361592502427</v>
+        <v>6.523361592502377</v>
       </c>
       <c r="L118" t="n">
-        <v>11.66804559417192</v>
+        <v>11.66804559417198</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>48.00714090231396</v>
+        <v>47.80614766007277</v>
       </c>
       <c r="B119" t="n">
         <v>0</v>
@@ -4947,36 +4947,36 @@
         <v>20</v>
       </c>
       <c r="D119" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="E119" t="n">
-        <v>6.229814680542411</v>
+        <v>6.217938888403745</v>
       </c>
       <c r="F119" t="n">
-        <v>7.775428450084238</v>
+        <v>7.790371035946718</v>
       </c>
       <c r="G119" t="n">
         <v>0.2063981465460308</v>
       </c>
       <c r="H119" t="n">
-        <v>5.574467231081984</v>
+        <v>5.574467231059043</v>
       </c>
       <c r="I119" t="n">
-        <v>21.79087610485097</v>
+        <v>21.79087610492635</v>
       </c>
       <c r="J119" t="n">
         <v>0.2</v>
       </c>
       <c r="K119" t="n">
-        <v>6.28095394305458</v>
+        <v>6.280953942809113</v>
       </c>
       <c r="L119" t="n">
-        <v>12.12507452459397</v>
+        <v>12.12507452495973</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>70.34975053170132</v>
+        <v>70.14875797500528</v>
       </c>
       <c r="B120" t="n">
         <v>0</v>
@@ -4985,36 +4985,36 @@
         <v>20</v>
       </c>
       <c r="D120" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="E120" t="n">
-        <v>6.229814680542418</v>
+        <v>6.217938888403745</v>
       </c>
       <c r="F120" t="n">
-        <v>7.775428450084251</v>
+        <v>7.790371035946718</v>
       </c>
       <c r="G120" t="n">
         <v>0.3137697936590399</v>
       </c>
       <c r="H120" t="n">
-        <v>5.453144591001646</v>
+        <v>5.453144588869441</v>
       </c>
       <c r="I120" t="n">
-        <v>22.30141150939633</v>
+        <v>22.30141151682902</v>
       </c>
       <c r="J120" t="n">
         <v>0.3</v>
       </c>
       <c r="K120" t="n">
-        <v>6.083014358417758</v>
+        <v>6.083014349533672</v>
       </c>
       <c r="L120" t="n">
-        <v>12.52592282596257</v>
+        <v>12.52592283997302</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>90.85820507636862</v>
+        <v>90.65721367917203</v>
       </c>
       <c r="B121" t="n">
         <v>0</v>
@@ -5023,36 +5023,36 @@
         <v>20</v>
       </c>
       <c r="D121" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="E121" t="n">
-        <v>6.229814680542388</v>
+        <v>6.217938888403745</v>
       </c>
       <c r="F121" t="n">
-        <v>7.775428450084751</v>
+        <v>7.790371035946718</v>
       </c>
       <c r="G121" t="n">
         <v>0.4026174994879254</v>
       </c>
       <c r="H121" t="n">
-        <v>5.364503824148882</v>
+        <v>5.364503815816291</v>
       </c>
       <c r="I121" t="n">
-        <v>22.69026561983405</v>
+        <v>22.69026564987563</v>
       </c>
       <c r="J121" t="n">
         <v>0.4</v>
       </c>
       <c r="K121" t="n">
-        <v>5.916680425885118</v>
+        <v>5.916680413614788</v>
       </c>
       <c r="L121" t="n">
-        <v>12.8840308499487</v>
+        <v>12.88403087011925</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>199.6739991890056</v>
+        <v>199.4730073171624</v>
       </c>
       <c r="B122" t="n">
         <v>0</v>
@@ -5061,36 +5061,36 @@
         <v>20</v>
       </c>
       <c r="D122" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="E122" t="n">
-        <v>6.229814680542413</v>
+        <v>6.217938888403745</v>
       </c>
       <c r="F122" t="n">
-        <v>7.77542845008428</v>
+        <v>7.790371035946718</v>
       </c>
       <c r="G122" t="n">
         <v>0.9261043454272662</v>
       </c>
       <c r="H122" t="n">
-        <v>5.000219964684943</v>
+        <v>5.000219960714348</v>
       </c>
       <c r="I122" t="n">
-        <v>24.44707451116664</v>
+        <v>24.44707452766097</v>
       </c>
       <c r="J122" t="n">
         <v>0.9</v>
       </c>
       <c r="K122" t="n">
-        <v>5.389450425310831</v>
+        <v>5.38945042103501</v>
       </c>
       <c r="L122" t="n">
-        <v>14.16951723042999</v>
+        <v>14.16951723804407</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>20.77610213266333</v>
+        <v>20.4308600377757</v>
       </c>
       <c r="B123" t="n">
         <v>90</v>
@@ -5099,36 +5099,36 @@
         <v>0</v>
       </c>
       <c r="D123" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="E123" t="n">
-        <v>7.837064168615002</v>
+        <v>7.816385858994759</v>
       </c>
       <c r="F123" t="n">
-        <v>6.173805682149559</v>
+        <v>6.190202294374801</v>
       </c>
       <c r="G123" t="n">
         <v>0.1189512132472919</v>
       </c>
       <c r="H123" t="n">
-        <v>4.308972894003879</v>
+        <v>4.308972894003873</v>
       </c>
       <c r="I123" t="n">
-        <v>28.70126676014912</v>
+        <v>28.70126676014916</v>
       </c>
       <c r="J123" t="n">
         <v>0.1</v>
       </c>
       <c r="K123" t="n">
-        <v>3.770437980766414</v>
+        <v>3.770437980763477</v>
       </c>
       <c r="L123" t="n">
-        <v>20.4814558693205</v>
+        <v>20.48145586932859</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>30.26703441387749</v>
+        <v>29.92179231890644</v>
       </c>
       <c r="B124" t="n">
         <v>90</v>
@@ -5137,36 +5137,36 @@
         <v>0</v>
       </c>
       <c r="D124" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="E124" t="n">
-        <v>7.837064168614999</v>
+        <v>7.816385858994759</v>
       </c>
       <c r="F124" t="n">
-        <v>6.173805682149541</v>
+        <v>6.190202294374801</v>
       </c>
       <c r="G124" t="n">
         <v>0.1701643100102089</v>
       </c>
       <c r="H124" t="n">
-        <v>4.244175767458285</v>
+        <v>4.244175767458215</v>
       </c>
       <c r="I124" t="n">
-        <v>29.1813113645</v>
+        <v>29.1813113645004</v>
       </c>
       <c r="J124" t="n">
         <v>0.2</v>
       </c>
       <c r="K124" t="n">
-        <v>3.688256945374647</v>
+        <v>3.688256945374635</v>
       </c>
       <c r="L124" t="n">
-        <v>20.95905522000981</v>
+        <v>20.95905522000982</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>51.19915313046097</v>
+        <v>50.85391103597514</v>
       </c>
       <c r="B125" t="n">
         <v>90</v>
@@ -5175,36 +5175,36 @@
         <v>0</v>
       </c>
       <c r="D125" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="E125" t="n">
-        <v>7.837064168615</v>
+        <v>7.816385858994759</v>
       </c>
       <c r="F125" t="n">
-        <v>6.173805682149554</v>
+        <v>6.190202294374801</v>
       </c>
       <c r="G125" t="n">
         <v>0.3214442565952542</v>
       </c>
       <c r="H125" t="n">
-        <v>4.093997882615534</v>
+        <v>4.093997882612885</v>
       </c>
       <c r="I125" t="n">
-        <v>30.36191609374881</v>
+        <v>30.36191609376469</v>
       </c>
       <c r="J125" t="n">
         <v>0.3</v>
       </c>
       <c r="K125" t="n">
-        <v>3.630536246129323</v>
+        <v>3.6305362461251</v>
       </c>
       <c r="L125" t="n">
-        <v>21.30839062991482</v>
+        <v>21.30839063000439</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>58.88742559902227</v>
+        <v>58.54218328657098</v>
       </c>
       <c r="B126" t="n">
         <v>90</v>
@@ -5213,36 +5213,36 @@
         <v>0</v>
       </c>
       <c r="D126" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="E126" t="n">
-        <v>7.837064168615</v>
+        <v>7.816385858994759</v>
       </c>
       <c r="F126" t="n">
-        <v>6.173805682149554</v>
+        <v>6.190202294374801</v>
       </c>
       <c r="G126" t="n">
         <v>0.3720151345183279</v>
       </c>
       <c r="H126" t="n">
-        <v>4.053242978902857</v>
+        <v>4.053242978898653</v>
       </c>
       <c r="I126" t="n">
-        <v>30.69998519193065</v>
+        <v>30.69998519195634</v>
       </c>
       <c r="J126" t="n">
         <v>0.4</v>
       </c>
       <c r="K126" t="n">
-        <v>3.586463213376665</v>
+        <v>3.586463201325808</v>
       </c>
       <c r="L126" t="n">
-        <v>21.58328154599474</v>
+        <v>21.58328153292529</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>122.9848839960663</v>
+        <v>122.6396419643746</v>
       </c>
       <c r="B127" t="n">
         <v>90</v>
@@ -5251,36 +5251,36 @@
         <v>0</v>
       </c>
       <c r="D127" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="E127" t="n">
-        <v>7.837064168615002</v>
+        <v>7.816385858994759</v>
       </c>
       <c r="F127" t="n">
-        <v>6.173805682149539</v>
+        <v>6.190202294374801</v>
       </c>
       <c r="G127" t="n">
         <v>0.9137793267857967</v>
       </c>
       <c r="H127" t="n">
-        <v>3.761181232691152</v>
+        <v>3.761181232690995</v>
       </c>
       <c r="I127" t="n">
-        <v>33.37985343681326</v>
+        <v>33.37985343681439</v>
       </c>
       <c r="J127" t="n">
         <v>0.9</v>
       </c>
       <c r="K127" t="n">
-        <v>3.45374127260206</v>
+        <v>3.453741261201504</v>
       </c>
       <c r="L127" t="n">
-        <v>22.45695698889998</v>
+        <v>22.45695708958642</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>1.835788085108026</v>
+        <v>1.479819226903291</v>
       </c>
       <c r="B128" t="n">
         <v>90</v>
@@ -5289,36 +5289,36 @@
         <v>-25</v>
       </c>
       <c r="D128" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="E128" t="n">
-        <v>9.699347069291379</v>
+        <v>9.674792499509962</v>
       </c>
       <c r="F128" t="n">
-        <v>4.985069224042773</v>
+        <v>4.997753447165163</v>
       </c>
       <c r="G128" t="n">
         <v>0.1189512132472919</v>
       </c>
       <c r="H128" t="n">
-        <v>2.681662652128345</v>
+        <v>2.681662652128343</v>
       </c>
       <c r="I128" t="n">
-        <v>50.50392244784169</v>
+        <v>50.50392244784171</v>
       </c>
       <c r="J128" t="n">
         <v>0.1</v>
       </c>
       <c r="K128" t="n">
-        <v>1.90837928704069</v>
+        <v>1.90837928704039</v>
       </c>
       <c r="L128" t="n">
-        <v>43.73432903617852</v>
+        <v>43.73432903617801</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>2.634739230834278</v>
+        <v>2.278770424542715</v>
       </c>
       <c r="B129" t="n">
         <v>90</v>
@@ -5327,36 +5327,36 @@
         <v>-25</v>
       </c>
       <c r="D129" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="E129" t="n">
-        <v>9.699347069291399</v>
+        <v>9.674792499509962</v>
       </c>
       <c r="F129" t="n">
-        <v>4.985069224042785</v>
+        <v>4.997753447165163</v>
       </c>
       <c r="G129" t="n">
         <v>0.1701643100102089</v>
       </c>
       <c r="H129" t="n">
-        <v>2.675665367384082</v>
+        <v>2.675665367383425</v>
       </c>
       <c r="I129" t="n">
-        <v>50.65999279091609</v>
+        <v>50.65999279092375</v>
       </c>
       <c r="J129" t="n">
         <v>0.2</v>
       </c>
       <c r="K129" t="n">
-        <v>1.904998512780959</v>
+        <v>1.904998511383552</v>
       </c>
       <c r="L129" t="n">
-        <v>43.83169431849718</v>
+        <v>43.83169431566786</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>4.564451747724794</v>
+        <v>4.208482904155056</v>
       </c>
       <c r="B130" t="n">
         <v>90</v>
@@ -5365,36 +5365,36 @@
         <v>-25</v>
       </c>
       <c r="D130" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="E130" t="n">
-        <v>9.699347069291395</v>
+        <v>9.674792499509962</v>
       </c>
       <c r="F130" t="n">
-        <v>4.985069224042761</v>
+        <v>4.997753447165163</v>
       </c>
       <c r="G130" t="n">
         <v>0.3214442565952542</v>
       </c>
       <c r="H130" t="n">
-        <v>2.659988679030274</v>
+        <v>2.659988678897837</v>
       </c>
       <c r="I130" t="n">
-        <v>51.07378872710795</v>
+        <v>51.07378872950585</v>
       </c>
       <c r="J130" t="n">
         <v>0.3</v>
       </c>
       <c r="K130" t="n">
-        <v>1.90166973875314</v>
+        <v>1.901669738753147</v>
       </c>
       <c r="L130" t="n">
-        <v>43.92805650531964</v>
+        <v>43.92805650531956</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>5.247608665200418</v>
+        <v>4.8916398429132</v>
       </c>
       <c r="B131" t="n">
         <v>90</v>
@@ -5403,36 +5403,36 @@
         <v>-25</v>
       </c>
       <c r="D131" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="E131" t="n">
-        <v>9.69934706929139</v>
+        <v>9.674792499509962</v>
       </c>
       <c r="F131" t="n">
-        <v>4.985069224042777</v>
+        <v>4.997753447165163</v>
       </c>
       <c r="G131" t="n">
         <v>0.3720151345183279</v>
       </c>
       <c r="H131" t="n">
-        <v>2.655296704660302</v>
+        <v>2.655296704350982</v>
       </c>
       <c r="I131" t="n">
-        <v>51.19931357277207</v>
+        <v>51.19931357927751</v>
       </c>
       <c r="J131" t="n">
         <v>0.4</v>
       </c>
       <c r="K131" t="n">
-        <v>1.898391433026318</v>
+        <v>1.898391433029715</v>
       </c>
       <c r="L131" t="n">
-        <v>44.02344164232335</v>
+        <v>44.02344164232841</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>10.86255706230495</v>
+        <v>10.50658820414483</v>
       </c>
       <c r="B132" t="n">
         <v>90</v>
@@ -5441,31 +5441,31 @@
         <v>-25</v>
       </c>
       <c r="D132" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="E132" t="n">
-        <v>9.699347069291385</v>
+        <v>9.674792499509962</v>
       </c>
       <c r="F132" t="n">
-        <v>4.985069224042773</v>
+        <v>4.997753447165163</v>
       </c>
       <c r="G132" t="n">
         <v>0.9137793267857967</v>
       </c>
       <c r="H132" t="n">
-        <v>2.615721871101633</v>
+        <v>2.615721871101264</v>
       </c>
       <c r="I132" t="n">
-        <v>52.29043361349095</v>
+        <v>52.2904336135009</v>
       </c>
       <c r="J132" t="n">
         <v>0.9</v>
       </c>
       <c r="K132" t="n">
-        <v>1.882707929980482</v>
+        <v>1.88270792998054</v>
       </c>
       <c r="L132" t="n">
-        <v>44.48654708293421</v>
+        <v>44.48654708292889</v>
       </c>
     </row>
   </sheetData>
